--- a/kcylog/kcylog-ui/public/sbcz.xlsx
+++ b/kcylog/kcylog-ui/public/sbcz.xlsx
@@ -4,17 +4,17 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27660" windowHeight="11620"/>
+    <workbookView windowWidth="27660" windowHeight="11640" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="工程测绘部" sheetId="2" r:id="rId1"/>
-    <sheet name="管线工程部 " sheetId="3" r:id="rId2"/>
+    <sheet name="管线工程部" sheetId="3" r:id="rId2"/>
     <sheet name="不动产测绘部" sheetId="4" r:id="rId3"/>
     <sheet name="地理信息部" sheetId="5" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">工程测绘部!$A$1:$P$19</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'管线工程部 '!$A$1:$Q$19</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">管线工程部!$A$1:$Q$19</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">不动产测绘部!$A$1:$P$19</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">地理信息部!$A$1:$Q$19</definedName>
   </definedNames>
@@ -759,6 +759,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>2025年度福清分公司</t>
     </r>
     <r>
@@ -804,6 +810,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>2025年度福清分公司</t>
     </r>
     <r>
@@ -828,6 +840,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>2025年度福清分公司</t>
     </r>
     <r>
@@ -1782,7 +1800,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="80">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1798,9 +1816,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1825,16 +1840,10 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="176" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="176" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1852,9 +1861,6 @@
     <xf numFmtId="176" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1867,18 +1873,12 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="176" fontId="6" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1888,15 +1888,9 @@
     <xf numFmtId="176" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="176" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="176" fontId="6" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1951,9 +1945,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1968,60 +1959,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -2553,815 +2490,815 @@
   <dimension ref="A1:R19"/>
   <sheetFormatPr defaultColWidth="9.69230769230769" defaultRowHeight="17.6"/>
   <cols>
-    <col min="1" max="1" width="10.6346153846154" style="62" customWidth="1"/>
-    <col min="2" max="2" width="11.3076923076923" style="62" customWidth="1"/>
-    <col min="3" max="3" width="12.1153846153846" style="62" customWidth="1"/>
-    <col min="4" max="16" width="11.3076923076923" style="62" customWidth="1"/>
-    <col min="17" max="16384" width="9.69230769230769" style="62"/>
+    <col min="1" max="1" width="10.6346153846154" style="1" customWidth="1"/>
+    <col min="2" max="2" width="11.3076923076923" style="1" customWidth="1"/>
+    <col min="3" max="3" width="12.1153846153846" style="1" customWidth="1"/>
+    <col min="4" max="16" width="11.3076923076923" style="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.69230769230769" style="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="42" customHeight="1" spans="1:16">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
-      <c r="E1" s="65"/>
-      <c r="F1" s="65"/>
-      <c r="G1" s="65"/>
-      <c r="H1" s="65"/>
-      <c r="I1" s="65"/>
-      <c r="J1" s="65"/>
-      <c r="K1" s="65"/>
-      <c r="L1" s="65"/>
-      <c r="M1" s="65"/>
-      <c r="N1" s="65"/>
-      <c r="O1" s="65"/>
-      <c r="P1" s="65"/>
-    </row>
-    <row r="2" s="62" customFormat="1" ht="20" customHeight="1" spans="1:16">
-      <c r="A2" s="66" t="s">
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
+      <c r="G1" s="6"/>
+      <c r="H1" s="6"/>
+      <c r="I1" s="6"/>
+      <c r="J1" s="6"/>
+      <c r="K1" s="6"/>
+      <c r="L1" s="6"/>
+      <c r="M1" s="6"/>
+      <c r="N1" s="6"/>
+      <c r="O1" s="6"/>
+      <c r="P1" s="6"/>
+    </row>
+    <row r="2" s="1" customFormat="1" ht="20" customHeight="1" spans="1:16">
+      <c r="A2" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="66"/>
-      <c r="C2" s="66"/>
-      <c r="D2" s="66"/>
-      <c r="E2" s="66"/>
-      <c r="F2" s="66"/>
-      <c r="G2" s="66"/>
-      <c r="H2" s="66"/>
-      <c r="I2" s="66"/>
-      <c r="J2" s="66"/>
-      <c r="K2" s="66"/>
-      <c r="L2" s="66"/>
-      <c r="M2" s="66"/>
-      <c r="N2" s="66"/>
-      <c r="O2" s="66"/>
-      <c r="P2" s="66"/>
+      <c r="B2" s="7"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="7"/>
+      <c r="G2" s="7"/>
+      <c r="H2" s="7"/>
+      <c r="I2" s="7"/>
+      <c r="J2" s="7"/>
+      <c r="K2" s="7"/>
+      <c r="L2" s="7"/>
+      <c r="M2" s="7"/>
+      <c r="N2" s="7"/>
+      <c r="O2" s="7"/>
+      <c r="P2" s="7"/>
     </row>
     <row r="3" ht="26" customHeight="1" spans="1:16">
-      <c r="A3" s="67" t="s">
+      <c r="A3" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="67"/>
-      <c r="C3" s="67"/>
-      <c r="D3" s="67" t="s">
+      <c r="B3" s="8"/>
+      <c r="C3" s="8"/>
+      <c r="D3" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="67"/>
-      <c r="F3" s="67"/>
-      <c r="G3" s="67"/>
-      <c r="H3" s="67"/>
-      <c r="I3" s="67"/>
-      <c r="J3" s="67"/>
-      <c r="K3" s="67"/>
-      <c r="L3" s="67"/>
-      <c r="M3" s="67"/>
-      <c r="N3" s="67"/>
-      <c r="O3" s="76"/>
-      <c r="P3" s="77" t="s">
+      <c r="E3" s="8"/>
+      <c r="F3" s="8"/>
+      <c r="G3" s="8"/>
+      <c r="H3" s="8"/>
+      <c r="I3" s="8"/>
+      <c r="J3" s="8"/>
+      <c r="K3" s="8"/>
+      <c r="L3" s="8"/>
+      <c r="M3" s="8"/>
+      <c r="N3" s="8"/>
+      <c r="O3" s="48"/>
+      <c r="P3" s="50" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="4" ht="26" customHeight="1" spans="1:16">
-      <c r="A4" s="68"/>
-      <c r="B4" s="68"/>
-      <c r="C4" s="68"/>
-      <c r="D4" s="68" t="s">
+      <c r="A4" s="10"/>
+      <c r="B4" s="10"/>
+      <c r="C4" s="10"/>
+      <c r="D4" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="68" t="s">
+      <c r="E4" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="F4" s="68" t="s">
+      <c r="F4" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="68" t="s">
+      <c r="G4" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="H4" s="68" t="s">
+      <c r="H4" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="I4" s="68" t="s">
+      <c r="I4" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="J4" s="68" t="s">
+      <c r="J4" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="K4" s="68" t="s">
+      <c r="K4" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="L4" s="68" t="s">
+      <c r="L4" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="M4" s="68" t="s">
+      <c r="M4" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="N4" s="68" t="s">
+      <c r="N4" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="O4" s="78" t="s">
+      <c r="O4" s="49" t="s">
         <v>16</v>
       </c>
-      <c r="P4" s="79"/>
-    </row>
-    <row r="5" s="63" customFormat="1" ht="33" customHeight="1" spans="1:16">
-      <c r="A5" s="69" t="s">
+      <c r="P4" s="51"/>
+    </row>
+    <row r="5" s="2" customFormat="1" ht="33" customHeight="1" spans="1:16">
+      <c r="A5" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="69" t="s">
+      <c r="B5" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="C5" s="69"/>
-      <c r="D5" s="37" t="s">
+      <c r="C5" s="12"/>
+      <c r="D5" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="E5" s="37" t="s">
+      <c r="E5" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="F5" s="37" t="s">
+      <c r="F5" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="G5" s="37" t="s">
+      <c r="G5" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="H5" s="37" t="s">
+      <c r="H5" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="I5" s="37" t="s">
+      <c r="I5" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="J5" s="37" t="s">
+      <c r="J5" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="K5" s="37" t="s">
+      <c r="K5" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="L5" s="37" t="s">
+      <c r="L5" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="M5" s="37" t="s">
+      <c r="M5" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="N5" s="37" t="s">
+      <c r="N5" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="O5" s="45" t="s">
+      <c r="O5" s="37" t="s">
         <v>30</v>
       </c>
-      <c r="P5" s="50" t="s">
+      <c r="P5" s="42" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="6" s="63" customFormat="1" ht="33" customHeight="1" spans="1:16">
-      <c r="A6" s="69"/>
-      <c r="B6" s="69" t="s">
+    <row r="6" s="2" customFormat="1" ht="33" customHeight="1" spans="1:16">
+      <c r="A6" s="12"/>
+      <c r="B6" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="C6" s="69"/>
-      <c r="D6" s="37" t="s">
+      <c r="C6" s="12"/>
+      <c r="D6" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="E6" s="37" t="s">
+      <c r="E6" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="F6" s="37" t="s">
+      <c r="F6" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="G6" s="37" t="s">
+      <c r="G6" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="H6" s="37" t="s">
+      <c r="H6" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="I6" s="37" t="s">
+      <c r="I6" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="J6" s="37" t="s">
+      <c r="J6" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="K6" s="37" t="s">
+      <c r="K6" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="L6" s="37" t="s">
+      <c r="L6" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="M6" s="37" t="s">
+      <c r="M6" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="N6" s="37" t="s">
+      <c r="N6" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="O6" s="45" t="s">
+      <c r="O6" s="37" t="s">
         <v>44</v>
       </c>
-      <c r="P6" s="50" t="s">
+      <c r="P6" s="42" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="7" s="63" customFormat="1" ht="33" customHeight="1" spans="1:16">
-      <c r="A7" s="69"/>
-      <c r="B7" s="69" t="s">
+    <row r="7" s="2" customFormat="1" ht="33" customHeight="1" spans="1:16">
+      <c r="A7" s="12"/>
+      <c r="B7" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="C7" s="69"/>
-      <c r="D7" s="37" t="s">
+      <c r="C7" s="12"/>
+      <c r="D7" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="E7" s="37" t="s">
+      <c r="E7" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="F7" s="37" t="s">
+      <c r="F7" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="G7" s="37" t="s">
+      <c r="G7" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="H7" s="37" t="s">
+      <c r="H7" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="I7" s="37" t="s">
+      <c r="I7" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="J7" s="37" t="s">
+      <c r="J7" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="K7" s="37" t="s">
+      <c r="K7" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="L7" s="37" t="s">
+      <c r="L7" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="M7" s="37" t="s">
+      <c r="M7" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="N7" s="37" t="s">
+      <c r="N7" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="O7" s="45" t="s">
+      <c r="O7" s="37" t="s">
         <v>58</v>
       </c>
-      <c r="P7" s="50" t="s">
+      <c r="P7" s="42" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="8" s="63" customFormat="1" ht="33" customHeight="1" spans="1:16">
-      <c r="A8" s="69"/>
-      <c r="B8" s="69" t="s">
+    <row r="8" s="2" customFormat="1" ht="33" customHeight="1" spans="1:16">
+      <c r="A8" s="12"/>
+      <c r="B8" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="C8" s="69"/>
-      <c r="D8" s="37" t="s">
+      <c r="C8" s="12"/>
+      <c r="D8" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="E8" s="37" t="s">
+      <c r="E8" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="F8" s="37" t="s">
+      <c r="F8" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="G8" s="37" t="s">
+      <c r="G8" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="H8" s="37" t="s">
+      <c r="H8" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="I8" s="37" t="s">
+      <c r="I8" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="J8" s="37" t="s">
+      <c r="J8" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="K8" s="37" t="s">
+      <c r="K8" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="L8" s="37" t="s">
+      <c r="L8" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="M8" s="37" t="s">
+      <c r="M8" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="N8" s="37" t="s">
+      <c r="N8" s="14" t="s">
         <v>71</v>
       </c>
-      <c r="O8" s="45" t="s">
+      <c r="O8" s="37" t="s">
         <v>72</v>
       </c>
-      <c r="P8" s="50" t="s">
+      <c r="P8" s="42" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="9" s="63" customFormat="1" ht="33" customHeight="1" spans="1:16">
-      <c r="A9" s="69"/>
-      <c r="B9" s="69" t="s">
+    <row r="9" s="2" customFormat="1" ht="33" customHeight="1" spans="1:16">
+      <c r="A9" s="12"/>
+      <c r="B9" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="C9" s="69"/>
-      <c r="D9" s="37" t="s">
+      <c r="C9" s="12"/>
+      <c r="D9" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="E9" s="37" t="s">
+      <c r="E9" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="F9" s="37" t="s">
+      <c r="F9" s="14" t="s">
         <v>77</v>
       </c>
-      <c r="G9" s="37" t="s">
+      <c r="G9" s="14" t="s">
         <v>78</v>
       </c>
-      <c r="H9" s="37" t="s">
+      <c r="H9" s="14" t="s">
         <v>79</v>
       </c>
-      <c r="I9" s="37" t="s">
+      <c r="I9" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="J9" s="37" t="s">
+      <c r="J9" s="14" t="s">
         <v>81</v>
       </c>
-      <c r="K9" s="37" t="s">
+      <c r="K9" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="L9" s="37" t="s">
+      <c r="L9" s="14" t="s">
         <v>83</v>
       </c>
-      <c r="M9" s="37" t="s">
+      <c r="M9" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="N9" s="37" t="s">
+      <c r="N9" s="14" t="s">
         <v>85</v>
       </c>
-      <c r="O9" s="45" t="s">
+      <c r="O9" s="37" t="s">
         <v>86</v>
       </c>
-      <c r="P9" s="50" t="s">
+      <c r="P9" s="42" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="10" s="63" customFormat="1" ht="33" customHeight="1" spans="1:16">
-      <c r="A10" s="69"/>
-      <c r="B10" s="69" t="s">
+    <row r="10" s="2" customFormat="1" ht="33" customHeight="1" spans="1:16">
+      <c r="A10" s="12"/>
+      <c r="B10" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="C10" s="69"/>
-      <c r="D10" s="37" t="s">
+      <c r="C10" s="12"/>
+      <c r="D10" s="14" t="s">
         <v>89</v>
       </c>
-      <c r="E10" s="37" t="s">
+      <c r="E10" s="14" t="s">
         <v>90</v>
       </c>
-      <c r="F10" s="37" t="s">
+      <c r="F10" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="G10" s="37" t="s">
+      <c r="G10" s="14" t="s">
         <v>92</v>
       </c>
-      <c r="H10" s="37" t="s">
+      <c r="H10" s="14" t="s">
         <v>93</v>
       </c>
-      <c r="I10" s="37" t="s">
+      <c r="I10" s="14" t="s">
         <v>94</v>
       </c>
-      <c r="J10" s="37" t="s">
+      <c r="J10" s="14" t="s">
         <v>95</v>
       </c>
-      <c r="K10" s="37" t="s">
+      <c r="K10" s="14" t="s">
         <v>96</v>
       </c>
-      <c r="L10" s="37" t="s">
+      <c r="L10" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="M10" s="37" t="s">
+      <c r="M10" s="14" t="s">
         <v>98</v>
       </c>
-      <c r="N10" s="37" t="s">
+      <c r="N10" s="14" t="s">
         <v>99</v>
       </c>
-      <c r="O10" s="37" t="s">
+      <c r="O10" s="14" t="s">
         <v>100</v>
       </c>
-      <c r="P10" s="50" t="s">
+      <c r="P10" s="42" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="11" s="63" customFormat="1" ht="33" customHeight="1" spans="1:16">
-      <c r="A11" s="69"/>
-      <c r="B11" s="69" t="s">
+    <row r="11" s="2" customFormat="1" ht="33" customHeight="1" spans="1:16">
+      <c r="A11" s="12"/>
+      <c r="B11" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="C11" s="69"/>
-      <c r="D11" s="37" t="s">
+      <c r="C11" s="12"/>
+      <c r="D11" s="14" t="s">
         <v>103</v>
       </c>
-      <c r="E11" s="37" t="s">
+      <c r="E11" s="14" t="s">
         <v>104</v>
       </c>
-      <c r="F11" s="37" t="s">
+      <c r="F11" s="14" t="s">
         <v>105</v>
       </c>
-      <c r="G11" s="37" t="s">
+      <c r="G11" s="14" t="s">
         <v>106</v>
       </c>
-      <c r="H11" s="37" t="s">
+      <c r="H11" s="14" t="s">
         <v>107</v>
       </c>
-      <c r="I11" s="37" t="s">
+      <c r="I11" s="14" t="s">
         <v>108</v>
       </c>
-      <c r="J11" s="37" t="s">
+      <c r="J11" s="14" t="s">
         <v>109</v>
       </c>
-      <c r="K11" s="37" t="s">
+      <c r="K11" s="14" t="s">
         <v>110</v>
       </c>
-      <c r="L11" s="37" t="s">
+      <c r="L11" s="14" t="s">
         <v>111</v>
       </c>
-      <c r="M11" s="37" t="s">
+      <c r="M11" s="14" t="s">
         <v>112</v>
       </c>
-      <c r="N11" s="37" t="s">
+      <c r="N11" s="14" t="s">
         <v>113</v>
       </c>
-      <c r="O11" s="45" t="s">
+      <c r="O11" s="37" t="s">
         <v>114</v>
       </c>
-      <c r="P11" s="50" t="s">
+      <c r="P11" s="42" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="12" s="64" customFormat="1" ht="33" customHeight="1" spans="1:16">
-      <c r="A12" s="70"/>
-      <c r="B12" s="70" t="s">
+    <row r="12" s="3" customFormat="1" ht="33" customHeight="1" spans="1:16">
+      <c r="A12" s="15"/>
+      <c r="B12" s="15" t="s">
         <v>116</v>
       </c>
-      <c r="C12" s="70"/>
-      <c r="D12" s="38" t="s">
+      <c r="C12" s="15"/>
+      <c r="D12" s="30" t="s">
         <v>117</v>
       </c>
-      <c r="E12" s="38" t="s">
+      <c r="E12" s="30" t="s">
         <v>118</v>
       </c>
-      <c r="F12" s="38" t="s">
+      <c r="F12" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="G12" s="38" t="s">
+      <c r="G12" s="30" t="s">
         <v>120</v>
       </c>
-      <c r="H12" s="38" t="s">
+      <c r="H12" s="30" t="s">
         <v>121</v>
       </c>
-      <c r="I12" s="38" t="s">
+      <c r="I12" s="30" t="s">
         <v>122</v>
       </c>
-      <c r="J12" s="38" t="s">
+      <c r="J12" s="30" t="s">
         <v>123</v>
       </c>
-      <c r="K12" s="38" t="s">
+      <c r="K12" s="30" t="s">
         <v>124</v>
       </c>
-      <c r="L12" s="38" t="s">
+      <c r="L12" s="30" t="s">
         <v>125</v>
       </c>
-      <c r="M12" s="38" t="s">
+      <c r="M12" s="30" t="s">
         <v>126</v>
       </c>
-      <c r="N12" s="38" t="s">
+      <c r="N12" s="30" t="s">
         <v>127</v>
       </c>
-      <c r="O12" s="38" t="s">
+      <c r="O12" s="30" t="s">
         <v>128</v>
       </c>
-      <c r="P12" s="54" t="s">
+      <c r="P12" s="46" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="13" s="63" customFormat="1" ht="85" customHeight="1" spans="1:16">
-      <c r="A13" s="69" t="s">
+    <row r="13" s="2" customFormat="1" ht="85" customHeight="1" spans="1:16">
+      <c r="A13" s="12" t="s">
         <v>130</v>
       </c>
-      <c r="B13" s="69" t="s">
+      <c r="B13" s="12" t="s">
         <v>131</v>
       </c>
-      <c r="C13" s="69" t="s">
+      <c r="C13" s="12" t="s">
         <v>132</v>
       </c>
-      <c r="D13" s="37" t="s">
+      <c r="D13" s="14" t="s">
         <v>133</v>
       </c>
-      <c r="E13" s="37" t="s">
+      <c r="E13" s="14" t="s">
         <v>134</v>
       </c>
-      <c r="F13" s="37" t="s">
+      <c r="F13" s="14" t="s">
         <v>135</v>
       </c>
-      <c r="G13" s="37" t="s">
+      <c r="G13" s="14" t="s">
         <v>136</v>
       </c>
-      <c r="H13" s="37" t="s">
+      <c r="H13" s="14" t="s">
         <v>137</v>
       </c>
-      <c r="I13" s="37" t="s">
+      <c r="I13" s="14" t="s">
         <v>138</v>
       </c>
-      <c r="J13" s="37" t="s">
+      <c r="J13" s="14" t="s">
         <v>139</v>
       </c>
-      <c r="K13" s="37" t="s">
+      <c r="K13" s="14" t="s">
         <v>140</v>
       </c>
-      <c r="L13" s="37" t="s">
+      <c r="L13" s="14" t="s">
         <v>141</v>
       </c>
-      <c r="M13" s="37" t="s">
+      <c r="M13" s="14" t="s">
         <v>142</v>
       </c>
-      <c r="N13" s="37" t="s">
+      <c r="N13" s="14" t="s">
         <v>143</v>
       </c>
-      <c r="O13" s="45" t="s">
+      <c r="O13" s="37" t="s">
         <v>144</v>
       </c>
-      <c r="P13" s="50" t="s">
+      <c r="P13" s="42" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="14" s="63" customFormat="1" ht="97" customHeight="1" spans="1:16">
-      <c r="A14" s="69"/>
-      <c r="B14" s="69"/>
-      <c r="C14" s="69" t="s">
+    <row r="14" s="2" customFormat="1" ht="97" customHeight="1" spans="1:16">
+      <c r="A14" s="12"/>
+      <c r="B14" s="12"/>
+      <c r="C14" s="12" t="s">
         <v>146</v>
       </c>
-      <c r="D14" s="37" t="s">
+      <c r="D14" s="14" t="s">
         <v>147</v>
       </c>
-      <c r="E14" s="37" t="s">
+      <c r="E14" s="14" t="s">
         <v>148</v>
       </c>
-      <c r="F14" s="37" t="s">
+      <c r="F14" s="14" t="s">
         <v>149</v>
       </c>
-      <c r="G14" s="37" t="s">
+      <c r="G14" s="14" t="s">
         <v>150</v>
       </c>
-      <c r="H14" s="37" t="s">
+      <c r="H14" s="14" t="s">
         <v>151</v>
       </c>
-      <c r="I14" s="37" t="s">
+      <c r="I14" s="14" t="s">
         <v>152</v>
       </c>
-      <c r="J14" s="37" t="s">
+      <c r="J14" s="14" t="s">
         <v>153</v>
       </c>
-      <c r="K14" s="37" t="s">
+      <c r="K14" s="14" t="s">
         <v>154</v>
       </c>
-      <c r="L14" s="37" t="s">
+      <c r="L14" s="14" t="s">
         <v>155</v>
       </c>
-      <c r="M14" s="37" t="s">
+      <c r="M14" s="14" t="s">
         <v>156</v>
       </c>
-      <c r="N14" s="37" t="s">
+      <c r="N14" s="14" t="s">
         <v>157</v>
       </c>
-      <c r="O14" s="45" t="s">
+      <c r="O14" s="37" t="s">
         <v>158</v>
       </c>
-      <c r="P14" s="50" t="s">
+      <c r="P14" s="42" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="15" s="63" customFormat="1" ht="33" customHeight="1" spans="1:16">
-      <c r="A15" s="69"/>
-      <c r="B15" s="69" t="s">
+    <row r="15" s="2" customFormat="1" ht="33" customHeight="1" spans="1:16">
+      <c r="A15" s="12"/>
+      <c r="B15" s="12" t="s">
         <v>160</v>
       </c>
-      <c r="C15" s="69"/>
-      <c r="D15" s="37" t="s">
+      <c r="C15" s="12"/>
+      <c r="D15" s="14" t="s">
         <v>161</v>
       </c>
-      <c r="E15" s="37" t="s">
+      <c r="E15" s="14" t="s">
         <v>162</v>
       </c>
-      <c r="F15" s="37" t="s">
+      <c r="F15" s="14" t="s">
         <v>163</v>
       </c>
-      <c r="G15" s="37" t="s">
+      <c r="G15" s="14" t="s">
         <v>164</v>
       </c>
-      <c r="H15" s="37" t="s">
+      <c r="H15" s="14" t="s">
         <v>165</v>
       </c>
-      <c r="I15" s="37" t="s">
+      <c r="I15" s="14" t="s">
         <v>166</v>
       </c>
-      <c r="J15" s="37" t="s">
+      <c r="J15" s="14" t="s">
         <v>167</v>
       </c>
-      <c r="K15" s="37" t="s">
+      <c r="K15" s="14" t="s">
         <v>168</v>
       </c>
-      <c r="L15" s="37" t="s">
+      <c r="L15" s="14" t="s">
         <v>169</v>
       </c>
-      <c r="M15" s="37" t="s">
+      <c r="M15" s="14" t="s">
         <v>170</v>
       </c>
-      <c r="N15" s="37" t="s">
+      <c r="N15" s="14" t="s">
         <v>171</v>
       </c>
-      <c r="O15" s="45" t="s">
+      <c r="O15" s="37" t="s">
         <v>172</v>
       </c>
-      <c r="P15" s="50" t="s">
+      <c r="P15" s="42" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="16" s="63" customFormat="1" ht="33" customHeight="1" spans="1:16">
-      <c r="A16" s="69"/>
-      <c r="B16" s="71" t="s">
+    <row r="16" s="2" customFormat="1" ht="33" customHeight="1" spans="1:16">
+      <c r="A16" s="12"/>
+      <c r="B16" s="17" t="s">
         <v>174</v>
       </c>
-      <c r="C16" s="72"/>
-      <c r="D16" s="37" t="s">
+      <c r="C16" s="18"/>
+      <c r="D16" s="14" t="s">
         <v>175</v>
       </c>
-      <c r="E16" s="37" t="s">
+      <c r="E16" s="14" t="s">
         <v>176</v>
       </c>
-      <c r="F16" s="37" t="s">
+      <c r="F16" s="14" t="s">
         <v>177</v>
       </c>
-      <c r="G16" s="37" t="s">
+      <c r="G16" s="14" t="s">
         <v>178</v>
       </c>
-      <c r="H16" s="37" t="s">
+      <c r="H16" s="14" t="s">
         <v>179</v>
       </c>
-      <c r="I16" s="37" t="s">
+      <c r="I16" s="14" t="s">
         <v>180</v>
       </c>
-      <c r="J16" s="37" t="s">
+      <c r="J16" s="14" t="s">
         <v>181</v>
       </c>
-      <c r="K16" s="37" t="s">
+      <c r="K16" s="14" t="s">
         <v>182</v>
       </c>
-      <c r="L16" s="37" t="s">
+      <c r="L16" s="14" t="s">
         <v>183</v>
       </c>
-      <c r="M16" s="37" t="s">
+      <c r="M16" s="14" t="s">
         <v>184</v>
       </c>
-      <c r="N16" s="37" t="s">
+      <c r="N16" s="14" t="s">
         <v>185</v>
       </c>
-      <c r="O16" s="45" t="s">
+      <c r="O16" s="37" t="s">
         <v>186</v>
       </c>
-      <c r="P16" s="50" t="s">
+      <c r="P16" s="42" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="17" s="63" customFormat="1" ht="33" customHeight="1" spans="1:18">
-      <c r="A17" s="69"/>
-      <c r="B17" s="71" t="s">
+    <row r="17" s="2" customFormat="1" ht="33" customHeight="1" spans="1:18">
+      <c r="A17" s="12"/>
+      <c r="B17" s="17" t="s">
         <v>188</v>
       </c>
-      <c r="C17" s="72"/>
-      <c r="D17" s="37" t="s">
+      <c r="C17" s="18"/>
+      <c r="D17" s="14" t="s">
         <v>189</v>
       </c>
-      <c r="E17" s="37" t="s">
+      <c r="E17" s="14" t="s">
         <v>190</v>
       </c>
-      <c r="F17" s="37" t="s">
+      <c r="F17" s="14" t="s">
         <v>191</v>
       </c>
-      <c r="G17" s="37" t="s">
+      <c r="G17" s="14" t="s">
         <v>192</v>
       </c>
-      <c r="H17" s="37" t="s">
+      <c r="H17" s="14" t="s">
         <v>193</v>
       </c>
-      <c r="I17" s="37" t="s">
+      <c r="I17" s="14" t="s">
         <v>194</v>
       </c>
-      <c r="J17" s="37" t="s">
+      <c r="J17" s="14" t="s">
         <v>195</v>
       </c>
-      <c r="K17" s="37" t="s">
+      <c r="K17" s="14" t="s">
         <v>196</v>
       </c>
-      <c r="L17" s="37" t="s">
+      <c r="L17" s="14" t="s">
         <v>197</v>
       </c>
-      <c r="M17" s="37" t="s">
+      <c r="M17" s="14" t="s">
         <v>198</v>
       </c>
-      <c r="N17" s="37" t="s">
+      <c r="N17" s="14" t="s">
         <v>199</v>
       </c>
-      <c r="O17" s="45" t="s">
+      <c r="O17" s="37" t="s">
         <v>200</v>
       </c>
-      <c r="P17" s="50" t="s">
+      <c r="P17" s="42" t="s">
         <v>201</v>
       </c>
-      <c r="R17" s="63" t="s">
+      <c r="R17" s="2" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="18" s="64" customFormat="1" ht="33" customHeight="1" spans="1:16">
-      <c r="A18" s="70"/>
-      <c r="B18" s="73" t="s">
+    <row r="18" s="3" customFormat="1" ht="33" customHeight="1" spans="1:16">
+      <c r="A18" s="15"/>
+      <c r="B18" s="20" t="s">
         <v>203</v>
       </c>
-      <c r="C18" s="74"/>
-      <c r="D18" s="38" t="s">
+      <c r="C18" s="21"/>
+      <c r="D18" s="30" t="s">
         <v>204</v>
       </c>
-      <c r="E18" s="38" t="s">
+      <c r="E18" s="30" t="s">
         <v>205</v>
       </c>
-      <c r="F18" s="38" t="s">
+      <c r="F18" s="30" t="s">
         <v>206</v>
       </c>
-      <c r="G18" s="38" t="s">
+      <c r="G18" s="30" t="s">
         <v>207</v>
       </c>
-      <c r="H18" s="38" t="s">
+      <c r="H18" s="30" t="s">
         <v>208</v>
       </c>
-      <c r="I18" s="38" t="s">
+      <c r="I18" s="30" t="s">
         <v>209</v>
       </c>
-      <c r="J18" s="38" t="s">
+      <c r="J18" s="30" t="s">
         <v>210</v>
       </c>
-      <c r="K18" s="38" t="s">
+      <c r="K18" s="30" t="s">
         <v>211</v>
       </c>
-      <c r="L18" s="38" t="s">
+      <c r="L18" s="30" t="s">
         <v>212</v>
       </c>
-      <c r="M18" s="38" t="s">
+      <c r="M18" s="30" t="s">
         <v>213</v>
       </c>
-      <c r="N18" s="38" t="s">
+      <c r="N18" s="30" t="s">
         <v>214</v>
       </c>
-      <c r="O18" s="38" t="s">
+      <c r="O18" s="30" t="s">
         <v>215</v>
       </c>
-      <c r="P18" s="54" t="s">
+      <c r="P18" s="46" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="19" s="64" customFormat="1" ht="42" customHeight="1" spans="1:16">
-      <c r="A19" s="75" t="s">
+    <row r="19" s="3" customFormat="1" ht="42" customHeight="1" spans="1:16">
+      <c r="A19" s="23" t="s">
         <v>217</v>
       </c>
-      <c r="B19" s="75"/>
-      <c r="C19" s="75"/>
-      <c r="D19" s="39" t="s">
+      <c r="B19" s="23"/>
+      <c r="C19" s="23"/>
+      <c r="D19" s="31" t="s">
         <v>218</v>
       </c>
-      <c r="E19" s="39" t="s">
+      <c r="E19" s="31" t="s">
         <v>219</v>
       </c>
-      <c r="F19" s="39" t="s">
+      <c r="F19" s="31" t="s">
         <v>220</v>
       </c>
-      <c r="G19" s="39" t="s">
+      <c r="G19" s="31" t="s">
         <v>221</v>
       </c>
-      <c r="H19" s="39" t="s">
+      <c r="H19" s="31" t="s">
         <v>222</v>
       </c>
-      <c r="I19" s="39" t="s">
+      <c r="I19" s="31" t="s">
         <v>223</v>
       </c>
-      <c r="J19" s="39" t="s">
+      <c r="J19" s="31" t="s">
         <v>224</v>
       </c>
-      <c r="K19" s="39" t="s">
+      <c r="K19" s="31" t="s">
         <v>225</v>
       </c>
-      <c r="L19" s="39" t="s">
+      <c r="L19" s="31" t="s">
         <v>226</v>
       </c>
-      <c r="M19" s="39" t="s">
+      <c r="M19" s="31" t="s">
         <v>227</v>
       </c>
-      <c r="N19" s="39" t="s">
+      <c r="N19" s="31" t="s">
         <v>228</v>
       </c>
-      <c r="O19" s="39" t="s">
+      <c r="O19" s="31" t="s">
         <v>229</v>
       </c>
-      <c r="P19" s="54" t="s">
+      <c r="P19" s="46" t="s">
         <v>230</v>
       </c>
     </row>
@@ -3403,874 +3340,874 @@
   <dimension ref="A1:R20"/>
   <sheetFormatPr defaultColWidth="9.69230769230769" defaultRowHeight="17.6"/>
   <cols>
-    <col min="1" max="1" width="10.6346153846154" style="5" customWidth="1"/>
-    <col min="2" max="2" width="11.3076923076923" style="5" customWidth="1"/>
-    <col min="3" max="4" width="12.1153846153846" style="5" customWidth="1"/>
-    <col min="5" max="17" width="11.3076923076923" style="5" customWidth="1"/>
-    <col min="18" max="18" width="11.7115384615385" style="5" customWidth="1"/>
-    <col min="19" max="16384" width="9.69230769230769" style="5"/>
+    <col min="1" max="1" width="10.6346153846154" style="1" customWidth="1"/>
+    <col min="2" max="2" width="11.3076923076923" style="1" customWidth="1"/>
+    <col min="3" max="4" width="12.1153846153846" style="1" customWidth="1"/>
+    <col min="5" max="17" width="11.3076923076923" style="1" customWidth="1"/>
+    <col min="18" max="18" width="11.7115384615385" style="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.69230769230769" style="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="42" customHeight="1" spans="1:17">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="6" t="s">
         <v>231</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
-      <c r="H1" s="7"/>
-      <c r="I1" s="7"/>
-      <c r="J1" s="7"/>
-      <c r="K1" s="7"/>
-      <c r="L1" s="7"/>
-      <c r="M1" s="7"/>
-      <c r="N1" s="7"/>
-      <c r="O1" s="7"/>
-      <c r="P1" s="7"/>
-      <c r="Q1" s="7"/>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
+      <c r="G1" s="6"/>
+      <c r="H1" s="6"/>
+      <c r="I1" s="6"/>
+      <c r="J1" s="6"/>
+      <c r="K1" s="6"/>
+      <c r="L1" s="6"/>
+      <c r="M1" s="6"/>
+      <c r="N1" s="6"/>
+      <c r="O1" s="6"/>
+      <c r="P1" s="6"/>
+      <c r="Q1" s="6"/>
     </row>
     <row r="2" s="1" customFormat="1" ht="20" customHeight="1" spans="1:17">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="8"/>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="8"/>
-      <c r="G2" s="8"/>
-      <c r="H2" s="8"/>
-      <c r="I2" s="8"/>
-      <c r="J2" s="8"/>
-      <c r="K2" s="8"/>
-      <c r="L2" s="8"/>
-      <c r="M2" s="8"/>
-      <c r="N2" s="8"/>
-      <c r="O2" s="8"/>
-      <c r="P2" s="8"/>
-      <c r="Q2" s="8"/>
+      <c r="B2" s="7"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="7"/>
+      <c r="G2" s="7"/>
+      <c r="H2" s="7"/>
+      <c r="I2" s="7"/>
+      <c r="J2" s="7"/>
+      <c r="K2" s="7"/>
+      <c r="L2" s="7"/>
+      <c r="M2" s="7"/>
+      <c r="N2" s="7"/>
+      <c r="O2" s="7"/>
+      <c r="P2" s="7"/>
+      <c r="Q2" s="7"/>
     </row>
     <row r="3" ht="26" customHeight="1" spans="1:18">
-      <c r="A3" s="9" t="s">
+      <c r="A3" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="9"/>
-      <c r="C3" s="9"/>
-      <c r="D3" s="10" t="s">
+      <c r="B3" s="8"/>
+      <c r="C3" s="8"/>
+      <c r="D3" s="9" t="s">
         <v>232</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="E3" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="56"/>
-      <c r="G3" s="56"/>
-      <c r="H3" s="56"/>
-      <c r="I3" s="56"/>
-      <c r="J3" s="56"/>
-      <c r="K3" s="56"/>
-      <c r="L3" s="56"/>
-      <c r="M3" s="56"/>
-      <c r="N3" s="56"/>
-      <c r="O3" s="56"/>
-      <c r="P3" s="57"/>
-      <c r="Q3" s="59" t="s">
+      <c r="F3" s="8"/>
+      <c r="G3" s="8"/>
+      <c r="H3" s="8"/>
+      <c r="I3" s="8"/>
+      <c r="J3" s="8"/>
+      <c r="K3" s="8"/>
+      <c r="L3" s="8"/>
+      <c r="M3" s="8"/>
+      <c r="N3" s="8"/>
+      <c r="O3" s="8"/>
+      <c r="P3" s="48"/>
+      <c r="Q3" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="R3" s="47" t="s">
+      <c r="R3" s="39" t="s">
         <v>233</v>
       </c>
     </row>
     <row r="4" ht="26" customHeight="1" spans="1:18">
-      <c r="A4" s="11"/>
-      <c r="B4" s="11"/>
-      <c r="C4" s="11"/>
-      <c r="D4" s="12"/>
-      <c r="E4" s="11" t="s">
+      <c r="A4" s="10"/>
+      <c r="B4" s="10"/>
+      <c r="C4" s="10"/>
+      <c r="D4" s="11"/>
+      <c r="E4" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="F4" s="11" t="s">
+      <c r="F4" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="G4" s="11" t="s">
+      <c r="G4" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="H4" s="11" t="s">
+      <c r="H4" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="I4" s="11" t="s">
+      <c r="I4" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="J4" s="11" t="s">
+      <c r="J4" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="K4" s="11" t="s">
+      <c r="K4" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="L4" s="11" t="s">
+      <c r="L4" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="M4" s="11" t="s">
+      <c r="M4" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="N4" s="11" t="s">
+      <c r="N4" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="O4" s="11" t="s">
+      <c r="O4" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="P4" s="58" t="s">
+      <c r="P4" s="49" t="s">
         <v>16</v>
       </c>
-      <c r="Q4" s="60"/>
-      <c r="R4" s="49"/>
+      <c r="Q4" s="51"/>
+      <c r="R4" s="41"/>
     </row>
     <row r="5" s="2" customFormat="1" ht="33" customHeight="1" spans="1:18">
-      <c r="A5" s="13" t="s">
+      <c r="A5" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="13" t="s">
+      <c r="B5" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="C5" s="14"/>
-      <c r="D5" s="15" t="s">
+      <c r="C5" s="12"/>
+      <c r="D5" s="13" t="s">
         <v>234</v>
       </c>
-      <c r="E5" s="37" t="s">
+      <c r="E5" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="F5" s="37" t="s">
+      <c r="F5" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="G5" s="37" t="s">
+      <c r="G5" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="H5" s="37" t="s">
+      <c r="H5" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="I5" s="37" t="s">
+      <c r="I5" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="J5" s="37" t="s">
+      <c r="J5" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="K5" s="37" t="s">
+      <c r="K5" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="L5" s="37" t="s">
+      <c r="L5" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="M5" s="37" t="s">
+      <c r="M5" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="N5" s="37" t="s">
+      <c r="N5" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="O5" s="37" t="s">
+      <c r="O5" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="P5" s="45" t="s">
+      <c r="P5" s="37" t="s">
         <v>30</v>
       </c>
-      <c r="Q5" s="50" t="s">
+      <c r="Q5" s="42" t="s">
         <v>31</v>
       </c>
-      <c r="R5" s="49"/>
+      <c r="R5" s="41"/>
     </row>
     <row r="6" s="2" customFormat="1" ht="33" customHeight="1" spans="1:18">
-      <c r="A6" s="13"/>
-      <c r="B6" s="13" t="s">
+      <c r="A6" s="12"/>
+      <c r="B6" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="C6" s="13"/>
-      <c r="D6" s="16"/>
-      <c r="E6" s="37" t="s">
+      <c r="C6" s="12"/>
+      <c r="D6" s="13"/>
+      <c r="E6" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="F6" s="37" t="s">
+      <c r="F6" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="G6" s="37" t="s">
+      <c r="G6" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="H6" s="37" t="s">
+      <c r="H6" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="I6" s="37" t="s">
+      <c r="I6" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="J6" s="37" t="s">
+      <c r="J6" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="K6" s="37" t="s">
+      <c r="K6" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="L6" s="37" t="s">
+      <c r="L6" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="M6" s="37" t="s">
+      <c r="M6" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="N6" s="37" t="s">
+      <c r="N6" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="O6" s="37" t="s">
+      <c r="O6" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="P6" s="45" t="s">
+      <c r="P6" s="37" t="s">
         <v>44</v>
       </c>
-      <c r="Q6" s="50" t="s">
+      <c r="Q6" s="42" t="s">
         <v>45</v>
       </c>
-      <c r="R6" s="51" t="s">
+      <c r="R6" s="43" t="s">
         <v>235</v>
       </c>
     </row>
     <row r="7" s="2" customFormat="1" ht="33" customHeight="1" spans="1:18">
-      <c r="A7" s="13"/>
-      <c r="B7" s="13" t="s">
+      <c r="A7" s="12"/>
+      <c r="B7" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="C7" s="13"/>
-      <c r="D7" s="16"/>
-      <c r="E7" s="37" t="s">
+      <c r="C7" s="12"/>
+      <c r="D7" s="13"/>
+      <c r="E7" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="F7" s="37" t="s">
+      <c r="F7" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="G7" s="37" t="s">
+      <c r="G7" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="H7" s="37" t="s">
+      <c r="H7" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="I7" s="37" t="s">
+      <c r="I7" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="J7" s="37" t="s">
+      <c r="J7" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="K7" s="37" t="s">
+      <c r="K7" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="L7" s="37" t="s">
+      <c r="L7" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="M7" s="37" t="s">
+      <c r="M7" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="N7" s="37" t="s">
+      <c r="N7" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="O7" s="37" t="s">
+      <c r="O7" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="P7" s="45" t="s">
+      <c r="P7" s="37" t="s">
         <v>58</v>
       </c>
-      <c r="Q7" s="50" t="s">
+      <c r="Q7" s="42" t="s">
         <v>59</v>
       </c>
-      <c r="R7" s="52"/>
+      <c r="R7" s="44"/>
     </row>
     <row r="8" s="2" customFormat="1" ht="33" customHeight="1" spans="1:18">
-      <c r="A8" s="13"/>
-      <c r="B8" s="13" t="s">
+      <c r="A8" s="12"/>
+      <c r="B8" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="C8" s="14"/>
-      <c r="D8" s="16"/>
-      <c r="E8" s="37" t="s">
+      <c r="C8" s="12"/>
+      <c r="D8" s="13"/>
+      <c r="E8" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="F8" s="37" t="s">
+      <c r="F8" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="G8" s="37" t="s">
+      <c r="G8" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="H8" s="37" t="s">
+      <c r="H8" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="I8" s="37" t="s">
+      <c r="I8" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="J8" s="37" t="s">
+      <c r="J8" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="K8" s="37" t="s">
+      <c r="K8" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="L8" s="37" t="s">
+      <c r="L8" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="M8" s="37" t="s">
+      <c r="M8" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="N8" s="37" t="s">
+      <c r="N8" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="O8" s="37" t="s">
+      <c r="O8" s="14" t="s">
         <v>71</v>
       </c>
-      <c r="P8" s="45" t="s">
+      <c r="P8" s="37" t="s">
         <v>72</v>
       </c>
-      <c r="Q8" s="50" t="s">
+      <c r="Q8" s="42" t="s">
         <v>73</v>
       </c>
-      <c r="R8" s="52"/>
+      <c r="R8" s="44"/>
     </row>
     <row r="9" s="2" customFormat="1" ht="33" customHeight="1" spans="1:18">
-      <c r="A9" s="13"/>
-      <c r="B9" s="13" t="s">
+      <c r="A9" s="12"/>
+      <c r="B9" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="C9" s="13"/>
-      <c r="D9" s="16">
+      <c r="C9" s="12"/>
+      <c r="D9" s="13">
         <v>297900</v>
       </c>
-      <c r="E9" s="37" t="s">
+      <c r="E9" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="F9" s="37" t="s">
+      <c r="F9" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="G9" s="37" t="s">
+      <c r="G9" s="14" t="s">
         <v>77</v>
       </c>
-      <c r="H9" s="37" t="s">
+      <c r="H9" s="14" t="s">
         <v>78</v>
       </c>
-      <c r="I9" s="37" t="s">
+      <c r="I9" s="14" t="s">
         <v>79</v>
       </c>
-      <c r="J9" s="37" t="s">
+      <c r="J9" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="K9" s="37" t="s">
+      <c r="K9" s="14" t="s">
         <v>81</v>
       </c>
-      <c r="L9" s="37" t="s">
+      <c r="L9" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="M9" s="37" t="s">
+      <c r="M9" s="14" t="s">
         <v>83</v>
       </c>
-      <c r="N9" s="37" t="s">
+      <c r="N9" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="O9" s="37" t="s">
+      <c r="O9" s="14" t="s">
         <v>85</v>
       </c>
-      <c r="P9" s="45" t="s">
+      <c r="P9" s="37" t="s">
         <v>86</v>
       </c>
-      <c r="Q9" s="50" t="s">
+      <c r="Q9" s="42" t="s">
         <v>87</v>
       </c>
-      <c r="R9" s="53"/>
+      <c r="R9" s="45"/>
     </row>
     <row r="10" s="2" customFormat="1" ht="33" customHeight="1" spans="1:17">
-      <c r="A10" s="13"/>
-      <c r="B10" s="13" t="s">
+      <c r="A10" s="12"/>
+      <c r="B10" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="C10" s="14"/>
-      <c r="D10" s="15" t="s">
+      <c r="C10" s="12"/>
+      <c r="D10" s="13" t="s">
         <v>234</v>
       </c>
-      <c r="E10" s="37" t="s">
+      <c r="E10" s="14" t="s">
         <v>89</v>
       </c>
-      <c r="F10" s="37" t="s">
+      <c r="F10" s="14" t="s">
         <v>90</v>
       </c>
-      <c r="G10" s="37" t="s">
+      <c r="G10" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="H10" s="37" t="s">
+      <c r="H10" s="14" t="s">
         <v>92</v>
       </c>
-      <c r="I10" s="37" t="s">
+      <c r="I10" s="14" t="s">
         <v>93</v>
       </c>
-      <c r="J10" s="37" t="s">
+      <c r="J10" s="14" t="s">
         <v>94</v>
       </c>
-      <c r="K10" s="37" t="s">
+      <c r="K10" s="14" t="s">
         <v>95</v>
       </c>
-      <c r="L10" s="37" t="s">
+      <c r="L10" s="14" t="s">
         <v>96</v>
       </c>
-      <c r="M10" s="37" t="s">
+      <c r="M10" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="N10" s="37" t="s">
+      <c r="N10" s="14" t="s">
         <v>98</v>
       </c>
-      <c r="O10" s="37" t="s">
+      <c r="O10" s="14" t="s">
         <v>99</v>
       </c>
-      <c r="P10" s="37" t="s">
+      <c r="P10" s="14" t="s">
         <v>100</v>
       </c>
-      <c r="Q10" s="50" t="s">
+      <c r="Q10" s="42" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="11" s="2" customFormat="1" ht="33" customHeight="1" spans="1:17">
-      <c r="A11" s="13"/>
-      <c r="B11" s="13" t="s">
+      <c r="A11" s="12"/>
+      <c r="B11" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="C11" s="13"/>
-      <c r="D11" s="15" t="s">
+      <c r="C11" s="12"/>
+      <c r="D11" s="13" t="s">
         <v>234</v>
       </c>
-      <c r="E11" s="37" t="s">
+      <c r="E11" s="14" t="s">
         <v>103</v>
       </c>
-      <c r="F11" s="37" t="s">
+      <c r="F11" s="14" t="s">
         <v>104</v>
       </c>
-      <c r="G11" s="37" t="s">
+      <c r="G11" s="14" t="s">
         <v>105</v>
       </c>
-      <c r="H11" s="37" t="s">
+      <c r="H11" s="14" t="s">
         <v>106</v>
       </c>
-      <c r="I11" s="37" t="s">
+      <c r="I11" s="14" t="s">
         <v>107</v>
       </c>
-      <c r="J11" s="37" t="s">
+      <c r="J11" s="14" t="s">
         <v>108</v>
       </c>
-      <c r="K11" s="37" t="s">
+      <c r="K11" s="14" t="s">
         <v>109</v>
       </c>
-      <c r="L11" s="37" t="s">
+      <c r="L11" s="14" t="s">
         <v>110</v>
       </c>
-      <c r="M11" s="37" t="s">
+      <c r="M11" s="14" t="s">
         <v>111</v>
       </c>
-      <c r="N11" s="37" t="s">
+      <c r="N11" s="14" t="s">
         <v>112</v>
       </c>
-      <c r="O11" s="37" t="s">
+      <c r="O11" s="14" t="s">
         <v>113</v>
       </c>
-      <c r="P11" s="45" t="s">
+      <c r="P11" s="37" t="s">
         <v>114</v>
       </c>
-      <c r="Q11" s="50" t="s">
+      <c r="Q11" s="42" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="12" s="3" customFormat="1" ht="33" customHeight="1" spans="1:18">
-      <c r="A12" s="18"/>
-      <c r="B12" s="18" t="s">
+      <c r="A12" s="15"/>
+      <c r="B12" s="15" t="s">
         <v>116</v>
       </c>
-      <c r="C12" s="18"/>
-      <c r="D12" s="19" t="s">
+      <c r="C12" s="15"/>
+      <c r="D12" s="16" t="s">
         <v>234</v>
       </c>
-      <c r="E12" s="38" t="s">
+      <c r="E12" s="30" t="s">
         <v>117</v>
       </c>
-      <c r="F12" s="38" t="s">
+      <c r="F12" s="30" t="s">
         <v>118</v>
       </c>
-      <c r="G12" s="38" t="s">
+      <c r="G12" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="H12" s="38" t="s">
+      <c r="H12" s="30" t="s">
         <v>120</v>
       </c>
-      <c r="I12" s="38" t="s">
+      <c r="I12" s="30" t="s">
         <v>121</v>
       </c>
-      <c r="J12" s="38" t="s">
+      <c r="J12" s="30" t="s">
         <v>122</v>
       </c>
-      <c r="K12" s="38" t="s">
+      <c r="K12" s="30" t="s">
         <v>123</v>
       </c>
-      <c r="L12" s="38" t="s">
+      <c r="L12" s="30" t="s">
         <v>124</v>
       </c>
-      <c r="M12" s="38" t="s">
+      <c r="M12" s="30" t="s">
         <v>125</v>
       </c>
-      <c r="N12" s="38" t="s">
+      <c r="N12" s="30" t="s">
         <v>126</v>
       </c>
-      <c r="O12" s="38" t="s">
+      <c r="O12" s="30" t="s">
         <v>127</v>
       </c>
-      <c r="P12" s="38" t="s">
+      <c r="P12" s="30" t="s">
         <v>128</v>
       </c>
-      <c r="Q12" s="54" t="s">
+      <c r="Q12" s="46" t="s">
         <v>129</v>
       </c>
-      <c r="R12" s="61"/>
+      <c r="R12" s="52"/>
     </row>
     <row r="13" s="2" customFormat="1" ht="56" customHeight="1" spans="1:17">
-      <c r="A13" s="13" t="s">
+      <c r="A13" s="12" t="s">
         <v>130</v>
       </c>
-      <c r="B13" s="13" t="s">
+      <c r="B13" s="12" t="s">
         <v>131</v>
       </c>
-      <c r="C13" s="13" t="s">
+      <c r="C13" s="12" t="s">
         <v>132</v>
       </c>
-      <c r="D13" s="15" t="s">
+      <c r="D13" s="13" t="s">
         <v>234</v>
       </c>
-      <c r="E13" s="37" t="s">
+      <c r="E13" s="14" t="s">
         <v>133</v>
       </c>
-      <c r="F13" s="37" t="s">
+      <c r="F13" s="14" t="s">
         <v>134</v>
       </c>
-      <c r="G13" s="37" t="s">
+      <c r="G13" s="14" t="s">
         <v>135</v>
       </c>
-      <c r="H13" s="37" t="s">
+      <c r="H13" s="14" t="s">
         <v>136</v>
       </c>
-      <c r="I13" s="37" t="s">
+      <c r="I13" s="14" t="s">
         <v>137</v>
       </c>
-      <c r="J13" s="37" t="s">
+      <c r="J13" s="14" t="s">
         <v>138</v>
       </c>
-      <c r="K13" s="37" t="s">
+      <c r="K13" s="14" t="s">
         <v>139</v>
       </c>
-      <c r="L13" s="37" t="s">
+      <c r="L13" s="14" t="s">
         <v>140</v>
       </c>
-      <c r="M13" s="37" t="s">
+      <c r="M13" s="14" t="s">
         <v>141</v>
       </c>
-      <c r="N13" s="37" t="s">
+      <c r="N13" s="14" t="s">
         <v>142</v>
       </c>
-      <c r="O13" s="37" t="s">
+      <c r="O13" s="14" t="s">
         <v>143</v>
       </c>
-      <c r="P13" s="45" t="s">
+      <c r="P13" s="37" t="s">
         <v>144</v>
       </c>
-      <c r="Q13" s="50" t="s">
+      <c r="Q13" s="42" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="14" s="2" customFormat="1" ht="63" customHeight="1" spans="1:17">
-      <c r="A14" s="14"/>
-      <c r="B14" s="14"/>
-      <c r="C14" s="13" t="s">
+      <c r="A14" s="12"/>
+      <c r="B14" s="12"/>
+      <c r="C14" s="12" t="s">
         <v>146</v>
       </c>
-      <c r="D14" s="15" t="s">
+      <c r="D14" s="13" t="s">
         <v>234</v>
       </c>
-      <c r="E14" s="37" t="s">
+      <c r="E14" s="14" t="s">
         <v>147</v>
       </c>
-      <c r="F14" s="37" t="s">
+      <c r="F14" s="14" t="s">
         <v>148</v>
       </c>
-      <c r="G14" s="37" t="s">
+      <c r="G14" s="14" t="s">
         <v>149</v>
       </c>
-      <c r="H14" s="37" t="s">
+      <c r="H14" s="14" t="s">
         <v>150</v>
       </c>
-      <c r="I14" s="37" t="s">
+      <c r="I14" s="14" t="s">
         <v>151</v>
       </c>
-      <c r="J14" s="37" t="s">
+      <c r="J14" s="14" t="s">
         <v>152</v>
       </c>
-      <c r="K14" s="37" t="s">
+      <c r="K14" s="14" t="s">
         <v>153</v>
       </c>
-      <c r="L14" s="37" t="s">
+      <c r="L14" s="14" t="s">
         <v>154</v>
       </c>
-      <c r="M14" s="37" t="s">
+      <c r="M14" s="14" t="s">
         <v>155</v>
       </c>
-      <c r="N14" s="37" t="s">
+      <c r="N14" s="14" t="s">
         <v>156</v>
       </c>
-      <c r="O14" s="37" t="s">
+      <c r="O14" s="14" t="s">
         <v>157</v>
       </c>
-      <c r="P14" s="45" t="s">
+      <c r="P14" s="37" t="s">
         <v>158</v>
       </c>
-      <c r="Q14" s="50" t="s">
+      <c r="Q14" s="42" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="15" s="2" customFormat="1" ht="33" customHeight="1" spans="1:17">
-      <c r="A15" s="14"/>
-      <c r="B15" s="13" t="s">
+      <c r="A15" s="12"/>
+      <c r="B15" s="12" t="s">
         <v>160</v>
       </c>
-      <c r="C15" s="14"/>
-      <c r="D15" s="15" t="s">
+      <c r="C15" s="12"/>
+      <c r="D15" s="13" t="s">
         <v>234</v>
       </c>
-      <c r="E15" s="37" t="s">
+      <c r="E15" s="14" t="s">
         <v>161</v>
       </c>
-      <c r="F15" s="37" t="s">
+      <c r="F15" s="14" t="s">
         <v>162</v>
       </c>
-      <c r="G15" s="37" t="s">
+      <c r="G15" s="14" t="s">
         <v>163</v>
       </c>
-      <c r="H15" s="37" t="s">
+      <c r="H15" s="14" t="s">
         <v>164</v>
       </c>
-      <c r="I15" s="37" t="s">
+      <c r="I15" s="14" t="s">
         <v>165</v>
       </c>
-      <c r="J15" s="37" t="s">
+      <c r="J15" s="14" t="s">
         <v>166</v>
       </c>
-      <c r="K15" s="37" t="s">
+      <c r="K15" s="14" t="s">
         <v>167</v>
       </c>
-      <c r="L15" s="37" t="s">
+      <c r="L15" s="14" t="s">
         <v>168</v>
       </c>
-      <c r="M15" s="37" t="s">
+      <c r="M15" s="14" t="s">
         <v>169</v>
       </c>
-      <c r="N15" s="37" t="s">
+      <c r="N15" s="14" t="s">
         <v>170</v>
       </c>
-      <c r="O15" s="37" t="s">
+      <c r="O15" s="14" t="s">
         <v>171</v>
       </c>
-      <c r="P15" s="45" t="s">
+      <c r="P15" s="37" t="s">
         <v>172</v>
       </c>
-      <c r="Q15" s="50" t="s">
+      <c r="Q15" s="42" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="16" s="2" customFormat="1" ht="33" customHeight="1" spans="1:17">
-      <c r="A16" s="14"/>
-      <c r="B16" s="20" t="s">
+      <c r="A16" s="12"/>
+      <c r="B16" s="17" t="s">
         <v>174</v>
       </c>
-      <c r="C16" s="21"/>
-      <c r="D16" s="22" t="s">
+      <c r="C16" s="18"/>
+      <c r="D16" s="19" t="s">
         <v>234</v>
       </c>
-      <c r="E16" s="37" t="s">
+      <c r="E16" s="14" t="s">
         <v>175</v>
       </c>
-      <c r="F16" s="37" t="s">
+      <c r="F16" s="14" t="s">
         <v>176</v>
       </c>
-      <c r="G16" s="37" t="s">
+      <c r="G16" s="14" t="s">
         <v>177</v>
       </c>
-      <c r="H16" s="37" t="s">
+      <c r="H16" s="14" t="s">
         <v>178</v>
       </c>
-      <c r="I16" s="37" t="s">
+      <c r="I16" s="14" t="s">
         <v>179</v>
       </c>
-      <c r="J16" s="37" t="s">
+      <c r="J16" s="14" t="s">
         <v>180</v>
       </c>
-      <c r="K16" s="37" t="s">
+      <c r="K16" s="14" t="s">
         <v>181</v>
       </c>
-      <c r="L16" s="37" t="s">
+      <c r="L16" s="14" t="s">
         <v>182</v>
       </c>
-      <c r="M16" s="37" t="s">
+      <c r="M16" s="14" t="s">
         <v>183</v>
       </c>
-      <c r="N16" s="37" t="s">
+      <c r="N16" s="14" t="s">
         <v>184</v>
       </c>
-      <c r="O16" s="37" t="s">
+      <c r="O16" s="14" t="s">
         <v>185</v>
       </c>
-      <c r="P16" s="45" t="s">
+      <c r="P16" s="37" t="s">
         <v>186</v>
       </c>
-      <c r="Q16" s="50" t="s">
+      <c r="Q16" s="42" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="17" s="2" customFormat="1" ht="33" customHeight="1" spans="1:17">
-      <c r="A17" s="14"/>
-      <c r="B17" s="20" t="s">
+      <c r="A17" s="12"/>
+      <c r="B17" s="17" t="s">
         <v>188</v>
       </c>
-      <c r="C17" s="21"/>
-      <c r="D17" s="22" t="s">
+      <c r="C17" s="18"/>
+      <c r="D17" s="19" t="s">
         <v>234</v>
       </c>
-      <c r="E17" s="37" t="s">
+      <c r="E17" s="14" t="s">
         <v>189</v>
       </c>
-      <c r="F17" s="37" t="s">
+      <c r="F17" s="14" t="s">
         <v>190</v>
       </c>
-      <c r="G17" s="37" t="s">
+      <c r="G17" s="14" t="s">
         <v>191</v>
       </c>
-      <c r="H17" s="37" t="s">
+      <c r="H17" s="14" t="s">
         <v>192</v>
       </c>
-      <c r="I17" s="37" t="s">
+      <c r="I17" s="14" t="s">
         <v>193</v>
       </c>
-      <c r="J17" s="37" t="s">
+      <c r="J17" s="14" t="s">
         <v>194</v>
       </c>
-      <c r="K17" s="37" t="s">
+      <c r="K17" s="14" t="s">
         <v>195</v>
       </c>
-      <c r="L17" s="37" t="s">
+      <c r="L17" s="14" t="s">
         <v>196</v>
       </c>
-      <c r="M17" s="37" t="s">
+      <c r="M17" s="14" t="s">
         <v>197</v>
       </c>
-      <c r="N17" s="37" t="s">
+      <c r="N17" s="14" t="s">
         <v>198</v>
       </c>
-      <c r="O17" s="37" t="s">
+      <c r="O17" s="14" t="s">
         <v>199</v>
       </c>
-      <c r="P17" s="45" t="s">
+      <c r="P17" s="37" t="s">
         <v>200</v>
       </c>
-      <c r="Q17" s="50" t="s">
+      <c r="Q17" s="42" t="s">
         <v>201</v>
       </c>
     </row>
     <row r="18" s="3" customFormat="1" ht="33" customHeight="1" spans="1:18">
-      <c r="A18" s="23"/>
-      <c r="B18" s="24" t="s">
+      <c r="A18" s="15"/>
+      <c r="B18" s="20" t="s">
         <v>203</v>
       </c>
-      <c r="C18" s="25"/>
-      <c r="D18" s="26" t="s">
+      <c r="C18" s="21"/>
+      <c r="D18" s="22" t="s">
         <v>234</v>
       </c>
-      <c r="E18" s="38" t="s">
+      <c r="E18" s="30" t="s">
         <v>204</v>
       </c>
-      <c r="F18" s="38" t="s">
+      <c r="F18" s="30" t="s">
         <v>205</v>
       </c>
-      <c r="G18" s="38" t="s">
+      <c r="G18" s="30" t="s">
         <v>206</v>
       </c>
-      <c r="H18" s="38" t="s">
+      <c r="H18" s="30" t="s">
         <v>207</v>
       </c>
-      <c r="I18" s="38" t="s">
+      <c r="I18" s="30" t="s">
         <v>208</v>
       </c>
-      <c r="J18" s="38" t="s">
+      <c r="J18" s="30" t="s">
         <v>209</v>
       </c>
-      <c r="K18" s="38" t="s">
+      <c r="K18" s="30" t="s">
         <v>210</v>
       </c>
-      <c r="L18" s="38" t="s">
+      <c r="L18" s="30" t="s">
         <v>211</v>
       </c>
-      <c r="M18" s="38" t="s">
+      <c r="M18" s="30" t="s">
         <v>212</v>
       </c>
-      <c r="N18" s="38" t="s">
+      <c r="N18" s="30" t="s">
         <v>213</v>
       </c>
-      <c r="O18" s="38" t="s">
+      <c r="O18" s="30" t="s">
         <v>214</v>
       </c>
-      <c r="P18" s="38" t="s">
+      <c r="P18" s="30" t="s">
         <v>215</v>
       </c>
-      <c r="Q18" s="54" t="s">
+      <c r="Q18" s="46" t="s">
         <v>216</v>
       </c>
-      <c r="R18" s="61"/>
+      <c r="R18" s="52"/>
     </row>
     <row r="19" s="3" customFormat="1" ht="42" customHeight="1" spans="1:18">
-      <c r="A19" s="27" t="s">
+      <c r="A19" s="23" t="s">
         <v>217</v>
       </c>
-      <c r="B19" s="28"/>
-      <c r="C19" s="28"/>
-      <c r="D19" s="29" t="s">
+      <c r="B19" s="23"/>
+      <c r="C19" s="23"/>
+      <c r="D19" s="24" t="s">
         <v>234</v>
       </c>
-      <c r="E19" s="39" t="s">
+      <c r="E19" s="31" t="s">
         <v>218</v>
       </c>
-      <c r="F19" s="39" t="s">
+      <c r="F19" s="31" t="s">
         <v>219</v>
       </c>
-      <c r="G19" s="39" t="s">
+      <c r="G19" s="31" t="s">
         <v>220</v>
       </c>
-      <c r="H19" s="39" t="s">
+      <c r="H19" s="31" t="s">
         <v>221</v>
       </c>
-      <c r="I19" s="39" t="s">
+      <c r="I19" s="31" t="s">
         <v>222</v>
       </c>
-      <c r="J19" s="39" t="s">
+      <c r="J19" s="31" t="s">
         <v>223</v>
       </c>
-      <c r="K19" s="39" t="s">
+      <c r="K19" s="31" t="s">
         <v>224</v>
       </c>
-      <c r="L19" s="39" t="s">
+      <c r="L19" s="31" t="s">
         <v>225</v>
       </c>
-      <c r="M19" s="39" t="s">
+      <c r="M19" s="31" t="s">
         <v>226</v>
       </c>
-      <c r="N19" s="39" t="s">
+      <c r="N19" s="31" t="s">
         <v>227</v>
       </c>
-      <c r="O19" s="39" t="s">
+      <c r="O19" s="31" t="s">
         <v>228</v>
       </c>
-      <c r="P19" s="39" t="s">
+      <c r="P19" s="31" t="s">
         <v>229</v>
       </c>
-      <c r="Q19" s="54" t="s">
+      <c r="Q19" s="46" t="s">
         <v>230</v>
       </c>
-      <c r="R19" s="61"/>
+      <c r="R19" s="52"/>
     </row>
     <row r="20" ht="82" customHeight="1" spans="1:5">
       <c r="A20" s="2" t="s">
@@ -4278,10 +4215,10 @@
       </c>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
-      <c r="D20" s="55" t="s">
+      <c r="D20" s="47" t="s">
         <v>237</v>
       </c>
-      <c r="E20" s="55" t="s">
+      <c r="E20" s="47" t="s">
         <v>238</v>
       </c>
     </row>
@@ -4327,812 +4264,812 @@
   <dimension ref="A1:P19"/>
   <sheetFormatPr defaultColWidth="9.69230769230769" defaultRowHeight="17.6"/>
   <cols>
-    <col min="1" max="1" width="10.6346153846154" style="5" customWidth="1"/>
-    <col min="2" max="2" width="11.3076923076923" style="5" customWidth="1"/>
-    <col min="3" max="3" width="12.1153846153846" style="5" customWidth="1"/>
-    <col min="4" max="16" width="11.3076923076923" style="6" customWidth="1"/>
-    <col min="17" max="16384" width="9.69230769230769" style="5"/>
+    <col min="1" max="1" width="10.6346153846154" style="1" customWidth="1"/>
+    <col min="2" max="2" width="11.3076923076923" style="1" customWidth="1"/>
+    <col min="3" max="3" width="12.1153846153846" style="1" customWidth="1"/>
+    <col min="4" max="16" width="11.3076923076923" style="5" customWidth="1"/>
+    <col min="17" max="16384" width="9.69230769230769" style="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="42" customHeight="1" spans="1:16">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="6" t="s">
         <v>239</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
-      <c r="G1" s="32"/>
-      <c r="H1" s="32"/>
-      <c r="I1" s="32"/>
-      <c r="J1" s="32"/>
-      <c r="K1" s="32"/>
-      <c r="L1" s="32"/>
-      <c r="M1" s="32"/>
-      <c r="N1" s="32"/>
-      <c r="O1" s="32"/>
-      <c r="P1" s="32"/>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
+      <c r="H1" s="26"/>
+      <c r="I1" s="26"/>
+      <c r="J1" s="26"/>
+      <c r="K1" s="26"/>
+      <c r="L1" s="26"/>
+      <c r="M1" s="26"/>
+      <c r="N1" s="26"/>
+      <c r="O1" s="26"/>
+      <c r="P1" s="26"/>
     </row>
     <row r="2" s="1" customFormat="1" ht="20" customHeight="1" spans="1:16">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="8"/>
-      <c r="C2" s="8"/>
-      <c r="D2" s="33"/>
-      <c r="E2" s="33"/>
-      <c r="F2" s="33"/>
-      <c r="G2" s="33"/>
-      <c r="H2" s="33"/>
-      <c r="I2" s="33"/>
-      <c r="J2" s="33"/>
-      <c r="K2" s="33"/>
-      <c r="L2" s="33"/>
-      <c r="M2" s="33"/>
-      <c r="N2" s="33"/>
-      <c r="O2" s="33"/>
-      <c r="P2" s="33"/>
+      <c r="B2" s="7"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
+      <c r="F2" s="27"/>
+      <c r="G2" s="27"/>
+      <c r="H2" s="27"/>
+      <c r="I2" s="27"/>
+      <c r="J2" s="27"/>
+      <c r="K2" s="27"/>
+      <c r="L2" s="27"/>
+      <c r="M2" s="27"/>
+      <c r="N2" s="27"/>
+      <c r="O2" s="27"/>
+      <c r="P2" s="27"/>
     </row>
     <row r="3" ht="26" customHeight="1" spans="1:16">
-      <c r="A3" s="9" t="s">
+      <c r="A3" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="9"/>
-      <c r="C3" s="9"/>
-      <c r="D3" s="34" t="s">
+      <c r="B3" s="8"/>
+      <c r="C3" s="8"/>
+      <c r="D3" s="28" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="35"/>
-      <c r="F3" s="35"/>
-      <c r="G3" s="35"/>
-      <c r="H3" s="35"/>
-      <c r="I3" s="35"/>
-      <c r="J3" s="35"/>
-      <c r="K3" s="35"/>
-      <c r="L3" s="35"/>
-      <c r="M3" s="35"/>
-      <c r="N3" s="35"/>
-      <c r="O3" s="43"/>
-      <c r="P3" s="46" t="s">
+      <c r="E3" s="28"/>
+      <c r="F3" s="28"/>
+      <c r="G3" s="28"/>
+      <c r="H3" s="28"/>
+      <c r="I3" s="28"/>
+      <c r="J3" s="28"/>
+      <c r="K3" s="28"/>
+      <c r="L3" s="28"/>
+      <c r="M3" s="28"/>
+      <c r="N3" s="28"/>
+      <c r="O3" s="35"/>
+      <c r="P3" s="38" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="4" ht="26" customHeight="1" spans="1:16">
-      <c r="A4" s="11"/>
-      <c r="B4" s="11"/>
-      <c r="C4" s="11"/>
-      <c r="D4" s="36" t="s">
+      <c r="A4" s="10"/>
+      <c r="B4" s="10"/>
+      <c r="C4" s="10"/>
+      <c r="D4" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="36" t="s">
+      <c r="E4" s="29" t="s">
         <v>6</v>
       </c>
-      <c r="F4" s="36" t="s">
+      <c r="F4" s="29" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="36" t="s">
+      <c r="G4" s="29" t="s">
         <v>8</v>
       </c>
-      <c r="H4" s="36" t="s">
+      <c r="H4" s="29" t="s">
         <v>9</v>
       </c>
-      <c r="I4" s="36" t="s">
+      <c r="I4" s="29" t="s">
         <v>10</v>
       </c>
-      <c r="J4" s="36" t="s">
+      <c r="J4" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="K4" s="36" t="s">
+      <c r="K4" s="29" t="s">
         <v>12</v>
       </c>
-      <c r="L4" s="36" t="s">
+      <c r="L4" s="29" t="s">
         <v>13</v>
       </c>
-      <c r="M4" s="36" t="s">
+      <c r="M4" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="N4" s="36" t="s">
+      <c r="N4" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="O4" s="44" t="s">
+      <c r="O4" s="36" t="s">
         <v>16</v>
       </c>
-      <c r="P4" s="48"/>
+      <c r="P4" s="40"/>
     </row>
     <row r="5" s="2" customFormat="1" ht="33" customHeight="1" spans="1:16">
-      <c r="A5" s="13" t="s">
+      <c r="A5" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="13" t="s">
+      <c r="B5" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="C5" s="14"/>
-      <c r="D5" s="37" t="s">
+      <c r="C5" s="12"/>
+      <c r="D5" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="E5" s="37" t="s">
+      <c r="E5" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="F5" s="37" t="s">
+      <c r="F5" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="G5" s="37" t="s">
+      <c r="G5" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="H5" s="37" t="s">
+      <c r="H5" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="I5" s="37" t="s">
+      <c r="I5" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="J5" s="37" t="s">
+      <c r="J5" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="K5" s="37" t="s">
+      <c r="K5" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="L5" s="37" t="s">
+      <c r="L5" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="M5" s="37" t="s">
+      <c r="M5" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="N5" s="37" t="s">
+      <c r="N5" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="O5" s="45" t="s">
+      <c r="O5" s="37" t="s">
         <v>30</v>
       </c>
-      <c r="P5" s="50" t="s">
+      <c r="P5" s="42" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="6" s="2" customFormat="1" ht="33" customHeight="1" spans="1:16">
-      <c r="A6" s="13"/>
-      <c r="B6" s="13" t="s">
+      <c r="A6" s="12"/>
+      <c r="B6" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="C6" s="13"/>
-      <c r="D6" s="37" t="s">
+      <c r="C6" s="12"/>
+      <c r="D6" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="E6" s="37" t="s">
+      <c r="E6" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="F6" s="37" t="s">
+      <c r="F6" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="G6" s="37" t="s">
+      <c r="G6" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="H6" s="37" t="s">
+      <c r="H6" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="I6" s="37" t="s">
+      <c r="I6" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="J6" s="37" t="s">
+      <c r="J6" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="K6" s="37" t="s">
+      <c r="K6" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="L6" s="37" t="s">
+      <c r="L6" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="M6" s="37" t="s">
+      <c r="M6" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="N6" s="37" t="s">
+      <c r="N6" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="O6" s="45" t="s">
+      <c r="O6" s="37" t="s">
         <v>44</v>
       </c>
-      <c r="P6" s="50" t="s">
+      <c r="P6" s="42" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="7" s="2" customFormat="1" ht="33" customHeight="1" spans="1:16">
-      <c r="A7" s="13"/>
-      <c r="B7" s="13" t="s">
+      <c r="A7" s="12"/>
+      <c r="B7" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="C7" s="13"/>
-      <c r="D7" s="37" t="s">
+      <c r="C7" s="12"/>
+      <c r="D7" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="E7" s="37" t="s">
+      <c r="E7" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="F7" s="37" t="s">
+      <c r="F7" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="G7" s="37" t="s">
+      <c r="G7" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="H7" s="37" t="s">
+      <c r="H7" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="I7" s="37" t="s">
+      <c r="I7" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="J7" s="37" t="s">
+      <c r="J7" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="K7" s="37" t="s">
+      <c r="K7" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="L7" s="37" t="s">
+      <c r="L7" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="M7" s="37" t="s">
+      <c r="M7" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="N7" s="37" t="s">
+      <c r="N7" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="O7" s="45" t="s">
+      <c r="O7" s="37" t="s">
         <v>58</v>
       </c>
-      <c r="P7" s="50" t="s">
+      <c r="P7" s="42" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="8" s="2" customFormat="1" ht="33" customHeight="1" spans="1:16">
-      <c r="A8" s="13"/>
-      <c r="B8" s="13" t="s">
+      <c r="A8" s="12"/>
+      <c r="B8" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="C8" s="14"/>
-      <c r="D8" s="37" t="s">
+      <c r="C8" s="12"/>
+      <c r="D8" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="E8" s="37" t="s">
+      <c r="E8" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="F8" s="37" t="s">
+      <c r="F8" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="G8" s="37" t="s">
+      <c r="G8" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="H8" s="37" t="s">
+      <c r="H8" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="I8" s="37" t="s">
+      <c r="I8" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="J8" s="37" t="s">
+      <c r="J8" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="K8" s="37" t="s">
+      <c r="K8" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="L8" s="37" t="s">
+      <c r="L8" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="M8" s="37" t="s">
+      <c r="M8" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="N8" s="37" t="s">
+      <c r="N8" s="14" t="s">
         <v>71</v>
       </c>
-      <c r="O8" s="45" t="s">
+      <c r="O8" s="37" t="s">
         <v>72</v>
       </c>
-      <c r="P8" s="50" t="s">
+      <c r="P8" s="42" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="9" s="2" customFormat="1" ht="33" customHeight="1" spans="1:16">
-      <c r="A9" s="13"/>
-      <c r="B9" s="13" t="s">
+      <c r="A9" s="12"/>
+      <c r="B9" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="C9" s="13"/>
-      <c r="D9" s="37" t="s">
+      <c r="C9" s="12"/>
+      <c r="D9" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="E9" s="37" t="s">
+      <c r="E9" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="F9" s="37" t="s">
+      <c r="F9" s="14" t="s">
         <v>77</v>
       </c>
-      <c r="G9" s="37" t="s">
+      <c r="G9" s="14" t="s">
         <v>78</v>
       </c>
-      <c r="H9" s="37" t="s">
+      <c r="H9" s="14" t="s">
         <v>79</v>
       </c>
-      <c r="I9" s="37" t="s">
+      <c r="I9" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="J9" s="37" t="s">
+      <c r="J9" s="14" t="s">
         <v>81</v>
       </c>
-      <c r="K9" s="37" t="s">
+      <c r="K9" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="L9" s="37" t="s">
+      <c r="L9" s="14" t="s">
         <v>83</v>
       </c>
-      <c r="M9" s="37" t="s">
+      <c r="M9" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="N9" s="37" t="s">
+      <c r="N9" s="14" t="s">
         <v>85</v>
       </c>
-      <c r="O9" s="45" t="s">
+      <c r="O9" s="37" t="s">
         <v>86</v>
       </c>
-      <c r="P9" s="50" t="s">
+      <c r="P9" s="42" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="10" s="2" customFormat="1" ht="33" customHeight="1" spans="1:16">
-      <c r="A10" s="13"/>
-      <c r="B10" s="13" t="s">
+      <c r="A10" s="12"/>
+      <c r="B10" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="C10" s="14"/>
-      <c r="D10" s="37" t="s">
+      <c r="C10" s="12"/>
+      <c r="D10" s="14" t="s">
         <v>89</v>
       </c>
-      <c r="E10" s="37" t="s">
+      <c r="E10" s="14" t="s">
         <v>90</v>
       </c>
-      <c r="F10" s="37" t="s">
+      <c r="F10" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="G10" s="37" t="s">
+      <c r="G10" s="14" t="s">
         <v>92</v>
       </c>
-      <c r="H10" s="37" t="s">
+      <c r="H10" s="14" t="s">
         <v>93</v>
       </c>
-      <c r="I10" s="37" t="s">
+      <c r="I10" s="14" t="s">
         <v>94</v>
       </c>
-      <c r="J10" s="37" t="s">
+      <c r="J10" s="14" t="s">
         <v>95</v>
       </c>
-      <c r="K10" s="37" t="s">
+      <c r="K10" s="14" t="s">
         <v>96</v>
       </c>
-      <c r="L10" s="37" t="s">
+      <c r="L10" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="M10" s="37" t="s">
+      <c r="M10" s="14" t="s">
         <v>98</v>
       </c>
-      <c r="N10" s="37" t="s">
+      <c r="N10" s="14" t="s">
         <v>99</v>
       </c>
-      <c r="O10" s="37" t="s">
+      <c r="O10" s="14" t="s">
         <v>100</v>
       </c>
-      <c r="P10" s="50" t="s">
+      <c r="P10" s="42" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="11" s="2" customFormat="1" ht="33" customHeight="1" spans="1:16">
-      <c r="A11" s="13"/>
-      <c r="B11" s="13" t="s">
+      <c r="A11" s="12"/>
+      <c r="B11" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="C11" s="13"/>
-      <c r="D11" s="37" t="s">
+      <c r="C11" s="12"/>
+      <c r="D11" s="14" t="s">
         <v>103</v>
       </c>
-      <c r="E11" s="37" t="s">
+      <c r="E11" s="14" t="s">
         <v>104</v>
       </c>
-      <c r="F11" s="37" t="s">
+      <c r="F11" s="14" t="s">
         <v>105</v>
       </c>
-      <c r="G11" s="37" t="s">
+      <c r="G11" s="14" t="s">
         <v>106</v>
       </c>
-      <c r="H11" s="37" t="s">
+      <c r="H11" s="14" t="s">
         <v>107</v>
       </c>
-      <c r="I11" s="37" t="s">
+      <c r="I11" s="14" t="s">
         <v>108</v>
       </c>
-      <c r="J11" s="37" t="s">
+      <c r="J11" s="14" t="s">
         <v>109</v>
       </c>
-      <c r="K11" s="37" t="s">
+      <c r="K11" s="14" t="s">
         <v>110</v>
       </c>
-      <c r="L11" s="37" t="s">
+      <c r="L11" s="14" t="s">
         <v>111</v>
       </c>
-      <c r="M11" s="37" t="s">
+      <c r="M11" s="14" t="s">
         <v>112</v>
       </c>
-      <c r="N11" s="37" t="s">
+      <c r="N11" s="14" t="s">
         <v>113</v>
       </c>
-      <c r="O11" s="45" t="s">
+      <c r="O11" s="37" t="s">
         <v>114</v>
       </c>
-      <c r="P11" s="50" t="s">
+      <c r="P11" s="42" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="12" s="3" customFormat="1" ht="33" customHeight="1" spans="1:16">
-      <c r="A12" s="18"/>
-      <c r="B12" s="18" t="s">
+      <c r="A12" s="15"/>
+      <c r="B12" s="15" t="s">
         <v>116</v>
       </c>
-      <c r="C12" s="18"/>
-      <c r="D12" s="38" t="s">
+      <c r="C12" s="15"/>
+      <c r="D12" s="30" t="s">
         <v>117</v>
       </c>
-      <c r="E12" s="38" t="s">
+      <c r="E12" s="30" t="s">
         <v>118</v>
       </c>
-      <c r="F12" s="38" t="s">
+      <c r="F12" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="G12" s="38" t="s">
+      <c r="G12" s="30" t="s">
         <v>120</v>
       </c>
-      <c r="H12" s="38" t="s">
+      <c r="H12" s="30" t="s">
         <v>121</v>
       </c>
-      <c r="I12" s="38" t="s">
+      <c r="I12" s="30" t="s">
         <v>122</v>
       </c>
-      <c r="J12" s="38" t="s">
+      <c r="J12" s="30" t="s">
         <v>123</v>
       </c>
-      <c r="K12" s="38" t="s">
+      <c r="K12" s="30" t="s">
         <v>124</v>
       </c>
-      <c r="L12" s="38" t="s">
+      <c r="L12" s="30" t="s">
         <v>125</v>
       </c>
-      <c r="M12" s="38" t="s">
+      <c r="M12" s="30" t="s">
         <v>126</v>
       </c>
-      <c r="N12" s="38" t="s">
+      <c r="N12" s="30" t="s">
         <v>127</v>
       </c>
-      <c r="O12" s="38" t="s">
+      <c r="O12" s="30" t="s">
         <v>128</v>
       </c>
-      <c r="P12" s="54" t="s">
+      <c r="P12" s="46" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="13" s="2" customFormat="1" ht="57" customHeight="1" spans="1:16">
-      <c r="A13" s="13" t="s">
+      <c r="A13" s="12" t="s">
         <v>130</v>
       </c>
-      <c r="B13" s="13" t="s">
+      <c r="B13" s="12" t="s">
         <v>131</v>
       </c>
-      <c r="C13" s="13" t="s">
+      <c r="C13" s="12" t="s">
         <v>132</v>
       </c>
-      <c r="D13" s="37" t="s">
+      <c r="D13" s="14" t="s">
         <v>133</v>
       </c>
-      <c r="E13" s="37" t="s">
+      <c r="E13" s="14" t="s">
         <v>134</v>
       </c>
-      <c r="F13" s="37" t="s">
+      <c r="F13" s="14" t="s">
         <v>135</v>
       </c>
-      <c r="G13" s="37" t="s">
+      <c r="G13" s="14" t="s">
         <v>136</v>
       </c>
-      <c r="H13" s="37" t="s">
+      <c r="H13" s="14" t="s">
         <v>137</v>
       </c>
-      <c r="I13" s="37" t="s">
+      <c r="I13" s="14" t="s">
         <v>138</v>
       </c>
-      <c r="J13" s="37" t="s">
+      <c r="J13" s="14" t="s">
         <v>139</v>
       </c>
-      <c r="K13" s="37" t="s">
+      <c r="K13" s="14" t="s">
         <v>140</v>
       </c>
-      <c r="L13" s="37" t="s">
+      <c r="L13" s="14" t="s">
         <v>141</v>
       </c>
-      <c r="M13" s="37" t="s">
+      <c r="M13" s="14" t="s">
         <v>142</v>
       </c>
-      <c r="N13" s="37" t="s">
+      <c r="N13" s="14" t="s">
         <v>143</v>
       </c>
-      <c r="O13" s="45" t="s">
+      <c r="O13" s="37" t="s">
         <v>144</v>
       </c>
-      <c r="P13" s="50" t="s">
+      <c r="P13" s="42" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="14" s="2" customFormat="1" ht="63" customHeight="1" spans="1:16">
-      <c r="A14" s="14"/>
-      <c r="B14" s="14"/>
-      <c r="C14" s="13" t="s">
+      <c r="A14" s="12"/>
+      <c r="B14" s="12"/>
+      <c r="C14" s="12" t="s">
         <v>146</v>
       </c>
-      <c r="D14" s="37" t="s">
+      <c r="D14" s="14" t="s">
         <v>147</v>
       </c>
-      <c r="E14" s="37" t="s">
+      <c r="E14" s="14" t="s">
         <v>148</v>
       </c>
-      <c r="F14" s="37" t="s">
+      <c r="F14" s="14" t="s">
         <v>149</v>
       </c>
-      <c r="G14" s="37" t="s">
+      <c r="G14" s="14" t="s">
         <v>150</v>
       </c>
-      <c r="H14" s="37" t="s">
+      <c r="H14" s="14" t="s">
         <v>151</v>
       </c>
-      <c r="I14" s="37" t="s">
+      <c r="I14" s="14" t="s">
         <v>152</v>
       </c>
-      <c r="J14" s="37" t="s">
+      <c r="J14" s="14" t="s">
         <v>153</v>
       </c>
-      <c r="K14" s="37" t="s">
+      <c r="K14" s="14" t="s">
         <v>154</v>
       </c>
-      <c r="L14" s="37" t="s">
+      <c r="L14" s="14" t="s">
         <v>155</v>
       </c>
-      <c r="M14" s="37" t="s">
+      <c r="M14" s="14" t="s">
         <v>156</v>
       </c>
-      <c r="N14" s="37" t="s">
+      <c r="N14" s="14" t="s">
         <v>157</v>
       </c>
-      <c r="O14" s="45" t="s">
+      <c r="O14" s="37" t="s">
         <v>158</v>
       </c>
-      <c r="P14" s="50" t="s">
+      <c r="P14" s="42" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="15" s="2" customFormat="1" ht="33" customHeight="1" spans="1:16">
-      <c r="A15" s="14"/>
-      <c r="B15" s="13" t="s">
+      <c r="A15" s="12"/>
+      <c r="B15" s="12" t="s">
         <v>160</v>
       </c>
-      <c r="C15" s="14"/>
-      <c r="D15" s="37" t="s">
+      <c r="C15" s="12"/>
+      <c r="D15" s="14" t="s">
         <v>161</v>
       </c>
-      <c r="E15" s="37" t="s">
+      <c r="E15" s="14" t="s">
         <v>162</v>
       </c>
-      <c r="F15" s="37" t="s">
+      <c r="F15" s="14" t="s">
         <v>163</v>
       </c>
-      <c r="G15" s="37" t="s">
+      <c r="G15" s="14" t="s">
         <v>164</v>
       </c>
-      <c r="H15" s="37" t="s">
+      <c r="H15" s="14" t="s">
         <v>165</v>
       </c>
-      <c r="I15" s="37" t="s">
+      <c r="I15" s="14" t="s">
         <v>166</v>
       </c>
-      <c r="J15" s="37" t="s">
+      <c r="J15" s="14" t="s">
         <v>167</v>
       </c>
-      <c r="K15" s="37" t="s">
+      <c r="K15" s="14" t="s">
         <v>168</v>
       </c>
-      <c r="L15" s="37" t="s">
+      <c r="L15" s="14" t="s">
         <v>169</v>
       </c>
-      <c r="M15" s="37" t="s">
+      <c r="M15" s="14" t="s">
         <v>170</v>
       </c>
-      <c r="N15" s="37" t="s">
+      <c r="N15" s="14" t="s">
         <v>171</v>
       </c>
-      <c r="O15" s="45" t="s">
+      <c r="O15" s="37" t="s">
         <v>172</v>
       </c>
-      <c r="P15" s="50" t="s">
+      <c r="P15" s="42" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="16" s="2" customFormat="1" ht="33" customHeight="1" spans="1:16">
-      <c r="A16" s="14"/>
-      <c r="B16" s="20" t="s">
+      <c r="A16" s="12"/>
+      <c r="B16" s="17" t="s">
         <v>174</v>
       </c>
-      <c r="C16" s="21"/>
-      <c r="D16" s="37" t="s">
+      <c r="C16" s="18"/>
+      <c r="D16" s="14" t="s">
         <v>175</v>
       </c>
-      <c r="E16" s="37" t="s">
+      <c r="E16" s="14" t="s">
         <v>176</v>
       </c>
-      <c r="F16" s="37" t="s">
+      <c r="F16" s="14" t="s">
         <v>177</v>
       </c>
-      <c r="G16" s="37" t="s">
+      <c r="G16" s="14" t="s">
         <v>178</v>
       </c>
-      <c r="H16" s="37" t="s">
+      <c r="H16" s="14" t="s">
         <v>179</v>
       </c>
-      <c r="I16" s="37" t="s">
+      <c r="I16" s="14" t="s">
         <v>180</v>
       </c>
-      <c r="J16" s="37" t="s">
+      <c r="J16" s="14" t="s">
         <v>181</v>
       </c>
-      <c r="K16" s="37" t="s">
+      <c r="K16" s="14" t="s">
         <v>182</v>
       </c>
-      <c r="L16" s="37" t="s">
+      <c r="L16" s="14" t="s">
         <v>183</v>
       </c>
-      <c r="M16" s="37" t="s">
+      <c r="M16" s="14" t="s">
         <v>184</v>
       </c>
-      <c r="N16" s="37" t="s">
+      <c r="N16" s="14" t="s">
         <v>185</v>
       </c>
-      <c r="O16" s="45" t="s">
+      <c r="O16" s="37" t="s">
         <v>186</v>
       </c>
-      <c r="P16" s="50" t="s">
+      <c r="P16" s="42" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="17" s="2" customFormat="1" ht="33" customHeight="1" spans="1:16">
-      <c r="A17" s="14"/>
-      <c r="B17" s="20" t="s">
+      <c r="A17" s="12"/>
+      <c r="B17" s="17" t="s">
         <v>188</v>
       </c>
-      <c r="C17" s="21"/>
-      <c r="D17" s="37" t="s">
+      <c r="C17" s="18"/>
+      <c r="D17" s="14" t="s">
         <v>189</v>
       </c>
-      <c r="E17" s="37" t="s">
+      <c r="E17" s="14" t="s">
         <v>190</v>
       </c>
-      <c r="F17" s="37" t="s">
+      <c r="F17" s="14" t="s">
         <v>191</v>
       </c>
-      <c r="G17" s="37" t="s">
+      <c r="G17" s="14" t="s">
         <v>192</v>
       </c>
-      <c r="H17" s="37" t="s">
+      <c r="H17" s="14" t="s">
         <v>193</v>
       </c>
-      <c r="I17" s="37" t="s">
+      <c r="I17" s="14" t="s">
         <v>194</v>
       </c>
-      <c r="J17" s="37" t="s">
+      <c r="J17" s="14" t="s">
         <v>195</v>
       </c>
-      <c r="K17" s="37" t="s">
+      <c r="K17" s="14" t="s">
         <v>196</v>
       </c>
-      <c r="L17" s="37" t="s">
+      <c r="L17" s="14" t="s">
         <v>197</v>
       </c>
-      <c r="M17" s="37" t="s">
+      <c r="M17" s="14" t="s">
         <v>198</v>
       </c>
-      <c r="N17" s="37" t="s">
+      <c r="N17" s="14" t="s">
         <v>199</v>
       </c>
-      <c r="O17" s="45" t="s">
+      <c r="O17" s="37" t="s">
         <v>200</v>
       </c>
-      <c r="P17" s="50" t="s">
+      <c r="P17" s="42" t="s">
         <v>201</v>
       </c>
     </row>
     <row r="18" s="3" customFormat="1" ht="33" customHeight="1" spans="1:16">
-      <c r="A18" s="23"/>
-      <c r="B18" s="24" t="s">
+      <c r="A18" s="15"/>
+      <c r="B18" s="20" t="s">
         <v>203</v>
       </c>
-      <c r="C18" s="25"/>
-      <c r="D18" s="38" t="s">
+      <c r="C18" s="21"/>
+      <c r="D18" s="30" t="s">
         <v>204</v>
       </c>
-      <c r="E18" s="38" t="s">
+      <c r="E18" s="30" t="s">
         <v>205</v>
       </c>
-      <c r="F18" s="38" t="s">
+      <c r="F18" s="30" t="s">
         <v>206</v>
       </c>
-      <c r="G18" s="38" t="s">
+      <c r="G18" s="30" t="s">
         <v>207</v>
       </c>
-      <c r="H18" s="38" t="s">
+      <c r="H18" s="30" t="s">
         <v>208</v>
       </c>
-      <c r="I18" s="38" t="s">
+      <c r="I18" s="30" t="s">
         <v>209</v>
       </c>
-      <c r="J18" s="38" t="s">
+      <c r="J18" s="30" t="s">
         <v>210</v>
       </c>
-      <c r="K18" s="38" t="s">
+      <c r="K18" s="30" t="s">
         <v>211</v>
       </c>
-      <c r="L18" s="38" t="s">
+      <c r="L18" s="30" t="s">
         <v>212</v>
       </c>
-      <c r="M18" s="38" t="s">
+      <c r="M18" s="30" t="s">
         <v>213</v>
       </c>
-      <c r="N18" s="38" t="s">
+      <c r="N18" s="30" t="s">
         <v>214</v>
       </c>
-      <c r="O18" s="38" t="s">
+      <c r="O18" s="30" t="s">
         <v>215</v>
       </c>
-      <c r="P18" s="54" t="s">
+      <c r="P18" s="46" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="19" s="3" customFormat="1" ht="42" customHeight="1" spans="1:16">
-      <c r="A19" s="27" t="s">
+      <c r="A19" s="23" t="s">
         <v>217</v>
       </c>
-      <c r="B19" s="28"/>
-      <c r="C19" s="28"/>
-      <c r="D19" s="39" t="s">
+      <c r="B19" s="23"/>
+      <c r="C19" s="23"/>
+      <c r="D19" s="31" t="s">
         <v>218</v>
       </c>
-      <c r="E19" s="39" t="s">
+      <c r="E19" s="31" t="s">
         <v>219</v>
       </c>
-      <c r="F19" s="39" t="s">
+      <c r="F19" s="31" t="s">
         <v>220</v>
       </c>
-      <c r="G19" s="39" t="s">
+      <c r="G19" s="31" t="s">
         <v>221</v>
       </c>
-      <c r="H19" s="39" t="s">
+      <c r="H19" s="31" t="s">
         <v>222</v>
       </c>
-      <c r="I19" s="39" t="s">
+      <c r="I19" s="31" t="s">
         <v>223</v>
       </c>
-      <c r="J19" s="39" t="s">
+      <c r="J19" s="31" t="s">
         <v>224</v>
       </c>
-      <c r="K19" s="39" t="s">
+      <c r="K19" s="31" t="s">
         <v>225</v>
       </c>
-      <c r="L19" s="39" t="s">
+      <c r="L19" s="31" t="s">
         <v>226</v>
       </c>
-      <c r="M19" s="39" t="s">
+      <c r="M19" s="31" t="s">
         <v>227</v>
       </c>
-      <c r="N19" s="39" t="s">
+      <c r="N19" s="31" t="s">
         <v>228</v>
       </c>
-      <c r="O19" s="39" t="s">
+      <c r="O19" s="31" t="s">
         <v>229</v>
       </c>
-      <c r="P19" s="54" t="s">
+      <c r="P19" s="46" t="s">
         <v>230</v>
       </c>
     </row>
@@ -5174,922 +5111,922 @@
   <dimension ref="A1:R21"/>
   <sheetFormatPr defaultColWidth="9.69230769230769" defaultRowHeight="17.6"/>
   <cols>
-    <col min="1" max="1" width="10.6346153846154" style="5" customWidth="1"/>
-    <col min="2" max="2" width="11.3076923076923" style="5" customWidth="1"/>
-    <col min="3" max="4" width="11.9807692307692" style="5" customWidth="1"/>
-    <col min="5" max="17" width="11.3076923076923" style="6" customWidth="1"/>
-    <col min="18" max="16384" width="9.69230769230769" style="5"/>
+    <col min="1" max="1" width="10.6346153846154" style="1" customWidth="1"/>
+    <col min="2" max="2" width="11.3076923076923" style="1" customWidth="1"/>
+    <col min="3" max="4" width="11.9807692307692" style="1" customWidth="1"/>
+    <col min="5" max="17" width="11.3076923076923" style="5" customWidth="1"/>
+    <col min="18" max="16384" width="9.69230769230769" style="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="42" customHeight="1" spans="1:17">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="6" t="s">
         <v>240</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
-      <c r="G1" s="32"/>
-      <c r="H1" s="32"/>
-      <c r="I1" s="32"/>
-      <c r="J1" s="32"/>
-      <c r="K1" s="32"/>
-      <c r="L1" s="32"/>
-      <c r="M1" s="32"/>
-      <c r="N1" s="32"/>
-      <c r="O1" s="32"/>
-      <c r="P1" s="32"/>
-      <c r="Q1" s="32"/>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
+      <c r="H1" s="26"/>
+      <c r="I1" s="26"/>
+      <c r="J1" s="26"/>
+      <c r="K1" s="26"/>
+      <c r="L1" s="26"/>
+      <c r="M1" s="26"/>
+      <c r="N1" s="26"/>
+      <c r="O1" s="26"/>
+      <c r="P1" s="26"/>
+      <c r="Q1" s="26"/>
     </row>
     <row r="2" s="1" customFormat="1" ht="20" customHeight="1" spans="1:17">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="8"/>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="33"/>
-      <c r="F2" s="33"/>
-      <c r="G2" s="33"/>
-      <c r="H2" s="33"/>
-      <c r="I2" s="33"/>
-      <c r="J2" s="33"/>
-      <c r="K2" s="33"/>
-      <c r="L2" s="33"/>
-      <c r="M2" s="33"/>
-      <c r="N2" s="33"/>
-      <c r="O2" s="33"/>
-      <c r="P2" s="33"/>
-      <c r="Q2" s="33"/>
+      <c r="B2" s="7"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="27"/>
+      <c r="F2" s="27"/>
+      <c r="G2" s="27"/>
+      <c r="H2" s="27"/>
+      <c r="I2" s="27"/>
+      <c r="J2" s="27"/>
+      <c r="K2" s="27"/>
+      <c r="L2" s="27"/>
+      <c r="M2" s="27"/>
+      <c r="N2" s="27"/>
+      <c r="O2" s="27"/>
+      <c r="P2" s="27"/>
+      <c r="Q2" s="27"/>
     </row>
     <row r="3" ht="26" customHeight="1" spans="1:18">
-      <c r="A3" s="9" t="s">
+      <c r="A3" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="9"/>
-      <c r="C3" s="9"/>
-      <c r="D3" s="10" t="s">
+      <c r="B3" s="8"/>
+      <c r="C3" s="8"/>
+      <c r="D3" s="9" t="s">
         <v>232</v>
       </c>
-      <c r="E3" s="34" t="s">
+      <c r="E3" s="28" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="35"/>
-      <c r="G3" s="35"/>
-      <c r="H3" s="35"/>
-      <c r="I3" s="35"/>
-      <c r="J3" s="35"/>
-      <c r="K3" s="35"/>
-      <c r="L3" s="35"/>
-      <c r="M3" s="35"/>
-      <c r="N3" s="35"/>
-      <c r="O3" s="35"/>
-      <c r="P3" s="43"/>
-      <c r="Q3" s="46" t="s">
+      <c r="F3" s="28"/>
+      <c r="G3" s="28"/>
+      <c r="H3" s="28"/>
+      <c r="I3" s="28"/>
+      <c r="J3" s="28"/>
+      <c r="K3" s="28"/>
+      <c r="L3" s="28"/>
+      <c r="M3" s="28"/>
+      <c r="N3" s="28"/>
+      <c r="O3" s="28"/>
+      <c r="P3" s="35"/>
+      <c r="Q3" s="38" t="s">
         <v>4</v>
       </c>
-      <c r="R3" s="47" t="s">
+      <c r="R3" s="39" t="s">
         <v>233</v>
       </c>
     </row>
     <row r="4" ht="26" customHeight="1" spans="1:18">
-      <c r="A4" s="11"/>
-      <c r="B4" s="11"/>
-      <c r="C4" s="11"/>
-      <c r="D4" s="12"/>
-      <c r="E4" s="36" t="s">
+      <c r="A4" s="10"/>
+      <c r="B4" s="10"/>
+      <c r="C4" s="10"/>
+      <c r="D4" s="11"/>
+      <c r="E4" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="F4" s="36" t="s">
+      <c r="F4" s="29" t="s">
         <v>6</v>
       </c>
-      <c r="G4" s="36" t="s">
+      <c r="G4" s="29" t="s">
         <v>7</v>
       </c>
-      <c r="H4" s="36" t="s">
+      <c r="H4" s="29" t="s">
         <v>8</v>
       </c>
-      <c r="I4" s="36" t="s">
+      <c r="I4" s="29" t="s">
         <v>9</v>
       </c>
-      <c r="J4" s="36" t="s">
+      <c r="J4" s="29" t="s">
         <v>10</v>
       </c>
-      <c r="K4" s="36" t="s">
+      <c r="K4" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="L4" s="36" t="s">
+      <c r="L4" s="29" t="s">
         <v>12</v>
       </c>
-      <c r="M4" s="36" t="s">
+      <c r="M4" s="29" t="s">
         <v>13</v>
       </c>
-      <c r="N4" s="36" t="s">
+      <c r="N4" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="O4" s="36" t="s">
+      <c r="O4" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="P4" s="44" t="s">
+      <c r="P4" s="36" t="s">
         <v>16</v>
       </c>
-      <c r="Q4" s="48"/>
-      <c r="R4" s="49"/>
+      <c r="Q4" s="40"/>
+      <c r="R4" s="41"/>
     </row>
     <row r="5" s="2" customFormat="1" ht="33" customHeight="1" spans="1:18">
-      <c r="A5" s="13" t="s">
+      <c r="A5" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="13" t="s">
+      <c r="B5" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="C5" s="14"/>
-      <c r="D5" s="15" t="s">
+      <c r="C5" s="12"/>
+      <c r="D5" s="13" t="s">
         <v>234</v>
       </c>
-      <c r="E5" s="37" t="s">
+      <c r="E5" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="F5" s="37" t="s">
+      <c r="F5" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="G5" s="37" t="s">
+      <c r="G5" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="H5" s="37" t="s">
+      <c r="H5" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="I5" s="37" t="s">
+      <c r="I5" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="J5" s="37" t="s">
+      <c r="J5" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="K5" s="37" t="s">
+      <c r="K5" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="L5" s="37" t="s">
+      <c r="L5" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="M5" s="37" t="s">
+      <c r="M5" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="N5" s="37" t="s">
+      <c r="N5" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="O5" s="37" t="s">
+      <c r="O5" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="P5" s="45" t="s">
+      <c r="P5" s="37" t="s">
         <v>30</v>
       </c>
-      <c r="Q5" s="50" t="s">
+      <c r="Q5" s="42" t="s">
         <v>31</v>
       </c>
-      <c r="R5" s="49"/>
+      <c r="R5" s="41"/>
     </row>
     <row r="6" s="2" customFormat="1" ht="33" customHeight="1" spans="1:18">
-      <c r="A6" s="13"/>
-      <c r="B6" s="13" t="s">
+      <c r="A6" s="12"/>
+      <c r="B6" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="C6" s="13"/>
-      <c r="D6" s="16" t="s">
+      <c r="C6" s="12"/>
+      <c r="D6" s="13" t="s">
         <v>234</v>
       </c>
-      <c r="E6" s="37" t="s">
+      <c r="E6" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="F6" s="37" t="s">
+      <c r="F6" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="G6" s="37" t="s">
+      <c r="G6" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="H6" s="37" t="s">
+      <c r="H6" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="I6" s="37" t="s">
+      <c r="I6" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="J6" s="37" t="s">
+      <c r="J6" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="K6" s="37" t="s">
+      <c r="K6" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="L6" s="37" t="s">
+      <c r="L6" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="M6" s="37" t="s">
+      <c r="M6" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="N6" s="37" t="s">
+      <c r="N6" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="O6" s="37" t="s">
+      <c r="O6" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="P6" s="45" t="s">
+      <c r="P6" s="37" t="s">
         <v>44</v>
       </c>
-      <c r="Q6" s="50" t="s">
+      <c r="Q6" s="42" t="s">
         <v>45</v>
       </c>
-      <c r="R6" s="51" t="s">
+      <c r="R6" s="43" t="s">
         <v>235</v>
       </c>
     </row>
     <row r="7" s="2" customFormat="1" ht="33" customHeight="1" spans="1:18">
-      <c r="A7" s="13"/>
-      <c r="B7" s="13" t="s">
+      <c r="A7" s="12"/>
+      <c r="B7" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="C7" s="13"/>
-      <c r="D7" s="16" t="s">
+      <c r="C7" s="12"/>
+      <c r="D7" s="13" t="s">
         <v>234</v>
       </c>
-      <c r="E7" s="37" t="s">
+      <c r="E7" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="F7" s="37" t="s">
+      <c r="F7" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="G7" s="37" t="s">
+      <c r="G7" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="H7" s="37" t="s">
+      <c r="H7" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="I7" s="37" t="s">
+      <c r="I7" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="J7" s="37" t="s">
+      <c r="J7" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="K7" s="37" t="s">
+      <c r="K7" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="L7" s="37" t="s">
+      <c r="L7" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="M7" s="37" t="s">
+      <c r="M7" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="N7" s="37" t="s">
+      <c r="N7" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="O7" s="37" t="s">
+      <c r="O7" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="P7" s="45" t="s">
+      <c r="P7" s="37" t="s">
         <v>58</v>
       </c>
-      <c r="Q7" s="50" t="s">
+      <c r="Q7" s="42" t="s">
         <v>59</v>
       </c>
-      <c r="R7" s="52"/>
+      <c r="R7" s="44"/>
     </row>
     <row r="8" s="2" customFormat="1" ht="33" customHeight="1" spans="1:18">
-      <c r="A8" s="13"/>
-      <c r="B8" s="13" t="s">
+      <c r="A8" s="12"/>
+      <c r="B8" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="C8" s="14"/>
-      <c r="D8" s="16" t="s">
+      <c r="C8" s="12"/>
+      <c r="D8" s="13" t="s">
         <v>234</v>
       </c>
-      <c r="E8" s="37" t="s">
+      <c r="E8" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="F8" s="37" t="s">
+      <c r="F8" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="G8" s="37" t="s">
+      <c r="G8" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="H8" s="37" t="s">
+      <c r="H8" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="I8" s="37" t="s">
+      <c r="I8" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="J8" s="37" t="s">
+      <c r="J8" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="K8" s="37" t="s">
+      <c r="K8" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="L8" s="37" t="s">
+      <c r="L8" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="M8" s="37" t="s">
+      <c r="M8" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="N8" s="37" t="s">
+      <c r="N8" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="O8" s="37" t="s">
+      <c r="O8" s="14" t="s">
         <v>71</v>
       </c>
-      <c r="P8" s="45" t="s">
+      <c r="P8" s="37" t="s">
         <v>72</v>
       </c>
-      <c r="Q8" s="50" t="s">
+      <c r="Q8" s="42" t="s">
         <v>73</v>
       </c>
-      <c r="R8" s="52"/>
+      <c r="R8" s="44"/>
     </row>
     <row r="9" s="2" customFormat="1" ht="33" customHeight="1" spans="1:18">
-      <c r="A9" s="13"/>
-      <c r="B9" s="13" t="s">
+      <c r="A9" s="12"/>
+      <c r="B9" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="C9" s="13"/>
-      <c r="D9" s="17">
+      <c r="C9" s="12"/>
+      <c r="D9" s="14">
         <f>970000</f>
         <v>970000</v>
       </c>
-      <c r="E9" s="37" t="s">
+      <c r="E9" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="F9" s="37" t="s">
+      <c r="F9" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="G9" s="37" t="s">
+      <c r="G9" s="14" t="s">
         <v>77</v>
       </c>
-      <c r="H9" s="37" t="s">
+      <c r="H9" s="14" t="s">
         <v>78</v>
       </c>
-      <c r="I9" s="37" t="s">
+      <c r="I9" s="14" t="s">
         <v>79</v>
       </c>
-      <c r="J9" s="37" t="s">
+      <c r="J9" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="K9" s="37" t="s">
+      <c r="K9" s="14" t="s">
         <v>81</v>
       </c>
-      <c r="L9" s="37" t="s">
+      <c r="L9" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="M9" s="37" t="s">
+      <c r="M9" s="14" t="s">
         <v>83</v>
       </c>
-      <c r="N9" s="37" t="s">
+      <c r="N9" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="O9" s="37" t="s">
+      <c r="O9" s="14" t="s">
         <v>85</v>
       </c>
-      <c r="P9" s="45" t="s">
+      <c r="P9" s="37" t="s">
         <v>86</v>
       </c>
-      <c r="Q9" s="50" t="s">
+      <c r="Q9" s="42" t="s">
         <v>87</v>
       </c>
-      <c r="R9" s="53"/>
+      <c r="R9" s="45"/>
     </row>
     <row r="10" s="2" customFormat="1" ht="33" customHeight="1" spans="1:17">
-      <c r="A10" s="13"/>
-      <c r="B10" s="13" t="s">
+      <c r="A10" s="12"/>
+      <c r="B10" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="C10" s="14"/>
-      <c r="D10" s="15" t="s">
+      <c r="C10" s="12"/>
+      <c r="D10" s="13" t="s">
         <v>234</v>
       </c>
-      <c r="E10" s="37" t="s">
+      <c r="E10" s="14" t="s">
         <v>89</v>
       </c>
-      <c r="F10" s="37" t="s">
+      <c r="F10" s="14" t="s">
         <v>90</v>
       </c>
-      <c r="G10" s="37" t="s">
+      <c r="G10" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="H10" s="37" t="s">
+      <c r="H10" s="14" t="s">
         <v>92</v>
       </c>
-      <c r="I10" s="37" t="s">
+      <c r="I10" s="14" t="s">
         <v>93</v>
       </c>
-      <c r="J10" s="37" t="s">
+      <c r="J10" s="14" t="s">
         <v>94</v>
       </c>
-      <c r="K10" s="37" t="s">
+      <c r="K10" s="14" t="s">
         <v>95</v>
       </c>
-      <c r="L10" s="37" t="s">
+      <c r="L10" s="14" t="s">
         <v>96</v>
       </c>
-      <c r="M10" s="37" t="s">
+      <c r="M10" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="N10" s="37" t="s">
+      <c r="N10" s="14" t="s">
         <v>98</v>
       </c>
-      <c r="O10" s="37" t="s">
+      <c r="O10" s="14" t="s">
         <v>99</v>
       </c>
-      <c r="P10" s="37" t="s">
+      <c r="P10" s="14" t="s">
         <v>100</v>
       </c>
-      <c r="Q10" s="50" t="s">
+      <c r="Q10" s="42" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="11" s="2" customFormat="1" ht="33" customHeight="1" spans="1:17">
-      <c r="A11" s="13"/>
-      <c r="B11" s="13" t="s">
+      <c r="A11" s="12"/>
+      <c r="B11" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="C11" s="13"/>
-      <c r="D11" s="15" t="s">
+      <c r="C11" s="12"/>
+      <c r="D11" s="13" t="s">
         <v>234</v>
       </c>
-      <c r="E11" s="37" t="s">
+      <c r="E11" s="14" t="s">
         <v>103</v>
       </c>
-      <c r="F11" s="37" t="s">
+      <c r="F11" s="14" t="s">
         <v>104</v>
       </c>
-      <c r="G11" s="37" t="s">
+      <c r="G11" s="14" t="s">
         <v>105</v>
       </c>
-      <c r="H11" s="37" t="s">
+      <c r="H11" s="14" t="s">
         <v>106</v>
       </c>
-      <c r="I11" s="37" t="s">
+      <c r="I11" s="14" t="s">
         <v>107</v>
       </c>
-      <c r="J11" s="37" t="s">
+      <c r="J11" s="14" t="s">
         <v>108</v>
       </c>
-      <c r="K11" s="37" t="s">
+      <c r="K11" s="14" t="s">
         <v>109</v>
       </c>
-      <c r="L11" s="37" t="s">
+      <c r="L11" s="14" t="s">
         <v>110</v>
       </c>
-      <c r="M11" s="37" t="s">
+      <c r="M11" s="14" t="s">
         <v>111</v>
       </c>
-      <c r="N11" s="37" t="s">
+      <c r="N11" s="14" t="s">
         <v>112</v>
       </c>
-      <c r="O11" s="37" t="s">
+      <c r="O11" s="14" t="s">
         <v>113</v>
       </c>
-      <c r="P11" s="45" t="s">
+      <c r="P11" s="37" t="s">
         <v>114</v>
       </c>
-      <c r="Q11" s="50" t="s">
+      <c r="Q11" s="42" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="12" s="3" customFormat="1" ht="33" customHeight="1" spans="1:17">
-      <c r="A12" s="18"/>
-      <c r="B12" s="18" t="s">
+      <c r="A12" s="15"/>
+      <c r="B12" s="15" t="s">
         <v>116</v>
       </c>
-      <c r="C12" s="18"/>
-      <c r="D12" s="19" t="s">
+      <c r="C12" s="15"/>
+      <c r="D12" s="16" t="s">
         <v>234</v>
       </c>
-      <c r="E12" s="38" t="s">
+      <c r="E12" s="30" t="s">
         <v>117</v>
       </c>
-      <c r="F12" s="38" t="s">
+      <c r="F12" s="30" t="s">
         <v>118</v>
       </c>
-      <c r="G12" s="38" t="s">
+      <c r="G12" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="H12" s="38" t="s">
+      <c r="H12" s="30" t="s">
         <v>120</v>
       </c>
-      <c r="I12" s="38" t="s">
+      <c r="I12" s="30" t="s">
         <v>121</v>
       </c>
-      <c r="J12" s="38" t="s">
+      <c r="J12" s="30" t="s">
         <v>122</v>
       </c>
-      <c r="K12" s="38" t="s">
+      <c r="K12" s="30" t="s">
         <v>123</v>
       </c>
-      <c r="L12" s="38" t="s">
+      <c r="L12" s="30" t="s">
         <v>124</v>
       </c>
-      <c r="M12" s="38" t="s">
+      <c r="M12" s="30" t="s">
         <v>125</v>
       </c>
-      <c r="N12" s="38" t="s">
+      <c r="N12" s="30" t="s">
         <v>126</v>
       </c>
-      <c r="O12" s="38" t="s">
+      <c r="O12" s="30" t="s">
         <v>127</v>
       </c>
-      <c r="P12" s="38" t="s">
+      <c r="P12" s="30" t="s">
         <v>128</v>
       </c>
-      <c r="Q12" s="54" t="s">
+      <c r="Q12" s="46" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="13" s="2" customFormat="1" ht="57" customHeight="1" spans="1:17">
-      <c r="A13" s="13" t="s">
+      <c r="A13" s="12" t="s">
         <v>130</v>
       </c>
-      <c r="B13" s="13" t="s">
+      <c r="B13" s="12" t="s">
         <v>131</v>
       </c>
-      <c r="C13" s="13" t="s">
+      <c r="C13" s="12" t="s">
         <v>132</v>
       </c>
-      <c r="D13" s="15" t="s">
+      <c r="D13" s="13" t="s">
         <v>234</v>
       </c>
-      <c r="E13" s="37" t="s">
+      <c r="E13" s="14" t="s">
         <v>133</v>
       </c>
-      <c r="F13" s="37" t="s">
+      <c r="F13" s="14" t="s">
         <v>134</v>
       </c>
-      <c r="G13" s="37" t="s">
+      <c r="G13" s="14" t="s">
         <v>135</v>
       </c>
-      <c r="H13" s="37" t="s">
+      <c r="H13" s="14" t="s">
         <v>136</v>
       </c>
-      <c r="I13" s="37" t="s">
+      <c r="I13" s="14" t="s">
         <v>137</v>
       </c>
-      <c r="J13" s="37" t="s">
+      <c r="J13" s="14" t="s">
         <v>138</v>
       </c>
-      <c r="K13" s="37" t="s">
+      <c r="K13" s="14" t="s">
         <v>139</v>
       </c>
-      <c r="L13" s="37" t="s">
+      <c r="L13" s="14" t="s">
         <v>140</v>
       </c>
-      <c r="M13" s="37" t="s">
+      <c r="M13" s="14" t="s">
         <v>141</v>
       </c>
-      <c r="N13" s="37" t="s">
+      <c r="N13" s="14" t="s">
         <v>142</v>
       </c>
-      <c r="O13" s="37" t="s">
+      <c r="O13" s="14" t="s">
         <v>143</v>
       </c>
-      <c r="P13" s="45" t="s">
+      <c r="P13" s="37" t="s">
         <v>144</v>
       </c>
-      <c r="Q13" s="50" t="s">
+      <c r="Q13" s="42" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="14" s="2" customFormat="1" ht="63" customHeight="1" spans="1:17">
-      <c r="A14" s="14"/>
-      <c r="B14" s="14"/>
-      <c r="C14" s="13" t="s">
+      <c r="A14" s="12"/>
+      <c r="B14" s="12"/>
+      <c r="C14" s="12" t="s">
         <v>146</v>
       </c>
-      <c r="D14" s="15" t="s">
+      <c r="D14" s="13" t="s">
         <v>234</v>
       </c>
-      <c r="E14" s="37" t="s">
+      <c r="E14" s="14" t="s">
         <v>147</v>
       </c>
-      <c r="F14" s="37" t="s">
+      <c r="F14" s="14" t="s">
         <v>148</v>
       </c>
-      <c r="G14" s="37" t="s">
+      <c r="G14" s="14" t="s">
         <v>149</v>
       </c>
-      <c r="H14" s="37" t="s">
+      <c r="H14" s="14" t="s">
         <v>150</v>
       </c>
-      <c r="I14" s="37" t="s">
+      <c r="I14" s="14" t="s">
         <v>151</v>
       </c>
-      <c r="J14" s="37" t="s">
+      <c r="J14" s="14" t="s">
         <v>152</v>
       </c>
-      <c r="K14" s="37" t="s">
+      <c r="K14" s="14" t="s">
         <v>153</v>
       </c>
-      <c r="L14" s="37" t="s">
+      <c r="L14" s="14" t="s">
         <v>154</v>
       </c>
-      <c r="M14" s="37" t="s">
+      <c r="M14" s="14" t="s">
         <v>155</v>
       </c>
-      <c r="N14" s="37" t="s">
+      <c r="N14" s="14" t="s">
         <v>156</v>
       </c>
-      <c r="O14" s="37" t="s">
+      <c r="O14" s="14" t="s">
         <v>157</v>
       </c>
-      <c r="P14" s="45" t="s">
+      <c r="P14" s="37" t="s">
         <v>158</v>
       </c>
-      <c r="Q14" s="50" t="s">
+      <c r="Q14" s="42" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="15" s="2" customFormat="1" ht="33" customHeight="1" spans="1:17">
-      <c r="A15" s="14"/>
-      <c r="B15" s="13" t="s">
+      <c r="A15" s="12"/>
+      <c r="B15" s="12" t="s">
         <v>160</v>
       </c>
-      <c r="C15" s="14"/>
-      <c r="D15" s="15" t="s">
+      <c r="C15" s="12"/>
+      <c r="D15" s="13" t="s">
         <v>234</v>
       </c>
-      <c r="E15" s="37" t="s">
+      <c r="E15" s="14" t="s">
         <v>161</v>
       </c>
-      <c r="F15" s="37" t="s">
+      <c r="F15" s="14" t="s">
         <v>162</v>
       </c>
-      <c r="G15" s="37" t="s">
+      <c r="G15" s="14" t="s">
         <v>163</v>
       </c>
-      <c r="H15" s="37" t="s">
+      <c r="H15" s="14" t="s">
         <v>164</v>
       </c>
-      <c r="I15" s="37" t="s">
+      <c r="I15" s="14" t="s">
         <v>165</v>
       </c>
-      <c r="J15" s="37" t="s">
+      <c r="J15" s="14" t="s">
         <v>166</v>
       </c>
-      <c r="K15" s="37" t="s">
+      <c r="K15" s="14" t="s">
         <v>167</v>
       </c>
-      <c r="L15" s="37" t="s">
+      <c r="L15" s="14" t="s">
         <v>168</v>
       </c>
-      <c r="M15" s="37" t="s">
+      <c r="M15" s="14" t="s">
         <v>169</v>
       </c>
-      <c r="N15" s="37" t="s">
+      <c r="N15" s="14" t="s">
         <v>170</v>
       </c>
-      <c r="O15" s="37" t="s">
+      <c r="O15" s="14" t="s">
         <v>171</v>
       </c>
-      <c r="P15" s="45" t="s">
+      <c r="P15" s="37" t="s">
         <v>172</v>
       </c>
-      <c r="Q15" s="50" t="s">
+      <c r="Q15" s="42" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="16" s="2" customFormat="1" ht="33" customHeight="1" spans="1:17">
-      <c r="A16" s="14"/>
-      <c r="B16" s="20" t="s">
+      <c r="A16" s="12"/>
+      <c r="B16" s="17" t="s">
         <v>174</v>
       </c>
-      <c r="C16" s="21"/>
-      <c r="D16" s="22" t="s">
+      <c r="C16" s="18"/>
+      <c r="D16" s="19" t="s">
         <v>234</v>
       </c>
-      <c r="E16" s="37" t="s">
+      <c r="E16" s="14" t="s">
         <v>175</v>
       </c>
-      <c r="F16" s="37" t="s">
+      <c r="F16" s="14" t="s">
         <v>176</v>
       </c>
-      <c r="G16" s="37" t="s">
+      <c r="G16" s="14" t="s">
         <v>177</v>
       </c>
-      <c r="H16" s="37" t="s">
+      <c r="H16" s="14" t="s">
         <v>178</v>
       </c>
-      <c r="I16" s="37" t="s">
+      <c r="I16" s="14" t="s">
         <v>179</v>
       </c>
-      <c r="J16" s="37" t="s">
+      <c r="J16" s="14" t="s">
         <v>180</v>
       </c>
-      <c r="K16" s="37" t="s">
+      <c r="K16" s="14" t="s">
         <v>181</v>
       </c>
-      <c r="L16" s="37" t="s">
+      <c r="L16" s="14" t="s">
         <v>182</v>
       </c>
-      <c r="M16" s="37" t="s">
+      <c r="M16" s="14" t="s">
         <v>183</v>
       </c>
-      <c r="N16" s="37" t="s">
+      <c r="N16" s="14" t="s">
         <v>184</v>
       </c>
-      <c r="O16" s="37" t="s">
+      <c r="O16" s="14" t="s">
         <v>185</v>
       </c>
-      <c r="P16" s="45" t="s">
+      <c r="P16" s="37" t="s">
         <v>186</v>
       </c>
-      <c r="Q16" s="50" t="s">
+      <c r="Q16" s="42" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="17" s="2" customFormat="1" ht="33" customHeight="1" spans="1:17">
-      <c r="A17" s="14"/>
-      <c r="B17" s="20" t="s">
+      <c r="A17" s="12"/>
+      <c r="B17" s="17" t="s">
         <v>188</v>
       </c>
-      <c r="C17" s="21"/>
-      <c r="D17" s="22" t="s">
+      <c r="C17" s="18"/>
+      <c r="D17" s="19" t="s">
         <v>234</v>
       </c>
-      <c r="E17" s="37" t="s">
+      <c r="E17" s="14" t="s">
         <v>189</v>
       </c>
-      <c r="F17" s="37" t="s">
+      <c r="F17" s="14" t="s">
         <v>190</v>
       </c>
-      <c r="G17" s="37" t="s">
+      <c r="G17" s="14" t="s">
         <v>191</v>
       </c>
-      <c r="H17" s="37" t="s">
+      <c r="H17" s="14" t="s">
         <v>192</v>
       </c>
-      <c r="I17" s="37" t="s">
+      <c r="I17" s="14" t="s">
         <v>193</v>
       </c>
-      <c r="J17" s="37" t="s">
+      <c r="J17" s="14" t="s">
         <v>194</v>
       </c>
-      <c r="K17" s="37" t="s">
+      <c r="K17" s="14" t="s">
         <v>195</v>
       </c>
-      <c r="L17" s="37" t="s">
+      <c r="L17" s="14" t="s">
         <v>196</v>
       </c>
-      <c r="M17" s="37" t="s">
+      <c r="M17" s="14" t="s">
         <v>197</v>
       </c>
-      <c r="N17" s="37" t="s">
+      <c r="N17" s="14" t="s">
         <v>198</v>
       </c>
-      <c r="O17" s="37" t="s">
+      <c r="O17" s="14" t="s">
         <v>199</v>
       </c>
-      <c r="P17" s="45" t="s">
+      <c r="P17" s="37" t="s">
         <v>200</v>
       </c>
-      <c r="Q17" s="50" t="s">
+      <c r="Q17" s="42" t="s">
         <v>201</v>
       </c>
     </row>
     <row r="18" s="3" customFormat="1" ht="33" customHeight="1" spans="1:17">
-      <c r="A18" s="23"/>
-      <c r="B18" s="24" t="s">
+      <c r="A18" s="15"/>
+      <c r="B18" s="20" t="s">
         <v>203</v>
       </c>
-      <c r="C18" s="25"/>
-      <c r="D18" s="26" t="s">
+      <c r="C18" s="21"/>
+      <c r="D18" s="22" t="s">
         <v>234</v>
       </c>
-      <c r="E18" s="38" t="s">
+      <c r="E18" s="30" t="s">
         <v>204</v>
       </c>
-      <c r="F18" s="38" t="s">
+      <c r="F18" s="30" t="s">
         <v>205</v>
       </c>
-      <c r="G18" s="38" t="s">
+      <c r="G18" s="30" t="s">
         <v>206</v>
       </c>
-      <c r="H18" s="38" t="s">
+      <c r="H18" s="30" t="s">
         <v>207</v>
       </c>
-      <c r="I18" s="38" t="s">
+      <c r="I18" s="30" t="s">
         <v>208</v>
       </c>
-      <c r="J18" s="38" t="s">
+      <c r="J18" s="30" t="s">
         <v>209</v>
       </c>
-      <c r="K18" s="38" t="s">
+      <c r="K18" s="30" t="s">
         <v>210</v>
       </c>
-      <c r="L18" s="38" t="s">
+      <c r="L18" s="30" t="s">
         <v>211</v>
       </c>
-      <c r="M18" s="38" t="s">
+      <c r="M18" s="30" t="s">
         <v>212</v>
       </c>
-      <c r="N18" s="38" t="s">
+      <c r="N18" s="30" t="s">
         <v>213</v>
       </c>
-      <c r="O18" s="38" t="s">
+      <c r="O18" s="30" t="s">
         <v>214</v>
       </c>
-      <c r="P18" s="38" t="s">
+      <c r="P18" s="30" t="s">
         <v>215</v>
       </c>
-      <c r="Q18" s="54" t="s">
+      <c r="Q18" s="46" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="19" s="3" customFormat="1" ht="42" customHeight="1" spans="1:17">
-      <c r="A19" s="27" t="s">
+      <c r="A19" s="23" t="s">
         <v>217</v>
       </c>
-      <c r="B19" s="28"/>
-      <c r="C19" s="28"/>
-      <c r="D19" s="29" t="s">
+      <c r="B19" s="23"/>
+      <c r="C19" s="23"/>
+      <c r="D19" s="24" t="s">
         <v>234</v>
       </c>
-      <c r="E19" s="39" t="s">
+      <c r="E19" s="31" t="s">
         <v>218</v>
       </c>
-      <c r="F19" s="39" t="s">
+      <c r="F19" s="31" t="s">
         <v>219</v>
       </c>
-      <c r="G19" s="39" t="s">
+      <c r="G19" s="31" t="s">
         <v>220</v>
       </c>
-      <c r="H19" s="39" t="s">
+      <c r="H19" s="31" t="s">
         <v>221</v>
       </c>
-      <c r="I19" s="39" t="s">
+      <c r="I19" s="31" t="s">
         <v>222</v>
       </c>
-      <c r="J19" s="39" t="s">
+      <c r="J19" s="31" t="s">
         <v>223</v>
       </c>
-      <c r="K19" s="39" t="s">
+      <c r="K19" s="31" t="s">
         <v>224</v>
       </c>
-      <c r="L19" s="39" t="s">
+      <c r="L19" s="31" t="s">
         <v>225</v>
       </c>
-      <c r="M19" s="39" t="s">
+      <c r="M19" s="31" t="s">
         <v>226</v>
       </c>
-      <c r="N19" s="39" t="s">
+      <c r="N19" s="31" t="s">
         <v>227</v>
       </c>
-      <c r="O19" s="39" t="s">
+      <c r="O19" s="31" t="s">
         <v>228</v>
       </c>
-      <c r="P19" s="39" t="s">
+      <c r="P19" s="31" t="s">
         <v>229</v>
       </c>
-      <c r="Q19" s="54" t="s">
+      <c r="Q19" s="46" t="s">
         <v>230</v>
       </c>
     </row>
     <row r="20" ht="38" customHeight="1" spans="1:17">
-      <c r="A20" s="30" t="s">
+      <c r="A20" s="25" t="s">
         <v>241</v>
       </c>
-      <c r="B20" s="31"/>
-      <c r="C20" s="31"/>
-      <c r="D20" s="31"/>
-      <c r="E20" s="40" t="s">
+      <c r="B20" s="25"/>
+      <c r="C20" s="25"/>
+      <c r="D20" s="25"/>
+      <c r="E20" s="32" t="s">
         <v>242</v>
       </c>
-      <c r="F20" s="40" t="s">
+      <c r="F20" s="32" t="s">
         <v>243</v>
       </c>
-      <c r="G20" s="40" t="s">
+      <c r="G20" s="32" t="s">
         <v>244</v>
       </c>
-      <c r="H20" s="40" t="s">
+      <c r="H20" s="32" t="s">
         <v>245</v>
       </c>
-      <c r="I20" s="40" t="s">
+      <c r="I20" s="32" t="s">
         <v>246</v>
       </c>
-      <c r="J20" s="40" t="s">
+      <c r="J20" s="32" t="s">
         <v>247</v>
       </c>
-      <c r="K20" s="40" t="s">
+      <c r="K20" s="32" t="s">
         <v>248</v>
       </c>
-      <c r="L20" s="40" t="s">
+      <c r="L20" s="32" t="s">
         <v>249</v>
       </c>
-      <c r="M20" s="40" t="s">
+      <c r="M20" s="32" t="s">
         <v>250</v>
       </c>
-      <c r="N20" s="40" t="s">
+      <c r="N20" s="32" t="s">
         <v>251</v>
       </c>
-      <c r="O20" s="40" t="s">
+      <c r="O20" s="32" t="s">
         <v>252</v>
       </c>
-      <c r="P20" s="40" t="s">
+      <c r="P20" s="32" t="s">
         <v>253</v>
       </c>
-      <c r="Q20" s="40" t="s">
+      <c r="Q20" s="32" t="s">
         <v>254</v>
       </c>
     </row>
@@ -6100,25 +6037,25 @@
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
       <c r="D21" s="2"/>
-      <c r="E21" s="41" t="s">
+      <c r="E21" s="33" t="s">
         <v>255</v>
       </c>
-      <c r="F21" s="41" t="s">
+      <c r="F21" s="33" t="s">
         <v>256</v>
       </c>
-      <c r="G21" s="41" t="s">
+      <c r="G21" s="33" t="s">
         <v>257</v>
       </c>
-      <c r="H21" s="42"/>
-      <c r="I21" s="42"/>
-      <c r="J21" s="42"/>
-      <c r="K21" s="42"/>
-      <c r="L21" s="42"/>
-      <c r="M21" s="42"/>
-      <c r="N21" s="42"/>
-      <c r="O21" s="42"/>
-      <c r="P21" s="42"/>
-      <c r="Q21" s="42"/>
+      <c r="H21" s="34"/>
+      <c r="I21" s="34"/>
+      <c r="J21" s="34"/>
+      <c r="K21" s="34"/>
+      <c r="L21" s="34"/>
+      <c r="M21" s="34"/>
+      <c r="N21" s="34"/>
+      <c r="O21" s="34"/>
+      <c r="P21" s="34"/>
+      <c r="Q21" s="34"/>
     </row>
   </sheetData>
   <mergeCells count="26">

--- a/kcylog/kcylog-ui/public/sbcz.xlsx
+++ b/kcylog/kcylog-ui/public/sbcz.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27660" windowHeight="11640" activeTab="1"/>
+    <workbookView windowWidth="27660" windowHeight="11620"/>
   </bookViews>
   <sheets>
     <sheet name="工程测绘部" sheetId="2" r:id="rId1"/>
@@ -14,9 +14,9 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">工程测绘部!$A$1:$P$19</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">管线工程部!$A$1:$Q$19</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">管线工程部!$A$1:$P$19</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">不动产测绘部!$A$1:$P$19</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">地理信息部!$A$1:$Q$19</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">地理信息部!$A$1:$P$19</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,16 +36,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="973" uniqueCount="258">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="941" uniqueCount="251">
   <si>
     <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>2025年度福清分公司</t>
+      <t>2026年度福清分公司</t>
     </r>
     <r>
       <rPr>
@@ -759,13 +753,7 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>2025年度福清分公司</t>
+      <t>2026年度福清分公司</t>
     </r>
     <r>
       <rPr>
@@ -788,35 +776,17 @@
     </r>
   </si>
   <si>
-    <t>上一年度结余</t>
-  </si>
-  <si>
     <t>结余</t>
   </si>
   <si>
-    <t>/</t>
-  </si>
-  <si>
     <t>{jy}</t>
   </si>
   <si>
     <t>备注说明：</t>
   </si>
   <si>
-    <t>2024年11月预结17个乡镇29.79万元</t>
-  </si>
-  <si>
-    <t>1月生产经营收入减11月预结17个乡镇29.79万元，预留30万元</t>
-  </si>
-  <si>
     <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>2025年度福清分公司</t>
+      <t>2026年度福清分公司</t>
     </r>
     <r>
       <rPr>
@@ -840,13 +810,7 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>2025年度福清分公司</t>
+      <t>2026年度福清分公司</t>
     </r>
     <r>
       <rPr>
@@ -909,15 +873,6 @@
   </si>
   <si>
     <t>{yfhj}</t>
-  </si>
-  <si>
-    <t>预结2024航0187部分</t>
-  </si>
-  <si>
-    <t>2024航0187进度结算</t>
-  </si>
-  <si>
-    <t>扣2024航0187历史预结570000，2024航0185历史已结970000</t>
   </si>
 </sst>
 </file>
@@ -968,14 +923,14 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
-      <sz val="12"/>
-      <color rgb="FFFF0000"/>
+      <sz val="11"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -1337,7 +1292,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="24">
+  <borders count="22">
     <border>
       <left/>
       <right/>
@@ -1357,88 +1312,6 @@
       </top>
       <bottom style="thin">
         <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color indexed="8"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="8"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1479,6 +1352,34 @@
       </right>
       <top style="thin">
         <color indexed="8"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
       </top>
       <bottom style="thin">
         <color auto="1"/>
@@ -1549,6 +1450,34 @@
       <top/>
       <bottom style="thin">
         <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="8"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1676,7 +1605,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1688,34 +1617,34 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="19" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="19" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="19" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="22" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="23" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="21" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1800,7 +1729,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1822,143 +1751,122 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="6" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="6" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="6" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="6" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="6" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="6" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="6" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="6" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -2518,787 +2426,787 @@
       <c r="P1" s="6"/>
     </row>
     <row r="2" s="1" customFormat="1" ht="20" customHeight="1" spans="1:16">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
-      <c r="M2" s="7"/>
-      <c r="N2" s="7"/>
-      <c r="O2" s="7"/>
-      <c r="P2" s="7"/>
+      <c r="B2" s="8"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="8"/>
+      <c r="F2" s="8"/>
+      <c r="G2" s="8"/>
+      <c r="H2" s="8"/>
+      <c r="I2" s="8"/>
+      <c r="J2" s="8"/>
+      <c r="K2" s="8"/>
+      <c r="L2" s="8"/>
+      <c r="M2" s="8"/>
+      <c r="N2" s="8"/>
+      <c r="O2" s="8"/>
+      <c r="P2" s="8"/>
     </row>
     <row r="3" ht="26" customHeight="1" spans="1:16">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="8"/>
-      <c r="C3" s="8"/>
-      <c r="D3" s="8" t="s">
+      <c r="B3" s="10"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="8"/>
-      <c r="F3" s="8"/>
-      <c r="G3" s="8"/>
-      <c r="H3" s="8"/>
-      <c r="I3" s="8"/>
-      <c r="J3" s="8"/>
-      <c r="K3" s="8"/>
-      <c r="L3" s="8"/>
-      <c r="M3" s="8"/>
-      <c r="N3" s="8"/>
-      <c r="O3" s="48"/>
-      <c r="P3" s="50" t="s">
+      <c r="E3" s="10"/>
+      <c r="F3" s="10"/>
+      <c r="G3" s="10"/>
+      <c r="H3" s="10"/>
+      <c r="I3" s="10"/>
+      <c r="J3" s="10"/>
+      <c r="K3" s="10"/>
+      <c r="L3" s="10"/>
+      <c r="M3" s="10"/>
+      <c r="N3" s="10"/>
+      <c r="O3" s="40"/>
+      <c r="P3" s="41" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="4" ht="26" customHeight="1" spans="1:16">
-      <c r="A4" s="10"/>
-      <c r="B4" s="10"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10" t="s">
+      <c r="A4" s="15"/>
+      <c r="B4" s="15"/>
+      <c r="C4" s="15"/>
+      <c r="D4" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="10" t="s">
+      <c r="E4" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="F4" s="10" t="s">
+      <c r="F4" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="10" t="s">
+      <c r="G4" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="H4" s="10" t="s">
+      <c r="H4" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="I4" s="10" t="s">
+      <c r="I4" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="J4" s="10" t="s">
+      <c r="J4" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="K4" s="10" t="s">
+      <c r="K4" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="L4" s="10" t="s">
+      <c r="L4" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="M4" s="10" t="s">
+      <c r="M4" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="N4" s="10" t="s">
+      <c r="N4" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="O4" s="49" t="s">
+      <c r="O4" s="42" t="s">
         <v>16</v>
       </c>
-      <c r="P4" s="51"/>
+      <c r="P4" s="43"/>
     </row>
     <row r="5" s="2" customFormat="1" ht="33" customHeight="1" spans="1:16">
-      <c r="A5" s="12" t="s">
+      <c r="A5" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="12" t="s">
+      <c r="B5" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="C5" s="12"/>
-      <c r="D5" s="14" t="s">
+      <c r="C5" s="20"/>
+      <c r="D5" s="21" t="s">
         <v>19</v>
       </c>
-      <c r="E5" s="14" t="s">
+      <c r="E5" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="F5" s="14" t="s">
+      <c r="F5" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="G5" s="14" t="s">
+      <c r="G5" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="H5" s="14" t="s">
+      <c r="H5" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="I5" s="14" t="s">
+      <c r="I5" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="J5" s="14" t="s">
+      <c r="J5" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="K5" s="14" t="s">
+      <c r="K5" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="L5" s="14" t="s">
+      <c r="L5" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="M5" s="14" t="s">
+      <c r="M5" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="N5" s="14" t="s">
+      <c r="N5" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="O5" s="37" t="s">
+      <c r="O5" s="22" t="s">
         <v>30</v>
       </c>
-      <c r="P5" s="42" t="s">
+      <c r="P5" s="23" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="6" s="2" customFormat="1" ht="33" customHeight="1" spans="1:16">
-      <c r="A6" s="12"/>
-      <c r="B6" s="12" t="s">
+      <c r="A6" s="20"/>
+      <c r="B6" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="C6" s="12"/>
-      <c r="D6" s="14" t="s">
+      <c r="C6" s="20"/>
+      <c r="D6" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="E6" s="14" t="s">
+      <c r="E6" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="F6" s="14" t="s">
+      <c r="F6" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="G6" s="14" t="s">
+      <c r="G6" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="H6" s="14" t="s">
+      <c r="H6" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="I6" s="14" t="s">
+      <c r="I6" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="J6" s="14" t="s">
+      <c r="J6" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="K6" s="14" t="s">
+      <c r="K6" s="21" t="s">
         <v>40</v>
       </c>
-      <c r="L6" s="14" t="s">
+      <c r="L6" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="M6" s="14" t="s">
+      <c r="M6" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="N6" s="14" t="s">
+      <c r="N6" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="O6" s="37" t="s">
+      <c r="O6" s="22" t="s">
         <v>44</v>
       </c>
-      <c r="P6" s="42" t="s">
+      <c r="P6" s="23" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="7" s="2" customFormat="1" ht="33" customHeight="1" spans="1:16">
-      <c r="A7" s="12"/>
-      <c r="B7" s="12" t="s">
+      <c r="A7" s="20"/>
+      <c r="B7" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="C7" s="12"/>
-      <c r="D7" s="14" t="s">
+      <c r="C7" s="20"/>
+      <c r="D7" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="E7" s="14" t="s">
+      <c r="E7" s="21" t="s">
         <v>48</v>
       </c>
-      <c r="F7" s="14" t="s">
+      <c r="F7" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="G7" s="14" t="s">
+      <c r="G7" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="H7" s="14" t="s">
+      <c r="H7" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="I7" s="14" t="s">
+      <c r="I7" s="21" t="s">
         <v>52</v>
       </c>
-      <c r="J7" s="14" t="s">
+      <c r="J7" s="21" t="s">
         <v>53</v>
       </c>
-      <c r="K7" s="14" t="s">
+      <c r="K7" s="21" t="s">
         <v>54</v>
       </c>
-      <c r="L7" s="14" t="s">
+      <c r="L7" s="21" t="s">
         <v>55</v>
       </c>
-      <c r="M7" s="14" t="s">
+      <c r="M7" s="21" t="s">
         <v>56</v>
       </c>
-      <c r="N7" s="14" t="s">
+      <c r="N7" s="21" t="s">
         <v>57</v>
       </c>
-      <c r="O7" s="37" t="s">
+      <c r="O7" s="22" t="s">
         <v>58</v>
       </c>
-      <c r="P7" s="42" t="s">
+      <c r="P7" s="23" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="8" s="2" customFormat="1" ht="33" customHeight="1" spans="1:16">
-      <c r="A8" s="12"/>
-      <c r="B8" s="12" t="s">
+      <c r="A8" s="20"/>
+      <c r="B8" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="C8" s="12"/>
-      <c r="D8" s="14" t="s">
+      <c r="C8" s="20"/>
+      <c r="D8" s="21" t="s">
         <v>61</v>
       </c>
-      <c r="E8" s="14" t="s">
+      <c r="E8" s="21" t="s">
         <v>62</v>
       </c>
-      <c r="F8" s="14" t="s">
+      <c r="F8" s="21" t="s">
         <v>63</v>
       </c>
-      <c r="G8" s="14" t="s">
+      <c r="G8" s="21" t="s">
         <v>64</v>
       </c>
-      <c r="H8" s="14" t="s">
+      <c r="H8" s="21" t="s">
         <v>65</v>
       </c>
-      <c r="I8" s="14" t="s">
+      <c r="I8" s="21" t="s">
         <v>66</v>
       </c>
-      <c r="J8" s="14" t="s">
+      <c r="J8" s="21" t="s">
         <v>67</v>
       </c>
-      <c r="K8" s="14" t="s">
+      <c r="K8" s="21" t="s">
         <v>68</v>
       </c>
-      <c r="L8" s="14" t="s">
+      <c r="L8" s="21" t="s">
         <v>69</v>
       </c>
-      <c r="M8" s="14" t="s">
+      <c r="M8" s="21" t="s">
         <v>70</v>
       </c>
-      <c r="N8" s="14" t="s">
+      <c r="N8" s="21" t="s">
         <v>71</v>
       </c>
-      <c r="O8" s="37" t="s">
+      <c r="O8" s="22" t="s">
         <v>72</v>
       </c>
-      <c r="P8" s="42" t="s">
+      <c r="P8" s="23" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="9" s="2" customFormat="1" ht="33" customHeight="1" spans="1:16">
-      <c r="A9" s="12"/>
-      <c r="B9" s="12" t="s">
+      <c r="A9" s="20"/>
+      <c r="B9" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="C9" s="12"/>
-      <c r="D9" s="14" t="s">
+      <c r="C9" s="20"/>
+      <c r="D9" s="21" t="s">
         <v>75</v>
       </c>
-      <c r="E9" s="14" t="s">
+      <c r="E9" s="21" t="s">
         <v>76</v>
       </c>
-      <c r="F9" s="14" t="s">
+      <c r="F9" s="21" t="s">
         <v>77</v>
       </c>
-      <c r="G9" s="14" t="s">
+      <c r="G9" s="21" t="s">
         <v>78</v>
       </c>
-      <c r="H9" s="14" t="s">
+      <c r="H9" s="21" t="s">
         <v>79</v>
       </c>
-      <c r="I9" s="14" t="s">
+      <c r="I9" s="21" t="s">
         <v>80</v>
       </c>
-      <c r="J9" s="14" t="s">
+      <c r="J9" s="21" t="s">
         <v>81</v>
       </c>
-      <c r="K9" s="14" t="s">
+      <c r="K9" s="21" t="s">
         <v>82</v>
       </c>
-      <c r="L9" s="14" t="s">
+      <c r="L9" s="21" t="s">
         <v>83</v>
       </c>
-      <c r="M9" s="14" t="s">
+      <c r="M9" s="21" t="s">
         <v>84</v>
       </c>
-      <c r="N9" s="14" t="s">
+      <c r="N9" s="21" t="s">
         <v>85</v>
       </c>
-      <c r="O9" s="37" t="s">
+      <c r="O9" s="22" t="s">
         <v>86</v>
       </c>
-      <c r="P9" s="42" t="s">
+      <c r="P9" s="23" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="10" s="2" customFormat="1" ht="33" customHeight="1" spans="1:16">
-      <c r="A10" s="12"/>
-      <c r="B10" s="12" t="s">
+      <c r="A10" s="20"/>
+      <c r="B10" s="20" t="s">
         <v>88</v>
       </c>
-      <c r="C10" s="12"/>
-      <c r="D10" s="14" t="s">
+      <c r="C10" s="20"/>
+      <c r="D10" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="E10" s="14" t="s">
+      <c r="E10" s="21" t="s">
         <v>90</v>
       </c>
-      <c r="F10" s="14" t="s">
+      <c r="F10" s="21" t="s">
         <v>91</v>
       </c>
-      <c r="G10" s="14" t="s">
+      <c r="G10" s="21" t="s">
         <v>92</v>
       </c>
-      <c r="H10" s="14" t="s">
+      <c r="H10" s="21" t="s">
         <v>93</v>
       </c>
-      <c r="I10" s="14" t="s">
+      <c r="I10" s="21" t="s">
         <v>94</v>
       </c>
-      <c r="J10" s="14" t="s">
+      <c r="J10" s="21" t="s">
         <v>95</v>
       </c>
-      <c r="K10" s="14" t="s">
+      <c r="K10" s="21" t="s">
         <v>96</v>
       </c>
-      <c r="L10" s="14" t="s">
+      <c r="L10" s="21" t="s">
         <v>97</v>
       </c>
-      <c r="M10" s="14" t="s">
+      <c r="M10" s="21" t="s">
         <v>98</v>
       </c>
-      <c r="N10" s="14" t="s">
+      <c r="N10" s="21" t="s">
         <v>99</v>
       </c>
-      <c r="O10" s="14" t="s">
+      <c r="O10" s="21" t="s">
         <v>100</v>
       </c>
-      <c r="P10" s="42" t="s">
+      <c r="P10" s="23" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="11" s="2" customFormat="1" ht="33" customHeight="1" spans="1:16">
-      <c r="A11" s="12"/>
-      <c r="B11" s="12" t="s">
+      <c r="A11" s="20"/>
+      <c r="B11" s="20" t="s">
         <v>102</v>
       </c>
-      <c r="C11" s="12"/>
-      <c r="D11" s="14" t="s">
+      <c r="C11" s="20"/>
+      <c r="D11" s="21" t="s">
         <v>103</v>
       </c>
-      <c r="E11" s="14" t="s">
+      <c r="E11" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="F11" s="14" t="s">
+      <c r="F11" s="21" t="s">
         <v>105</v>
       </c>
-      <c r="G11" s="14" t="s">
+      <c r="G11" s="21" t="s">
         <v>106</v>
       </c>
-      <c r="H11" s="14" t="s">
+      <c r="H11" s="21" t="s">
         <v>107</v>
       </c>
-      <c r="I11" s="14" t="s">
+      <c r="I11" s="21" t="s">
         <v>108</v>
       </c>
-      <c r="J11" s="14" t="s">
+      <c r="J11" s="21" t="s">
         <v>109</v>
       </c>
-      <c r="K11" s="14" t="s">
+      <c r="K11" s="21" t="s">
         <v>110</v>
       </c>
-      <c r="L11" s="14" t="s">
+      <c r="L11" s="21" t="s">
         <v>111</v>
       </c>
-      <c r="M11" s="14" t="s">
+      <c r="M11" s="21" t="s">
         <v>112</v>
       </c>
-      <c r="N11" s="14" t="s">
+      <c r="N11" s="21" t="s">
         <v>113</v>
       </c>
-      <c r="O11" s="37" t="s">
+      <c r="O11" s="22" t="s">
         <v>114</v>
       </c>
-      <c r="P11" s="42" t="s">
+      <c r="P11" s="23" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="12" s="3" customFormat="1" ht="33" customHeight="1" spans="1:16">
-      <c r="A12" s="15"/>
-      <c r="B12" s="15" t="s">
+      <c r="A12" s="27"/>
+      <c r="B12" s="27" t="s">
         <v>116</v>
       </c>
-      <c r="C12" s="15"/>
-      <c r="D12" s="30" t="s">
+      <c r="C12" s="27"/>
+      <c r="D12" s="28" t="s">
         <v>117</v>
       </c>
-      <c r="E12" s="30" t="s">
+      <c r="E12" s="28" t="s">
         <v>118</v>
       </c>
-      <c r="F12" s="30" t="s">
+      <c r="F12" s="28" t="s">
         <v>119</v>
       </c>
-      <c r="G12" s="30" t="s">
+      <c r="G12" s="28" t="s">
         <v>120</v>
       </c>
-      <c r="H12" s="30" t="s">
+      <c r="H12" s="28" t="s">
         <v>121</v>
       </c>
-      <c r="I12" s="30" t="s">
+      <c r="I12" s="28" t="s">
         <v>122</v>
       </c>
-      <c r="J12" s="30" t="s">
+      <c r="J12" s="28" t="s">
         <v>123</v>
       </c>
-      <c r="K12" s="30" t="s">
+      <c r="K12" s="28" t="s">
         <v>124</v>
       </c>
-      <c r="L12" s="30" t="s">
+      <c r="L12" s="28" t="s">
         <v>125</v>
       </c>
-      <c r="M12" s="30" t="s">
+      <c r="M12" s="28" t="s">
         <v>126</v>
       </c>
-      <c r="N12" s="30" t="s">
+      <c r="N12" s="28" t="s">
         <v>127</v>
       </c>
-      <c r="O12" s="30" t="s">
+      <c r="O12" s="28" t="s">
         <v>128</v>
       </c>
-      <c r="P12" s="46" t="s">
+      <c r="P12" s="29" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="13" s="2" customFormat="1" ht="85" customHeight="1" spans="1:16">
-      <c r="A13" s="12" t="s">
+      <c r="A13" s="20" t="s">
         <v>130</v>
       </c>
-      <c r="B13" s="12" t="s">
+      <c r="B13" s="20" t="s">
         <v>131</v>
       </c>
-      <c r="C13" s="12" t="s">
+      <c r="C13" s="20" t="s">
         <v>132</v>
       </c>
-      <c r="D13" s="14" t="s">
+      <c r="D13" s="21" t="s">
         <v>133</v>
       </c>
-      <c r="E13" s="14" t="s">
+      <c r="E13" s="21" t="s">
         <v>134</v>
       </c>
-      <c r="F13" s="14" t="s">
+      <c r="F13" s="21" t="s">
         <v>135</v>
       </c>
-      <c r="G13" s="14" t="s">
+      <c r="G13" s="21" t="s">
         <v>136</v>
       </c>
-      <c r="H13" s="14" t="s">
+      <c r="H13" s="21" t="s">
         <v>137</v>
       </c>
-      <c r="I13" s="14" t="s">
+      <c r="I13" s="21" t="s">
         <v>138</v>
       </c>
-      <c r="J13" s="14" t="s">
+      <c r="J13" s="21" t="s">
         <v>139</v>
       </c>
-      <c r="K13" s="14" t="s">
+      <c r="K13" s="21" t="s">
         <v>140</v>
       </c>
-      <c r="L13" s="14" t="s">
+      <c r="L13" s="21" t="s">
         <v>141</v>
       </c>
-      <c r="M13" s="14" t="s">
+      <c r="M13" s="21" t="s">
         <v>142</v>
       </c>
-      <c r="N13" s="14" t="s">
+      <c r="N13" s="21" t="s">
         <v>143</v>
       </c>
-      <c r="O13" s="37" t="s">
+      <c r="O13" s="22" t="s">
         <v>144</v>
       </c>
-      <c r="P13" s="42" t="s">
+      <c r="P13" s="23" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="14" s="2" customFormat="1" ht="97" customHeight="1" spans="1:16">
-      <c r="A14" s="12"/>
-      <c r="B14" s="12"/>
-      <c r="C14" s="12" t="s">
+      <c r="A14" s="20"/>
+      <c r="B14" s="20"/>
+      <c r="C14" s="20" t="s">
         <v>146</v>
       </c>
-      <c r="D14" s="14" t="s">
+      <c r="D14" s="21" t="s">
         <v>147</v>
       </c>
-      <c r="E14" s="14" t="s">
+      <c r="E14" s="21" t="s">
         <v>148</v>
       </c>
-      <c r="F14" s="14" t="s">
+      <c r="F14" s="21" t="s">
         <v>149</v>
       </c>
-      <c r="G14" s="14" t="s">
+      <c r="G14" s="21" t="s">
         <v>150</v>
       </c>
-      <c r="H14" s="14" t="s">
+      <c r="H14" s="21" t="s">
         <v>151</v>
       </c>
-      <c r="I14" s="14" t="s">
+      <c r="I14" s="21" t="s">
         <v>152</v>
       </c>
-      <c r="J14" s="14" t="s">
+      <c r="J14" s="21" t="s">
         <v>153</v>
       </c>
-      <c r="K14" s="14" t="s">
+      <c r="K14" s="21" t="s">
         <v>154</v>
       </c>
-      <c r="L14" s="14" t="s">
+      <c r="L14" s="21" t="s">
         <v>155</v>
       </c>
-      <c r="M14" s="14" t="s">
+      <c r="M14" s="21" t="s">
         <v>156</v>
       </c>
-      <c r="N14" s="14" t="s">
+      <c r="N14" s="21" t="s">
         <v>157</v>
       </c>
-      <c r="O14" s="37" t="s">
+      <c r="O14" s="22" t="s">
         <v>158</v>
       </c>
-      <c r="P14" s="42" t="s">
+      <c r="P14" s="23" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="15" s="2" customFormat="1" ht="33" customHeight="1" spans="1:16">
-      <c r="A15" s="12"/>
-      <c r="B15" s="12" t="s">
+      <c r="A15" s="20"/>
+      <c r="B15" s="20" t="s">
         <v>160</v>
       </c>
-      <c r="C15" s="12"/>
-      <c r="D15" s="14" t="s">
+      <c r="C15" s="20"/>
+      <c r="D15" s="21" t="s">
         <v>161</v>
       </c>
-      <c r="E15" s="14" t="s">
+      <c r="E15" s="21" t="s">
         <v>162</v>
       </c>
-      <c r="F15" s="14" t="s">
+      <c r="F15" s="21" t="s">
         <v>163</v>
       </c>
-      <c r="G15" s="14" t="s">
+      <c r="G15" s="21" t="s">
         <v>164</v>
       </c>
-      <c r="H15" s="14" t="s">
+      <c r="H15" s="21" t="s">
         <v>165</v>
       </c>
-      <c r="I15" s="14" t="s">
+      <c r="I15" s="21" t="s">
         <v>166</v>
       </c>
-      <c r="J15" s="14" t="s">
+      <c r="J15" s="21" t="s">
         <v>167</v>
       </c>
-      <c r="K15" s="14" t="s">
+      <c r="K15" s="21" t="s">
         <v>168</v>
       </c>
-      <c r="L15" s="14" t="s">
+      <c r="L15" s="21" t="s">
         <v>169</v>
       </c>
-      <c r="M15" s="14" t="s">
+      <c r="M15" s="21" t="s">
         <v>170</v>
       </c>
-      <c r="N15" s="14" t="s">
+      <c r="N15" s="21" t="s">
         <v>171</v>
       </c>
-      <c r="O15" s="37" t="s">
+      <c r="O15" s="22" t="s">
         <v>172</v>
       </c>
-      <c r="P15" s="42" t="s">
+      <c r="P15" s="23" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="16" s="2" customFormat="1" ht="33" customHeight="1" spans="1:16">
-      <c r="A16" s="12"/>
-      <c r="B16" s="17" t="s">
+      <c r="A16" s="20"/>
+      <c r="B16" s="30" t="s">
         <v>174</v>
       </c>
-      <c r="C16" s="18"/>
-      <c r="D16" s="14" t="s">
+      <c r="C16" s="31"/>
+      <c r="D16" s="21" t="s">
         <v>175</v>
       </c>
-      <c r="E16" s="14" t="s">
+      <c r="E16" s="21" t="s">
         <v>176</v>
       </c>
-      <c r="F16" s="14" t="s">
+      <c r="F16" s="21" t="s">
         <v>177</v>
       </c>
-      <c r="G16" s="14" t="s">
+      <c r="G16" s="21" t="s">
         <v>178</v>
       </c>
-      <c r="H16" s="14" t="s">
+      <c r="H16" s="21" t="s">
         <v>179</v>
       </c>
-      <c r="I16" s="14" t="s">
+      <c r="I16" s="21" t="s">
         <v>180</v>
       </c>
-      <c r="J16" s="14" t="s">
+      <c r="J16" s="21" t="s">
         <v>181</v>
       </c>
-      <c r="K16" s="14" t="s">
+      <c r="K16" s="21" t="s">
         <v>182</v>
       </c>
-      <c r="L16" s="14" t="s">
+      <c r="L16" s="21" t="s">
         <v>183</v>
       </c>
-      <c r="M16" s="14" t="s">
+      <c r="M16" s="21" t="s">
         <v>184</v>
       </c>
-      <c r="N16" s="14" t="s">
+      <c r="N16" s="21" t="s">
         <v>185</v>
       </c>
-      <c r="O16" s="37" t="s">
+      <c r="O16" s="22" t="s">
         <v>186</v>
       </c>
-      <c r="P16" s="42" t="s">
+      <c r="P16" s="23" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="17" s="2" customFormat="1" ht="33" customHeight="1" spans="1:18">
-      <c r="A17" s="12"/>
-      <c r="B17" s="17" t="s">
+      <c r="A17" s="20"/>
+      <c r="B17" s="30" t="s">
         <v>188</v>
       </c>
-      <c r="C17" s="18"/>
-      <c r="D17" s="14" t="s">
+      <c r="C17" s="31"/>
+      <c r="D17" s="21" t="s">
         <v>189</v>
       </c>
-      <c r="E17" s="14" t="s">
+      <c r="E17" s="21" t="s">
         <v>190</v>
       </c>
-      <c r="F17" s="14" t="s">
+      <c r="F17" s="21" t="s">
         <v>191</v>
       </c>
-      <c r="G17" s="14" t="s">
+      <c r="G17" s="21" t="s">
         <v>192</v>
       </c>
-      <c r="H17" s="14" t="s">
+      <c r="H17" s="21" t="s">
         <v>193</v>
       </c>
-      <c r="I17" s="14" t="s">
+      <c r="I17" s="21" t="s">
         <v>194</v>
       </c>
-      <c r="J17" s="14" t="s">
+      <c r="J17" s="21" t="s">
         <v>195</v>
       </c>
-      <c r="K17" s="14" t="s">
+      <c r="K17" s="21" t="s">
         <v>196</v>
       </c>
-      <c r="L17" s="14" t="s">
+      <c r="L17" s="21" t="s">
         <v>197</v>
       </c>
-      <c r="M17" s="14" t="s">
+      <c r="M17" s="21" t="s">
         <v>198</v>
       </c>
-      <c r="N17" s="14" t="s">
+      <c r="N17" s="21" t="s">
         <v>199</v>
       </c>
-      <c r="O17" s="37" t="s">
+      <c r="O17" s="22" t="s">
         <v>200</v>
       </c>
-      <c r="P17" s="42" t="s">
+      <c r="P17" s="23" t="s">
         <v>201</v>
       </c>
       <c r="R17" s="2" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="18" s="3" customFormat="1" ht="33" customHeight="1" spans="1:16">
-      <c r="A18" s="15"/>
-      <c r="B18" s="20" t="s">
+    <row r="18" s="3" customFormat="1" ht="33" customHeight="1" spans="1:18">
+      <c r="A18" s="27"/>
+      <c r="B18" s="32" t="s">
         <v>203</v>
       </c>
-      <c r="C18" s="21"/>
-      <c r="D18" s="30" t="s">
+      <c r="C18" s="33"/>
+      <c r="D18" s="28" t="s">
         <v>204</v>
       </c>
-      <c r="E18" s="30" t="s">
+      <c r="E18" s="28" t="s">
         <v>205</v>
       </c>
-      <c r="F18" s="30" t="s">
+      <c r="F18" s="28" t="s">
         <v>206</v>
       </c>
-      <c r="G18" s="30" t="s">
+      <c r="G18" s="28" t="s">
         <v>207</v>
       </c>
-      <c r="H18" s="30" t="s">
+      <c r="H18" s="28" t="s">
         <v>208</v>
       </c>
-      <c r="I18" s="30" t="s">
+      <c r="I18" s="28" t="s">
         <v>209</v>
       </c>
-      <c r="J18" s="30" t="s">
+      <c r="J18" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="K18" s="30" t="s">
+      <c r="K18" s="28" t="s">
         <v>211</v>
       </c>
-      <c r="L18" s="30" t="s">
+      <c r="L18" s="28" t="s">
         <v>212</v>
       </c>
-      <c r="M18" s="30" t="s">
+      <c r="M18" s="28" t="s">
         <v>213</v>
       </c>
-      <c r="N18" s="30" t="s">
+      <c r="N18" s="28" t="s">
         <v>214</v>
       </c>
-      <c r="O18" s="30" t="s">
+      <c r="O18" s="28" t="s">
         <v>215</v>
       </c>
-      <c r="P18" s="46" t="s">
+      <c r="P18" s="29" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="19" s="3" customFormat="1" ht="42" customHeight="1" spans="1:16">
-      <c r="A19" s="23" t="s">
+    <row r="19" s="3" customFormat="1" ht="42" customHeight="1" spans="1:18">
+      <c r="A19" s="34" t="s">
         <v>217</v>
       </c>
-      <c r="B19" s="23"/>
-      <c r="C19" s="23"/>
-      <c r="D19" s="31" t="s">
+      <c r="B19" s="34"/>
+      <c r="C19" s="34"/>
+      <c r="D19" s="35" t="s">
         <v>218</v>
       </c>
-      <c r="E19" s="31" t="s">
+      <c r="E19" s="35" t="s">
         <v>219</v>
       </c>
-      <c r="F19" s="31" t="s">
+      <c r="F19" s="35" t="s">
         <v>220</v>
       </c>
-      <c r="G19" s="31" t="s">
+      <c r="G19" s="35" t="s">
         <v>221</v>
       </c>
-      <c r="H19" s="31" t="s">
+      <c r="H19" s="35" t="s">
         <v>222</v>
       </c>
-      <c r="I19" s="31" t="s">
+      <c r="I19" s="35" t="s">
         <v>223</v>
       </c>
-      <c r="J19" s="31" t="s">
+      <c r="J19" s="35" t="s">
         <v>224</v>
       </c>
-      <c r="K19" s="31" t="s">
+      <c r="K19" s="35" t="s">
         <v>225</v>
       </c>
-      <c r="L19" s="31" t="s">
+      <c r="L19" s="35" t="s">
         <v>226</v>
       </c>
-      <c r="M19" s="31" t="s">
+      <c r="M19" s="35" t="s">
         <v>227</v>
       </c>
-      <c r="N19" s="31" t="s">
+      <c r="N19" s="35" t="s">
         <v>228</v>
       </c>
-      <c r="O19" s="31" t="s">
+      <c r="O19" s="35" t="s">
         <v>229</v>
       </c>
-      <c r="P19" s="46" t="s">
+      <c r="P19" s="29" t="s">
         <v>230</v>
       </c>
     </row>
@@ -3337,15 +3245,15 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:R20"/>
+  <dimension ref="A1:Q20"/>
   <sheetFormatPr defaultColWidth="9.69230769230769" defaultRowHeight="17.6"/>
   <cols>
     <col min="1" max="1" width="10.6346153846154" style="1" customWidth="1"/>
     <col min="2" max="2" width="11.3076923076923" style="1" customWidth="1"/>
-    <col min="3" max="4" width="12.1153846153846" style="1" customWidth="1"/>
-    <col min="5" max="17" width="11.3076923076923" style="1" customWidth="1"/>
-    <col min="18" max="18" width="11.7115384615385" style="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.69230769230769" style="1"/>
+    <col min="3" max="3" width="12.1153846153846" style="1" customWidth="1"/>
+    <col min="4" max="16" width="11.3076923076923" style="1" customWidth="1"/>
+    <col min="17" max="17" width="11.7115384615385" style="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.69230769230769" style="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="42" customHeight="1" spans="1:17">
@@ -3367,866 +3275,816 @@
       <c r="N1" s="6"/>
       <c r="O1" s="6"/>
       <c r="P1" s="6"/>
-      <c r="Q1" s="6"/>
     </row>
     <row r="2" s="1" customFormat="1" ht="20" customHeight="1" spans="1:17">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
-      <c r="M2" s="7"/>
-      <c r="N2" s="7"/>
-      <c r="O2" s="7"/>
-      <c r="P2" s="7"/>
-      <c r="Q2" s="7"/>
-    </row>
-    <row r="3" ht="26" customHeight="1" spans="1:18">
-      <c r="A3" s="8" t="s">
+      <c r="B2" s="8"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="8"/>
+      <c r="F2" s="8"/>
+      <c r="G2" s="8"/>
+      <c r="H2" s="8"/>
+      <c r="I2" s="8"/>
+      <c r="J2" s="8"/>
+      <c r="K2" s="8"/>
+      <c r="L2" s="8"/>
+      <c r="M2" s="8"/>
+      <c r="N2" s="8"/>
+      <c r="O2" s="8"/>
+      <c r="P2" s="8"/>
+    </row>
+    <row r="3" ht="26" customHeight="1" spans="1:17">
+      <c r="A3" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="8"/>
-      <c r="C3" s="8"/>
-      <c r="D3" s="9" t="s">
+      <c r="B3" s="10"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" s="10"/>
+      <c r="F3" s="10"/>
+      <c r="G3" s="10"/>
+      <c r="H3" s="10"/>
+      <c r="I3" s="10"/>
+      <c r="J3" s="10"/>
+      <c r="K3" s="10"/>
+      <c r="L3" s="10"/>
+      <c r="M3" s="10"/>
+      <c r="N3" s="10"/>
+      <c r="O3" s="40"/>
+      <c r="P3" s="41" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q3" s="14" t="s">
         <v>232</v>
       </c>
-      <c r="E3" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="F3" s="8"/>
-      <c r="G3" s="8"/>
-      <c r="H3" s="8"/>
-      <c r="I3" s="8"/>
-      <c r="J3" s="8"/>
-      <c r="K3" s="8"/>
-      <c r="L3" s="8"/>
-      <c r="M3" s="8"/>
-      <c r="N3" s="8"/>
-      <c r="O3" s="8"/>
-      <c r="P3" s="48"/>
-      <c r="Q3" s="50" t="s">
-        <v>4</v>
-      </c>
-      <c r="R3" s="39" t="s">
+    </row>
+    <row r="4" ht="26" customHeight="1" spans="1:17">
+      <c r="A4" s="15"/>
+      <c r="B4" s="15"/>
+      <c r="C4" s="15"/>
+      <c r="D4" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="E4" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="F4" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="G4" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="H4" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="I4" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="J4" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="K4" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="L4" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="M4" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="N4" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="O4" s="42" t="s">
+        <v>16</v>
+      </c>
+      <c r="P4" s="43"/>
+      <c r="Q4" s="19"/>
+    </row>
+    <row r="5" s="2" customFormat="1" ht="33" customHeight="1" spans="1:17">
+      <c r="A5" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="20"/>
+      <c r="D5" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="E5" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="F5" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="G5" s="21" t="s">
+        <v>22</v>
+      </c>
+      <c r="H5" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="I5" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="J5" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="K5" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="L5" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="M5" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="N5" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="O5" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="P5" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q5" s="19"/>
+    </row>
+    <row r="6" s="2" customFormat="1" ht="33" customHeight="1" spans="1:17">
+      <c r="A6" s="20"/>
+      <c r="B6" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="C6" s="20"/>
+      <c r="D6" s="21" t="s">
+        <v>33</v>
+      </c>
+      <c r="E6" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="F6" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="G6" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="H6" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="I6" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="J6" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="K6" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="L6" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="M6" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="N6" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="O6" s="22" t="s">
+        <v>44</v>
+      </c>
+      <c r="P6" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q6" s="24" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="4" ht="26" customHeight="1" spans="1:18">
-      <c r="A4" s="10"/>
-      <c r="B4" s="10"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="11"/>
-      <c r="E4" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="F4" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="G4" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="H4" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="I4" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="J4" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="K4" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="L4" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="M4" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="N4" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="O4" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="P4" s="49" t="s">
-        <v>16</v>
-      </c>
-      <c r="Q4" s="51"/>
-      <c r="R4" s="41"/>
-    </row>
-    <row r="5" s="2" customFormat="1" ht="33" customHeight="1" spans="1:18">
-      <c r="A5" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="B5" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="C5" s="12"/>
-      <c r="D5" s="13" t="s">
+    <row r="7" s="2" customFormat="1" ht="33" customHeight="1" spans="1:17">
+      <c r="A7" s="20"/>
+      <c r="B7" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="C7" s="20"/>
+      <c r="D7" s="21" t="s">
+        <v>47</v>
+      </c>
+      <c r="E7" s="21" t="s">
+        <v>48</v>
+      </c>
+      <c r="F7" s="21" t="s">
+        <v>49</v>
+      </c>
+      <c r="G7" s="21" t="s">
+        <v>50</v>
+      </c>
+      <c r="H7" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="I7" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="J7" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="K7" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="L7" s="21" t="s">
+        <v>55</v>
+      </c>
+      <c r="M7" s="21" t="s">
+        <v>56</v>
+      </c>
+      <c r="N7" s="21" t="s">
+        <v>57</v>
+      </c>
+      <c r="O7" s="22" t="s">
+        <v>58</v>
+      </c>
+      <c r="P7" s="23" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q7" s="25"/>
+    </row>
+    <row r="8" s="2" customFormat="1" ht="33" customHeight="1" spans="1:17">
+      <c r="A8" s="20"/>
+      <c r="B8" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="C8" s="20"/>
+      <c r="D8" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="E8" s="21" t="s">
+        <v>62</v>
+      </c>
+      <c r="F8" s="21" t="s">
+        <v>63</v>
+      </c>
+      <c r="G8" s="21" t="s">
+        <v>64</v>
+      </c>
+      <c r="H8" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="I8" s="21" t="s">
+        <v>66</v>
+      </c>
+      <c r="J8" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="K8" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="L8" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="M8" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="N8" s="21" t="s">
+        <v>71</v>
+      </c>
+      <c r="O8" s="22" t="s">
+        <v>72</v>
+      </c>
+      <c r="P8" s="23" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q8" s="25"/>
+    </row>
+    <row r="9" s="2" customFormat="1" ht="33" customHeight="1" spans="1:17">
+      <c r="A9" s="20"/>
+      <c r="B9" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="C9" s="20"/>
+      <c r="D9" s="21" t="s">
+        <v>75</v>
+      </c>
+      <c r="E9" s="21" t="s">
+        <v>76</v>
+      </c>
+      <c r="F9" s="21" t="s">
+        <v>77</v>
+      </c>
+      <c r="G9" s="21" t="s">
+        <v>78</v>
+      </c>
+      <c r="H9" s="21" t="s">
+        <v>79</v>
+      </c>
+      <c r="I9" s="21" t="s">
+        <v>80</v>
+      </c>
+      <c r="J9" s="21" t="s">
+        <v>81</v>
+      </c>
+      <c r="K9" s="21" t="s">
+        <v>82</v>
+      </c>
+      <c r="L9" s="21" t="s">
+        <v>83</v>
+      </c>
+      <c r="M9" s="21" t="s">
+        <v>84</v>
+      </c>
+      <c r="N9" s="21" t="s">
+        <v>85</v>
+      </c>
+      <c r="O9" s="22" t="s">
+        <v>86</v>
+      </c>
+      <c r="P9" s="23" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q9" s="26"/>
+    </row>
+    <row r="10" s="2" customFormat="1" ht="33" customHeight="1" spans="1:17">
+      <c r="A10" s="20"/>
+      <c r="B10" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="C10" s="20"/>
+      <c r="D10" s="21" t="s">
+        <v>89</v>
+      </c>
+      <c r="E10" s="21" t="s">
+        <v>90</v>
+      </c>
+      <c r="F10" s="21" t="s">
+        <v>91</v>
+      </c>
+      <c r="G10" s="21" t="s">
+        <v>92</v>
+      </c>
+      <c r="H10" s="21" t="s">
+        <v>93</v>
+      </c>
+      <c r="I10" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="J10" s="21" t="s">
+        <v>95</v>
+      </c>
+      <c r="K10" s="21" t="s">
+        <v>96</v>
+      </c>
+      <c r="L10" s="21" t="s">
+        <v>97</v>
+      </c>
+      <c r="M10" s="21" t="s">
+        <v>98</v>
+      </c>
+      <c r="N10" s="21" t="s">
+        <v>99</v>
+      </c>
+      <c r="O10" s="21" t="s">
+        <v>100</v>
+      </c>
+      <c r="P10" s="23" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="11" s="2" customFormat="1" ht="33" customHeight="1" spans="1:17">
+      <c r="A11" s="20"/>
+      <c r="B11" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="C11" s="20"/>
+      <c r="D11" s="21" t="s">
+        <v>103</v>
+      </c>
+      <c r="E11" s="21" t="s">
+        <v>104</v>
+      </c>
+      <c r="F11" s="21" t="s">
+        <v>105</v>
+      </c>
+      <c r="G11" s="21" t="s">
+        <v>106</v>
+      </c>
+      <c r="H11" s="21" t="s">
+        <v>107</v>
+      </c>
+      <c r="I11" s="21" t="s">
+        <v>108</v>
+      </c>
+      <c r="J11" s="21" t="s">
+        <v>109</v>
+      </c>
+      <c r="K11" s="21" t="s">
+        <v>110</v>
+      </c>
+      <c r="L11" s="21" t="s">
+        <v>111</v>
+      </c>
+      <c r="M11" s="21" t="s">
+        <v>112</v>
+      </c>
+      <c r="N11" s="21" t="s">
+        <v>113</v>
+      </c>
+      <c r="O11" s="22" t="s">
+        <v>114</v>
+      </c>
+      <c r="P11" s="23" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="12" s="3" customFormat="1" ht="33" customHeight="1" spans="1:17">
+      <c r="A12" s="27"/>
+      <c r="B12" s="27" t="s">
+        <v>116</v>
+      </c>
+      <c r="C12" s="27"/>
+      <c r="D12" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="E12" s="28" t="s">
+        <v>118</v>
+      </c>
+      <c r="F12" s="28" t="s">
+        <v>119</v>
+      </c>
+      <c r="G12" s="28" t="s">
+        <v>120</v>
+      </c>
+      <c r="H12" s="28" t="s">
+        <v>121</v>
+      </c>
+      <c r="I12" s="28" t="s">
+        <v>122</v>
+      </c>
+      <c r="J12" s="28" t="s">
+        <v>123</v>
+      </c>
+      <c r="K12" s="28" t="s">
+        <v>124</v>
+      </c>
+      <c r="L12" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="M12" s="28" t="s">
+        <v>126</v>
+      </c>
+      <c r="N12" s="28" t="s">
+        <v>127</v>
+      </c>
+      <c r="O12" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="P12" s="29" t="s">
+        <v>129</v>
+      </c>
+      <c r="Q12" s="44"/>
+    </row>
+    <row r="13" s="2" customFormat="1" ht="56" customHeight="1" spans="1:17">
+      <c r="A13" s="20" t="s">
+        <v>130</v>
+      </c>
+      <c r="B13" s="20" t="s">
+        <v>131</v>
+      </c>
+      <c r="C13" s="20" t="s">
+        <v>132</v>
+      </c>
+      <c r="D13" s="21" t="s">
+        <v>133</v>
+      </c>
+      <c r="E13" s="21" t="s">
+        <v>134</v>
+      </c>
+      <c r="F13" s="21" t="s">
+        <v>135</v>
+      </c>
+      <c r="G13" s="21" t="s">
+        <v>136</v>
+      </c>
+      <c r="H13" s="21" t="s">
+        <v>137</v>
+      </c>
+      <c r="I13" s="21" t="s">
+        <v>138</v>
+      </c>
+      <c r="J13" s="21" t="s">
+        <v>139</v>
+      </c>
+      <c r="K13" s="21" t="s">
+        <v>140</v>
+      </c>
+      <c r="L13" s="21" t="s">
+        <v>141</v>
+      </c>
+      <c r="M13" s="21" t="s">
+        <v>142</v>
+      </c>
+      <c r="N13" s="21" t="s">
+        <v>143</v>
+      </c>
+      <c r="O13" s="22" t="s">
+        <v>144</v>
+      </c>
+      <c r="P13" s="23" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="14" s="2" customFormat="1" ht="63" customHeight="1" spans="1:17">
+      <c r="A14" s="20"/>
+      <c r="B14" s="20"/>
+      <c r="C14" s="20" t="s">
+        <v>146</v>
+      </c>
+      <c r="D14" s="21" t="s">
+        <v>147</v>
+      </c>
+      <c r="E14" s="21" t="s">
+        <v>148</v>
+      </c>
+      <c r="F14" s="21" t="s">
+        <v>149</v>
+      </c>
+      <c r="G14" s="21" t="s">
+        <v>150</v>
+      </c>
+      <c r="H14" s="21" t="s">
+        <v>151</v>
+      </c>
+      <c r="I14" s="21" t="s">
+        <v>152</v>
+      </c>
+      <c r="J14" s="21" t="s">
+        <v>153</v>
+      </c>
+      <c r="K14" s="21" t="s">
+        <v>154</v>
+      </c>
+      <c r="L14" s="21" t="s">
+        <v>155</v>
+      </c>
+      <c r="M14" s="21" t="s">
+        <v>156</v>
+      </c>
+      <c r="N14" s="21" t="s">
+        <v>157</v>
+      </c>
+      <c r="O14" s="22" t="s">
+        <v>158</v>
+      </c>
+      <c r="P14" s="23" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="15" s="2" customFormat="1" ht="33" customHeight="1" spans="1:17">
+      <c r="A15" s="20"/>
+      <c r="B15" s="20" t="s">
+        <v>160</v>
+      </c>
+      <c r="C15" s="20"/>
+      <c r="D15" s="21" t="s">
+        <v>161</v>
+      </c>
+      <c r="E15" s="21" t="s">
+        <v>162</v>
+      </c>
+      <c r="F15" s="21" t="s">
+        <v>163</v>
+      </c>
+      <c r="G15" s="21" t="s">
+        <v>164</v>
+      </c>
+      <c r="H15" s="21" t="s">
+        <v>165</v>
+      </c>
+      <c r="I15" s="21" t="s">
+        <v>166</v>
+      </c>
+      <c r="J15" s="21" t="s">
+        <v>167</v>
+      </c>
+      <c r="K15" s="21" t="s">
+        <v>168</v>
+      </c>
+      <c r="L15" s="21" t="s">
+        <v>169</v>
+      </c>
+      <c r="M15" s="21" t="s">
+        <v>170</v>
+      </c>
+      <c r="N15" s="21" t="s">
+        <v>171</v>
+      </c>
+      <c r="O15" s="22" t="s">
+        <v>172</v>
+      </c>
+      <c r="P15" s="23" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="16" s="2" customFormat="1" ht="33" customHeight="1" spans="1:17">
+      <c r="A16" s="20"/>
+      <c r="B16" s="30" t="s">
+        <v>174</v>
+      </c>
+      <c r="C16" s="31"/>
+      <c r="D16" s="21" t="s">
+        <v>175</v>
+      </c>
+      <c r="E16" s="21" t="s">
+        <v>176</v>
+      </c>
+      <c r="F16" s="21" t="s">
+        <v>177</v>
+      </c>
+      <c r="G16" s="21" t="s">
+        <v>178</v>
+      </c>
+      <c r="H16" s="21" t="s">
+        <v>179</v>
+      </c>
+      <c r="I16" s="21" t="s">
+        <v>180</v>
+      </c>
+      <c r="J16" s="21" t="s">
+        <v>181</v>
+      </c>
+      <c r="K16" s="21" t="s">
+        <v>182</v>
+      </c>
+      <c r="L16" s="21" t="s">
+        <v>183</v>
+      </c>
+      <c r="M16" s="21" t="s">
+        <v>184</v>
+      </c>
+      <c r="N16" s="21" t="s">
+        <v>185</v>
+      </c>
+      <c r="O16" s="22" t="s">
+        <v>186</v>
+      </c>
+      <c r="P16" s="23" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="17" s="2" customFormat="1" ht="33" customHeight="1" spans="1:17">
+      <c r="A17" s="20"/>
+      <c r="B17" s="30" t="s">
+        <v>188</v>
+      </c>
+      <c r="C17" s="31"/>
+      <c r="D17" s="21" t="s">
+        <v>189</v>
+      </c>
+      <c r="E17" s="21" t="s">
+        <v>190</v>
+      </c>
+      <c r="F17" s="21" t="s">
+        <v>191</v>
+      </c>
+      <c r="G17" s="21" t="s">
+        <v>192</v>
+      </c>
+      <c r="H17" s="21" t="s">
+        <v>193</v>
+      </c>
+      <c r="I17" s="21" t="s">
+        <v>194</v>
+      </c>
+      <c r="J17" s="21" t="s">
+        <v>195</v>
+      </c>
+      <c r="K17" s="21" t="s">
+        <v>196</v>
+      </c>
+      <c r="L17" s="21" t="s">
+        <v>197</v>
+      </c>
+      <c r="M17" s="21" t="s">
+        <v>198</v>
+      </c>
+      <c r="N17" s="21" t="s">
+        <v>199</v>
+      </c>
+      <c r="O17" s="22" t="s">
+        <v>200</v>
+      </c>
+      <c r="P17" s="23" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="18" s="3" customFormat="1" ht="33" customHeight="1" spans="1:17">
+      <c r="A18" s="27"/>
+      <c r="B18" s="32" t="s">
+        <v>203</v>
+      </c>
+      <c r="C18" s="33"/>
+      <c r="D18" s="28" t="s">
+        <v>204</v>
+      </c>
+      <c r="E18" s="28" t="s">
+        <v>205</v>
+      </c>
+      <c r="F18" s="28" t="s">
+        <v>206</v>
+      </c>
+      <c r="G18" s="28" t="s">
+        <v>207</v>
+      </c>
+      <c r="H18" s="28" t="s">
+        <v>208</v>
+      </c>
+      <c r="I18" s="28" t="s">
+        <v>209</v>
+      </c>
+      <c r="J18" s="28" t="s">
+        <v>210</v>
+      </c>
+      <c r="K18" s="28" t="s">
+        <v>211</v>
+      </c>
+      <c r="L18" s="28" t="s">
+        <v>212</v>
+      </c>
+      <c r="M18" s="28" t="s">
+        <v>213</v>
+      </c>
+      <c r="N18" s="28" t="s">
+        <v>214</v>
+      </c>
+      <c r="O18" s="28" t="s">
+        <v>215</v>
+      </c>
+      <c r="P18" s="29" t="s">
+        <v>216</v>
+      </c>
+      <c r="Q18" s="44"/>
+    </row>
+    <row r="19" s="3" customFormat="1" ht="42" customHeight="1" spans="1:17">
+      <c r="A19" s="34" t="s">
+        <v>217</v>
+      </c>
+      <c r="B19" s="34"/>
+      <c r="C19" s="34"/>
+      <c r="D19" s="35" t="s">
+        <v>218</v>
+      </c>
+      <c r="E19" s="35" t="s">
+        <v>219</v>
+      </c>
+      <c r="F19" s="35" t="s">
+        <v>220</v>
+      </c>
+      <c r="G19" s="35" t="s">
+        <v>221</v>
+      </c>
+      <c r="H19" s="35" t="s">
+        <v>222</v>
+      </c>
+      <c r="I19" s="35" t="s">
+        <v>223</v>
+      </c>
+      <c r="J19" s="35" t="s">
+        <v>224</v>
+      </c>
+      <c r="K19" s="35" t="s">
+        <v>225</v>
+      </c>
+      <c r="L19" s="35" t="s">
+        <v>226</v>
+      </c>
+      <c r="M19" s="35" t="s">
+        <v>227</v>
+      </c>
+      <c r="N19" s="35" t="s">
+        <v>228</v>
+      </c>
+      <c r="O19" s="35" t="s">
+        <v>229</v>
+      </c>
+      <c r="P19" s="29" t="s">
+        <v>230</v>
+      </c>
+      <c r="Q19" s="44"/>
+    </row>
+    <row r="20" ht="82" customHeight="1" spans="1:17">
+      <c r="A20" s="2" t="s">
         <v>234</v>
-      </c>
-      <c r="E5" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="F5" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="G5" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="H5" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="I5" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="J5" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="K5" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="L5" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="M5" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="N5" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="O5" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="P5" s="37" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q5" s="42" t="s">
-        <v>31</v>
-      </c>
-      <c r="R5" s="41"/>
-    </row>
-    <row r="6" s="2" customFormat="1" ht="33" customHeight="1" spans="1:18">
-      <c r="A6" s="12"/>
-      <c r="B6" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="C6" s="12"/>
-      <c r="D6" s="13"/>
-      <c r="E6" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="F6" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="G6" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="H6" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="I6" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="J6" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="K6" s="14" t="s">
-        <v>39</v>
-      </c>
-      <c r="L6" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="M6" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="N6" s="14" t="s">
-        <v>42</v>
-      </c>
-      <c r="O6" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="P6" s="37" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q6" s="42" t="s">
-        <v>45</v>
-      </c>
-      <c r="R6" s="43" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="7" s="2" customFormat="1" ht="33" customHeight="1" spans="1:18">
-      <c r="A7" s="12"/>
-      <c r="B7" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="C7" s="12"/>
-      <c r="D7" s="13"/>
-      <c r="E7" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="F7" s="14" t="s">
-        <v>48</v>
-      </c>
-      <c r="G7" s="14" t="s">
-        <v>49</v>
-      </c>
-      <c r="H7" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="I7" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="J7" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="K7" s="14" t="s">
-        <v>53</v>
-      </c>
-      <c r="L7" s="14" t="s">
-        <v>54</v>
-      </c>
-      <c r="M7" s="14" t="s">
-        <v>55</v>
-      </c>
-      <c r="N7" s="14" t="s">
-        <v>56</v>
-      </c>
-      <c r="O7" s="14" t="s">
-        <v>57</v>
-      </c>
-      <c r="P7" s="37" t="s">
-        <v>58</v>
-      </c>
-      <c r="Q7" s="42" t="s">
-        <v>59</v>
-      </c>
-      <c r="R7" s="44"/>
-    </row>
-    <row r="8" s="2" customFormat="1" ht="33" customHeight="1" spans="1:18">
-      <c r="A8" s="12"/>
-      <c r="B8" s="12" t="s">
-        <v>60</v>
-      </c>
-      <c r="C8" s="12"/>
-      <c r="D8" s="13"/>
-      <c r="E8" s="14" t="s">
-        <v>61</v>
-      </c>
-      <c r="F8" s="14" t="s">
-        <v>62</v>
-      </c>
-      <c r="G8" s="14" t="s">
-        <v>63</v>
-      </c>
-      <c r="H8" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="I8" s="14" t="s">
-        <v>65</v>
-      </c>
-      <c r="J8" s="14" t="s">
-        <v>66</v>
-      </c>
-      <c r="K8" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="L8" s="14" t="s">
-        <v>68</v>
-      </c>
-      <c r="M8" s="14" t="s">
-        <v>69</v>
-      </c>
-      <c r="N8" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="O8" s="14" t="s">
-        <v>71</v>
-      </c>
-      <c r="P8" s="37" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q8" s="42" t="s">
-        <v>73</v>
-      </c>
-      <c r="R8" s="44"/>
-    </row>
-    <row r="9" s="2" customFormat="1" ht="33" customHeight="1" spans="1:18">
-      <c r="A9" s="12"/>
-      <c r="B9" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="C9" s="12"/>
-      <c r="D9" s="13">
-        <v>297900</v>
-      </c>
-      <c r="E9" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="F9" s="14" t="s">
-        <v>76</v>
-      </c>
-      <c r="G9" s="14" t="s">
-        <v>77</v>
-      </c>
-      <c r="H9" s="14" t="s">
-        <v>78</v>
-      </c>
-      <c r="I9" s="14" t="s">
-        <v>79</v>
-      </c>
-      <c r="J9" s="14" t="s">
-        <v>80</v>
-      </c>
-      <c r="K9" s="14" t="s">
-        <v>81</v>
-      </c>
-      <c r="L9" s="14" t="s">
-        <v>82</v>
-      </c>
-      <c r="M9" s="14" t="s">
-        <v>83</v>
-      </c>
-      <c r="N9" s="14" t="s">
-        <v>84</v>
-      </c>
-      <c r="O9" s="14" t="s">
-        <v>85</v>
-      </c>
-      <c r="P9" s="37" t="s">
-        <v>86</v>
-      </c>
-      <c r="Q9" s="42" t="s">
-        <v>87</v>
-      </c>
-      <c r="R9" s="45"/>
-    </row>
-    <row r="10" s="2" customFormat="1" ht="33" customHeight="1" spans="1:17">
-      <c r="A10" s="12"/>
-      <c r="B10" s="12" t="s">
-        <v>88</v>
-      </c>
-      <c r="C10" s="12"/>
-      <c r="D10" s="13" t="s">
-        <v>234</v>
-      </c>
-      <c r="E10" s="14" t="s">
-        <v>89</v>
-      </c>
-      <c r="F10" s="14" t="s">
-        <v>90</v>
-      </c>
-      <c r="G10" s="14" t="s">
-        <v>91</v>
-      </c>
-      <c r="H10" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="I10" s="14" t="s">
-        <v>93</v>
-      </c>
-      <c r="J10" s="14" t="s">
-        <v>94</v>
-      </c>
-      <c r="K10" s="14" t="s">
-        <v>95</v>
-      </c>
-      <c r="L10" s="14" t="s">
-        <v>96</v>
-      </c>
-      <c r="M10" s="14" t="s">
-        <v>97</v>
-      </c>
-      <c r="N10" s="14" t="s">
-        <v>98</v>
-      </c>
-      <c r="O10" s="14" t="s">
-        <v>99</v>
-      </c>
-      <c r="P10" s="14" t="s">
-        <v>100</v>
-      </c>
-      <c r="Q10" s="42" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="11" s="2" customFormat="1" ht="33" customHeight="1" spans="1:17">
-      <c r="A11" s="12"/>
-      <c r="B11" s="12" t="s">
-        <v>102</v>
-      </c>
-      <c r="C11" s="12"/>
-      <c r="D11" s="13" t="s">
-        <v>234</v>
-      </c>
-      <c r="E11" s="14" t="s">
-        <v>103</v>
-      </c>
-      <c r="F11" s="14" t="s">
-        <v>104</v>
-      </c>
-      <c r="G11" s="14" t="s">
-        <v>105</v>
-      </c>
-      <c r="H11" s="14" t="s">
-        <v>106</v>
-      </c>
-      <c r="I11" s="14" t="s">
-        <v>107</v>
-      </c>
-      <c r="J11" s="14" t="s">
-        <v>108</v>
-      </c>
-      <c r="K11" s="14" t="s">
-        <v>109</v>
-      </c>
-      <c r="L11" s="14" t="s">
-        <v>110</v>
-      </c>
-      <c r="M11" s="14" t="s">
-        <v>111</v>
-      </c>
-      <c r="N11" s="14" t="s">
-        <v>112</v>
-      </c>
-      <c r="O11" s="14" t="s">
-        <v>113</v>
-      </c>
-      <c r="P11" s="37" t="s">
-        <v>114</v>
-      </c>
-      <c r="Q11" s="42" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="12" s="3" customFormat="1" ht="33" customHeight="1" spans="1:18">
-      <c r="A12" s="15"/>
-      <c r="B12" s="15" t="s">
-        <v>116</v>
-      </c>
-      <c r="C12" s="15"/>
-      <c r="D12" s="16" t="s">
-        <v>234</v>
-      </c>
-      <c r="E12" s="30" t="s">
-        <v>117</v>
-      </c>
-      <c r="F12" s="30" t="s">
-        <v>118</v>
-      </c>
-      <c r="G12" s="30" t="s">
-        <v>119</v>
-      </c>
-      <c r="H12" s="30" t="s">
-        <v>120</v>
-      </c>
-      <c r="I12" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="J12" s="30" t="s">
-        <v>122</v>
-      </c>
-      <c r="K12" s="30" t="s">
-        <v>123</v>
-      </c>
-      <c r="L12" s="30" t="s">
-        <v>124</v>
-      </c>
-      <c r="M12" s="30" t="s">
-        <v>125</v>
-      </c>
-      <c r="N12" s="30" t="s">
-        <v>126</v>
-      </c>
-      <c r="O12" s="30" t="s">
-        <v>127</v>
-      </c>
-      <c r="P12" s="30" t="s">
-        <v>128</v>
-      </c>
-      <c r="Q12" s="46" t="s">
-        <v>129</v>
-      </c>
-      <c r="R12" s="52"/>
-    </row>
-    <row r="13" s="2" customFormat="1" ht="56" customHeight="1" spans="1:17">
-      <c r="A13" s="12" t="s">
-        <v>130</v>
-      </c>
-      <c r="B13" s="12" t="s">
-        <v>131</v>
-      </c>
-      <c r="C13" s="12" t="s">
-        <v>132</v>
-      </c>
-      <c r="D13" s="13" t="s">
-        <v>234</v>
-      </c>
-      <c r="E13" s="14" t="s">
-        <v>133</v>
-      </c>
-      <c r="F13" s="14" t="s">
-        <v>134</v>
-      </c>
-      <c r="G13" s="14" t="s">
-        <v>135</v>
-      </c>
-      <c r="H13" s="14" t="s">
-        <v>136</v>
-      </c>
-      <c r="I13" s="14" t="s">
-        <v>137</v>
-      </c>
-      <c r="J13" s="14" t="s">
-        <v>138</v>
-      </c>
-      <c r="K13" s="14" t="s">
-        <v>139</v>
-      </c>
-      <c r="L13" s="14" t="s">
-        <v>140</v>
-      </c>
-      <c r="M13" s="14" t="s">
-        <v>141</v>
-      </c>
-      <c r="N13" s="14" t="s">
-        <v>142</v>
-      </c>
-      <c r="O13" s="14" t="s">
-        <v>143</v>
-      </c>
-      <c r="P13" s="37" t="s">
-        <v>144</v>
-      </c>
-      <c r="Q13" s="42" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="14" s="2" customFormat="1" ht="63" customHeight="1" spans="1:17">
-      <c r="A14" s="12"/>
-      <c r="B14" s="12"/>
-      <c r="C14" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="D14" s="13" t="s">
-        <v>234</v>
-      </c>
-      <c r="E14" s="14" t="s">
-        <v>147</v>
-      </c>
-      <c r="F14" s="14" t="s">
-        <v>148</v>
-      </c>
-      <c r="G14" s="14" t="s">
-        <v>149</v>
-      </c>
-      <c r="H14" s="14" t="s">
-        <v>150</v>
-      </c>
-      <c r="I14" s="14" t="s">
-        <v>151</v>
-      </c>
-      <c r="J14" s="14" t="s">
-        <v>152</v>
-      </c>
-      <c r="K14" s="14" t="s">
-        <v>153</v>
-      </c>
-      <c r="L14" s="14" t="s">
-        <v>154</v>
-      </c>
-      <c r="M14" s="14" t="s">
-        <v>155</v>
-      </c>
-      <c r="N14" s="14" t="s">
-        <v>156</v>
-      </c>
-      <c r="O14" s="14" t="s">
-        <v>157</v>
-      </c>
-      <c r="P14" s="37" t="s">
-        <v>158</v>
-      </c>
-      <c r="Q14" s="42" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="15" s="2" customFormat="1" ht="33" customHeight="1" spans="1:17">
-      <c r="A15" s="12"/>
-      <c r="B15" s="12" t="s">
-        <v>160</v>
-      </c>
-      <c r="C15" s="12"/>
-      <c r="D15" s="13" t="s">
-        <v>234</v>
-      </c>
-      <c r="E15" s="14" t="s">
-        <v>161</v>
-      </c>
-      <c r="F15" s="14" t="s">
-        <v>162</v>
-      </c>
-      <c r="G15" s="14" t="s">
-        <v>163</v>
-      </c>
-      <c r="H15" s="14" t="s">
-        <v>164</v>
-      </c>
-      <c r="I15" s="14" t="s">
-        <v>165</v>
-      </c>
-      <c r="J15" s="14" t="s">
-        <v>166</v>
-      </c>
-      <c r="K15" s="14" t="s">
-        <v>167</v>
-      </c>
-      <c r="L15" s="14" t="s">
-        <v>168</v>
-      </c>
-      <c r="M15" s="14" t="s">
-        <v>169</v>
-      </c>
-      <c r="N15" s="14" t="s">
-        <v>170</v>
-      </c>
-      <c r="O15" s="14" t="s">
-        <v>171</v>
-      </c>
-      <c r="P15" s="37" t="s">
-        <v>172</v>
-      </c>
-      <c r="Q15" s="42" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="16" s="2" customFormat="1" ht="33" customHeight="1" spans="1:17">
-      <c r="A16" s="12"/>
-      <c r="B16" s="17" t="s">
-        <v>174</v>
-      </c>
-      <c r="C16" s="18"/>
-      <c r="D16" s="19" t="s">
-        <v>234</v>
-      </c>
-      <c r="E16" s="14" t="s">
-        <v>175</v>
-      </c>
-      <c r="F16" s="14" t="s">
-        <v>176</v>
-      </c>
-      <c r="G16" s="14" t="s">
-        <v>177</v>
-      </c>
-      <c r="H16" s="14" t="s">
-        <v>178</v>
-      </c>
-      <c r="I16" s="14" t="s">
-        <v>179</v>
-      </c>
-      <c r="J16" s="14" t="s">
-        <v>180</v>
-      </c>
-      <c r="K16" s="14" t="s">
-        <v>181</v>
-      </c>
-      <c r="L16" s="14" t="s">
-        <v>182</v>
-      </c>
-      <c r="M16" s="14" t="s">
-        <v>183</v>
-      </c>
-      <c r="N16" s="14" t="s">
-        <v>184</v>
-      </c>
-      <c r="O16" s="14" t="s">
-        <v>185</v>
-      </c>
-      <c r="P16" s="37" t="s">
-        <v>186</v>
-      </c>
-      <c r="Q16" s="42" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="17" s="2" customFormat="1" ht="33" customHeight="1" spans="1:17">
-      <c r="A17" s="12"/>
-      <c r="B17" s="17" t="s">
-        <v>188</v>
-      </c>
-      <c r="C17" s="18"/>
-      <c r="D17" s="19" t="s">
-        <v>234</v>
-      </c>
-      <c r="E17" s="14" t="s">
-        <v>189</v>
-      </c>
-      <c r="F17" s="14" t="s">
-        <v>190</v>
-      </c>
-      <c r="G17" s="14" t="s">
-        <v>191</v>
-      </c>
-      <c r="H17" s="14" t="s">
-        <v>192</v>
-      </c>
-      <c r="I17" s="14" t="s">
-        <v>193</v>
-      </c>
-      <c r="J17" s="14" t="s">
-        <v>194</v>
-      </c>
-      <c r="K17" s="14" t="s">
-        <v>195</v>
-      </c>
-      <c r="L17" s="14" t="s">
-        <v>196</v>
-      </c>
-      <c r="M17" s="14" t="s">
-        <v>197</v>
-      </c>
-      <c r="N17" s="14" t="s">
-        <v>198</v>
-      </c>
-      <c r="O17" s="14" t="s">
-        <v>199</v>
-      </c>
-      <c r="P17" s="37" t="s">
-        <v>200</v>
-      </c>
-      <c r="Q17" s="42" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="18" s="3" customFormat="1" ht="33" customHeight="1" spans="1:18">
-      <c r="A18" s="15"/>
-      <c r="B18" s="20" t="s">
-        <v>203</v>
-      </c>
-      <c r="C18" s="21"/>
-      <c r="D18" s="22" t="s">
-        <v>234</v>
-      </c>
-      <c r="E18" s="30" t="s">
-        <v>204</v>
-      </c>
-      <c r="F18" s="30" t="s">
-        <v>205</v>
-      </c>
-      <c r="G18" s="30" t="s">
-        <v>206</v>
-      </c>
-      <c r="H18" s="30" t="s">
-        <v>207</v>
-      </c>
-      <c r="I18" s="30" t="s">
-        <v>208</v>
-      </c>
-      <c r="J18" s="30" t="s">
-        <v>209</v>
-      </c>
-      <c r="K18" s="30" t="s">
-        <v>210</v>
-      </c>
-      <c r="L18" s="30" t="s">
-        <v>211</v>
-      </c>
-      <c r="M18" s="30" t="s">
-        <v>212</v>
-      </c>
-      <c r="N18" s="30" t="s">
-        <v>213</v>
-      </c>
-      <c r="O18" s="30" t="s">
-        <v>214</v>
-      </c>
-      <c r="P18" s="30" t="s">
-        <v>215</v>
-      </c>
-      <c r="Q18" s="46" t="s">
-        <v>216</v>
-      </c>
-      <c r="R18" s="52"/>
-    </row>
-    <row r="19" s="3" customFormat="1" ht="42" customHeight="1" spans="1:18">
-      <c r="A19" s="23" t="s">
-        <v>217</v>
-      </c>
-      <c r="B19" s="23"/>
-      <c r="C19" s="23"/>
-      <c r="D19" s="24" t="s">
-        <v>234</v>
-      </c>
-      <c r="E19" s="31" t="s">
-        <v>218</v>
-      </c>
-      <c r="F19" s="31" t="s">
-        <v>219</v>
-      </c>
-      <c r="G19" s="31" t="s">
-        <v>220</v>
-      </c>
-      <c r="H19" s="31" t="s">
-        <v>221</v>
-      </c>
-      <c r="I19" s="31" t="s">
-        <v>222</v>
-      </c>
-      <c r="J19" s="31" t="s">
-        <v>223</v>
-      </c>
-      <c r="K19" s="31" t="s">
-        <v>224</v>
-      </c>
-      <c r="L19" s="31" t="s">
-        <v>225</v>
-      </c>
-      <c r="M19" s="31" t="s">
-        <v>226</v>
-      </c>
-      <c r="N19" s="31" t="s">
-        <v>227</v>
-      </c>
-      <c r="O19" s="31" t="s">
-        <v>228</v>
-      </c>
-      <c r="P19" s="31" t="s">
-        <v>229</v>
-      </c>
-      <c r="Q19" s="46" t="s">
-        <v>230</v>
-      </c>
-      <c r="R19" s="52"/>
-    </row>
-    <row r="20" ht="82" customHeight="1" spans="1:5">
-      <c r="A20" s="2" t="s">
-        <v>236</v>
       </c>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
-      <c r="D20" s="47" t="s">
-        <v>237</v>
-      </c>
-      <c r="E20" s="47" t="s">
-        <v>238</v>
-      </c>
+      <c r="D20" s="45"/>
     </row>
   </sheetData>
-  <mergeCells count="25">
-    <mergeCell ref="A1:Q1"/>
-    <mergeCell ref="A2:Q2"/>
-    <mergeCell ref="E3:P3"/>
+  <mergeCells count="24">
+    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="A2:P2"/>
+    <mergeCell ref="D3:O3"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="B7:C7"/>
@@ -4244,10 +4102,9 @@
     <mergeCell ref="A5:A12"/>
     <mergeCell ref="A13:A18"/>
     <mergeCell ref="B13:B14"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="Q3:Q4"/>
-    <mergeCell ref="R3:R5"/>
-    <mergeCell ref="R6:R9"/>
+    <mergeCell ref="P3:P4"/>
+    <mergeCell ref="Q3:Q5"/>
+    <mergeCell ref="Q6:Q9"/>
     <mergeCell ref="A3:C4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511805555555556" footer="0.511805555555556"/>
@@ -4273,803 +4130,803 @@
   <sheetData>
     <row r="1" ht="42" customHeight="1" spans="1:16">
       <c r="A1" s="6" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26"/>
-      <c r="H1" s="26"/>
-      <c r="I1" s="26"/>
-      <c r="J1" s="26"/>
-      <c r="K1" s="26"/>
-      <c r="L1" s="26"/>
-      <c r="M1" s="26"/>
-      <c r="N1" s="26"/>
-      <c r="O1" s="26"/>
-      <c r="P1" s="26"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
+      <c r="H1" s="7"/>
+      <c r="I1" s="7"/>
+      <c r="J1" s="7"/>
+      <c r="K1" s="7"/>
+      <c r="L1" s="7"/>
+      <c r="M1" s="7"/>
+      <c r="N1" s="7"/>
+      <c r="O1" s="7"/>
+      <c r="P1" s="7"/>
     </row>
     <row r="2" s="1" customFormat="1" ht="20" customHeight="1" spans="1:16">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="27"/>
-      <c r="E2" s="27"/>
-      <c r="F2" s="27"/>
-      <c r="G2" s="27"/>
-      <c r="H2" s="27"/>
-      <c r="I2" s="27"/>
-      <c r="J2" s="27"/>
-      <c r="K2" s="27"/>
-      <c r="L2" s="27"/>
-      <c r="M2" s="27"/>
-      <c r="N2" s="27"/>
-      <c r="O2" s="27"/>
-      <c r="P2" s="27"/>
+      <c r="B2" s="8"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="9"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="9"/>
+      <c r="K2" s="9"/>
+      <c r="L2" s="9"/>
+      <c r="M2" s="9"/>
+      <c r="N2" s="9"/>
+      <c r="O2" s="9"/>
+      <c r="P2" s="9"/>
     </row>
     <row r="3" ht="26" customHeight="1" spans="1:16">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="8"/>
-      <c r="C3" s="8"/>
-      <c r="D3" s="28" t="s">
+      <c r="B3" s="10"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="28"/>
-      <c r="F3" s="28"/>
-      <c r="G3" s="28"/>
-      <c r="H3" s="28"/>
-      <c r="I3" s="28"/>
-      <c r="J3" s="28"/>
-      <c r="K3" s="28"/>
-      <c r="L3" s="28"/>
-      <c r="M3" s="28"/>
-      <c r="N3" s="28"/>
-      <c r="O3" s="35"/>
-      <c r="P3" s="38" t="s">
+      <c r="E3" s="11"/>
+      <c r="F3" s="11"/>
+      <c r="G3" s="11"/>
+      <c r="H3" s="11"/>
+      <c r="I3" s="11"/>
+      <c r="J3" s="11"/>
+      <c r="K3" s="11"/>
+      <c r="L3" s="11"/>
+      <c r="M3" s="11"/>
+      <c r="N3" s="11"/>
+      <c r="O3" s="12"/>
+      <c r="P3" s="13" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="4" ht="26" customHeight="1" spans="1:16">
-      <c r="A4" s="10"/>
-      <c r="B4" s="10"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="29" t="s">
+      <c r="A4" s="15"/>
+      <c r="B4" s="15"/>
+      <c r="C4" s="15"/>
+      <c r="D4" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="29" t="s">
+      <c r="E4" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="F4" s="29" t="s">
+      <c r="F4" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="29" t="s">
+      <c r="G4" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="H4" s="29" t="s">
+      <c r="H4" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="I4" s="29" t="s">
+      <c r="I4" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="J4" s="29" t="s">
+      <c r="J4" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="K4" s="29" t="s">
+      <c r="K4" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="L4" s="29" t="s">
+      <c r="L4" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="M4" s="29" t="s">
+      <c r="M4" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="N4" s="29" t="s">
+      <c r="N4" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="O4" s="36" t="s">
+      <c r="O4" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="P4" s="40"/>
+      <c r="P4" s="18"/>
     </row>
     <row r="5" s="2" customFormat="1" ht="33" customHeight="1" spans="1:16">
-      <c r="A5" s="12" t="s">
+      <c r="A5" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="12" t="s">
+      <c r="B5" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="C5" s="12"/>
-      <c r="D5" s="14" t="s">
+      <c r="C5" s="20"/>
+      <c r="D5" s="21" t="s">
         <v>19</v>
       </c>
-      <c r="E5" s="14" t="s">
+      <c r="E5" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="F5" s="14" t="s">
+      <c r="F5" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="G5" s="14" t="s">
+      <c r="G5" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="H5" s="14" t="s">
+      <c r="H5" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="I5" s="14" t="s">
+      <c r="I5" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="J5" s="14" t="s">
+      <c r="J5" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="K5" s="14" t="s">
+      <c r="K5" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="L5" s="14" t="s">
+      <c r="L5" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="M5" s="14" t="s">
+      <c r="M5" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="N5" s="14" t="s">
+      <c r="N5" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="O5" s="37" t="s">
+      <c r="O5" s="22" t="s">
         <v>30</v>
       </c>
-      <c r="P5" s="42" t="s">
+      <c r="P5" s="23" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="6" s="2" customFormat="1" ht="33" customHeight="1" spans="1:16">
-      <c r="A6" s="12"/>
-      <c r="B6" s="12" t="s">
+      <c r="A6" s="20"/>
+      <c r="B6" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="C6" s="12"/>
-      <c r="D6" s="14" t="s">
+      <c r="C6" s="20"/>
+      <c r="D6" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="E6" s="14" t="s">
+      <c r="E6" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="F6" s="14" t="s">
+      <c r="F6" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="G6" s="14" t="s">
+      <c r="G6" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="H6" s="14" t="s">
+      <c r="H6" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="I6" s="14" t="s">
+      <c r="I6" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="J6" s="14" t="s">
+      <c r="J6" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="K6" s="14" t="s">
+      <c r="K6" s="21" t="s">
         <v>40</v>
       </c>
-      <c r="L6" s="14" t="s">
+      <c r="L6" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="M6" s="14" t="s">
+      <c r="M6" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="N6" s="14" t="s">
+      <c r="N6" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="O6" s="37" t="s">
+      <c r="O6" s="22" t="s">
         <v>44</v>
       </c>
-      <c r="P6" s="42" t="s">
+      <c r="P6" s="23" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="7" s="2" customFormat="1" ht="33" customHeight="1" spans="1:16">
-      <c r="A7" s="12"/>
-      <c r="B7" s="12" t="s">
+      <c r="A7" s="20"/>
+      <c r="B7" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="C7" s="12"/>
-      <c r="D7" s="14" t="s">
+      <c r="C7" s="20"/>
+      <c r="D7" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="E7" s="14" t="s">
+      <c r="E7" s="21" t="s">
         <v>48</v>
       </c>
-      <c r="F7" s="14" t="s">
+      <c r="F7" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="G7" s="14" t="s">
+      <c r="G7" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="H7" s="14" t="s">
+      <c r="H7" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="I7" s="14" t="s">
+      <c r="I7" s="21" t="s">
         <v>52</v>
       </c>
-      <c r="J7" s="14" t="s">
+      <c r="J7" s="21" t="s">
         <v>53</v>
       </c>
-      <c r="K7" s="14" t="s">
+      <c r="K7" s="21" t="s">
         <v>54</v>
       </c>
-      <c r="L7" s="14" t="s">
+      <c r="L7" s="21" t="s">
         <v>55</v>
       </c>
-      <c r="M7" s="14" t="s">
+      <c r="M7" s="21" t="s">
         <v>56</v>
       </c>
-      <c r="N7" s="14" t="s">
+      <c r="N7" s="21" t="s">
         <v>57</v>
       </c>
-      <c r="O7" s="37" t="s">
+      <c r="O7" s="22" t="s">
         <v>58</v>
       </c>
-      <c r="P7" s="42" t="s">
+      <c r="P7" s="23" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="8" s="2" customFormat="1" ht="33" customHeight="1" spans="1:16">
-      <c r="A8" s="12"/>
-      <c r="B8" s="12" t="s">
+      <c r="A8" s="20"/>
+      <c r="B8" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="C8" s="12"/>
-      <c r="D8" s="14" t="s">
+      <c r="C8" s="20"/>
+      <c r="D8" s="21" t="s">
         <v>61</v>
       </c>
-      <c r="E8" s="14" t="s">
+      <c r="E8" s="21" t="s">
         <v>62</v>
       </c>
-      <c r="F8" s="14" t="s">
+      <c r="F8" s="21" t="s">
         <v>63</v>
       </c>
-      <c r="G8" s="14" t="s">
+      <c r="G8" s="21" t="s">
         <v>64</v>
       </c>
-      <c r="H8" s="14" t="s">
+      <c r="H8" s="21" t="s">
         <v>65</v>
       </c>
-      <c r="I8" s="14" t="s">
+      <c r="I8" s="21" t="s">
         <v>66</v>
       </c>
-      <c r="J8" s="14" t="s">
+      <c r="J8" s="21" t="s">
         <v>67</v>
       </c>
-      <c r="K8" s="14" t="s">
+      <c r="K8" s="21" t="s">
         <v>68</v>
       </c>
-      <c r="L8" s="14" t="s">
+      <c r="L8" s="21" t="s">
         <v>69</v>
       </c>
-      <c r="M8" s="14" t="s">
+      <c r="M8" s="21" t="s">
         <v>70</v>
       </c>
-      <c r="N8" s="14" t="s">
+      <c r="N8" s="21" t="s">
         <v>71</v>
       </c>
-      <c r="O8" s="37" t="s">
+      <c r="O8" s="22" t="s">
         <v>72</v>
       </c>
-      <c r="P8" s="42" t="s">
+      <c r="P8" s="23" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="9" s="2" customFormat="1" ht="33" customHeight="1" spans="1:16">
-      <c r="A9" s="12"/>
-      <c r="B9" s="12" t="s">
+      <c r="A9" s="20"/>
+      <c r="B9" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="C9" s="12"/>
-      <c r="D9" s="14" t="s">
+      <c r="C9" s="20"/>
+      <c r="D9" s="21" t="s">
         <v>75</v>
       </c>
-      <c r="E9" s="14" t="s">
+      <c r="E9" s="21" t="s">
         <v>76</v>
       </c>
-      <c r="F9" s="14" t="s">
+      <c r="F9" s="21" t="s">
         <v>77</v>
       </c>
-      <c r="G9" s="14" t="s">
+      <c r="G9" s="21" t="s">
         <v>78</v>
       </c>
-      <c r="H9" s="14" t="s">
+      <c r="H9" s="21" t="s">
         <v>79</v>
       </c>
-      <c r="I9" s="14" t="s">
+      <c r="I9" s="21" t="s">
         <v>80</v>
       </c>
-      <c r="J9" s="14" t="s">
+      <c r="J9" s="21" t="s">
         <v>81</v>
       </c>
-      <c r="K9" s="14" t="s">
+      <c r="K9" s="21" t="s">
         <v>82</v>
       </c>
-      <c r="L9" s="14" t="s">
+      <c r="L9" s="21" t="s">
         <v>83</v>
       </c>
-      <c r="M9" s="14" t="s">
+      <c r="M9" s="21" t="s">
         <v>84</v>
       </c>
-      <c r="N9" s="14" t="s">
+      <c r="N9" s="21" t="s">
         <v>85</v>
       </c>
-      <c r="O9" s="37" t="s">
+      <c r="O9" s="22" t="s">
         <v>86</v>
       </c>
-      <c r="P9" s="42" t="s">
+      <c r="P9" s="23" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="10" s="2" customFormat="1" ht="33" customHeight="1" spans="1:16">
-      <c r="A10" s="12"/>
-      <c r="B10" s="12" t="s">
+      <c r="A10" s="20"/>
+      <c r="B10" s="20" t="s">
         <v>88</v>
       </c>
-      <c r="C10" s="12"/>
-      <c r="D10" s="14" t="s">
+      <c r="C10" s="20"/>
+      <c r="D10" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="E10" s="14" t="s">
+      <c r="E10" s="21" t="s">
         <v>90</v>
       </c>
-      <c r="F10" s="14" t="s">
+      <c r="F10" s="21" t="s">
         <v>91</v>
       </c>
-      <c r="G10" s="14" t="s">
+      <c r="G10" s="21" t="s">
         <v>92</v>
       </c>
-      <c r="H10" s="14" t="s">
+      <c r="H10" s="21" t="s">
         <v>93</v>
       </c>
-      <c r="I10" s="14" t="s">
+      <c r="I10" s="21" t="s">
         <v>94</v>
       </c>
-      <c r="J10" s="14" t="s">
+      <c r="J10" s="21" t="s">
         <v>95</v>
       </c>
-      <c r="K10" s="14" t="s">
+      <c r="K10" s="21" t="s">
         <v>96</v>
       </c>
-      <c r="L10" s="14" t="s">
+      <c r="L10" s="21" t="s">
         <v>97</v>
       </c>
-      <c r="M10" s="14" t="s">
+      <c r="M10" s="21" t="s">
         <v>98</v>
       </c>
-      <c r="N10" s="14" t="s">
+      <c r="N10" s="21" t="s">
         <v>99</v>
       </c>
-      <c r="O10" s="14" t="s">
+      <c r="O10" s="21" t="s">
         <v>100</v>
       </c>
-      <c r="P10" s="42" t="s">
+      <c r="P10" s="23" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="11" s="2" customFormat="1" ht="33" customHeight="1" spans="1:16">
-      <c r="A11" s="12"/>
-      <c r="B11" s="12" t="s">
+      <c r="A11" s="20"/>
+      <c r="B11" s="20" t="s">
         <v>102</v>
       </c>
-      <c r="C11" s="12"/>
-      <c r="D11" s="14" t="s">
+      <c r="C11" s="20"/>
+      <c r="D11" s="21" t="s">
         <v>103</v>
       </c>
-      <c r="E11" s="14" t="s">
+      <c r="E11" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="F11" s="14" t="s">
+      <c r="F11" s="21" t="s">
         <v>105</v>
       </c>
-      <c r="G11" s="14" t="s">
+      <c r="G11" s="21" t="s">
         <v>106</v>
       </c>
-      <c r="H11" s="14" t="s">
+      <c r="H11" s="21" t="s">
         <v>107</v>
       </c>
-      <c r="I11" s="14" t="s">
+      <c r="I11" s="21" t="s">
         <v>108</v>
       </c>
-      <c r="J11" s="14" t="s">
+      <c r="J11" s="21" t="s">
         <v>109</v>
       </c>
-      <c r="K11" s="14" t="s">
+      <c r="K11" s="21" t="s">
         <v>110</v>
       </c>
-      <c r="L11" s="14" t="s">
+      <c r="L11" s="21" t="s">
         <v>111</v>
       </c>
-      <c r="M11" s="14" t="s">
+      <c r="M11" s="21" t="s">
         <v>112</v>
       </c>
-      <c r="N11" s="14" t="s">
+      <c r="N11" s="21" t="s">
         <v>113</v>
       </c>
-      <c r="O11" s="37" t="s">
+      <c r="O11" s="22" t="s">
         <v>114</v>
       </c>
-      <c r="P11" s="42" t="s">
+      <c r="P11" s="23" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="12" s="3" customFormat="1" ht="33" customHeight="1" spans="1:16">
-      <c r="A12" s="15"/>
-      <c r="B12" s="15" t="s">
+      <c r="A12" s="27"/>
+      <c r="B12" s="27" t="s">
         <v>116</v>
       </c>
-      <c r="C12" s="15"/>
-      <c r="D12" s="30" t="s">
+      <c r="C12" s="27"/>
+      <c r="D12" s="28" t="s">
         <v>117</v>
       </c>
-      <c r="E12" s="30" t="s">
+      <c r="E12" s="28" t="s">
         <v>118</v>
       </c>
-      <c r="F12" s="30" t="s">
+      <c r="F12" s="28" t="s">
         <v>119</v>
       </c>
-      <c r="G12" s="30" t="s">
+      <c r="G12" s="28" t="s">
         <v>120</v>
       </c>
-      <c r="H12" s="30" t="s">
+      <c r="H12" s="28" t="s">
         <v>121</v>
       </c>
-      <c r="I12" s="30" t="s">
+      <c r="I12" s="28" t="s">
         <v>122</v>
       </c>
-      <c r="J12" s="30" t="s">
+      <c r="J12" s="28" t="s">
         <v>123</v>
       </c>
-      <c r="K12" s="30" t="s">
+      <c r="K12" s="28" t="s">
         <v>124</v>
       </c>
-      <c r="L12" s="30" t="s">
+      <c r="L12" s="28" t="s">
         <v>125</v>
       </c>
-      <c r="M12" s="30" t="s">
+      <c r="M12" s="28" t="s">
         <v>126</v>
       </c>
-      <c r="N12" s="30" t="s">
+      <c r="N12" s="28" t="s">
         <v>127</v>
       </c>
-      <c r="O12" s="30" t="s">
+      <c r="O12" s="28" t="s">
         <v>128</v>
       </c>
-      <c r="P12" s="46" t="s">
+      <c r="P12" s="29" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="13" s="2" customFormat="1" ht="57" customHeight="1" spans="1:16">
-      <c r="A13" s="12" t="s">
+      <c r="A13" s="20" t="s">
         <v>130</v>
       </c>
-      <c r="B13" s="12" t="s">
+      <c r="B13" s="20" t="s">
         <v>131</v>
       </c>
-      <c r="C13" s="12" t="s">
+      <c r="C13" s="20" t="s">
         <v>132</v>
       </c>
-      <c r="D13" s="14" t="s">
+      <c r="D13" s="21" t="s">
         <v>133</v>
       </c>
-      <c r="E13" s="14" t="s">
+      <c r="E13" s="21" t="s">
         <v>134</v>
       </c>
-      <c r="F13" s="14" t="s">
+      <c r="F13" s="21" t="s">
         <v>135</v>
       </c>
-      <c r="G13" s="14" t="s">
+      <c r="G13" s="21" t="s">
         <v>136</v>
       </c>
-      <c r="H13" s="14" t="s">
+      <c r="H13" s="21" t="s">
         <v>137</v>
       </c>
-      <c r="I13" s="14" t="s">
+      <c r="I13" s="21" t="s">
         <v>138</v>
       </c>
-      <c r="J13" s="14" t="s">
+      <c r="J13" s="21" t="s">
         <v>139</v>
       </c>
-      <c r="K13" s="14" t="s">
+      <c r="K13" s="21" t="s">
         <v>140</v>
       </c>
-      <c r="L13" s="14" t="s">
+      <c r="L13" s="21" t="s">
         <v>141</v>
       </c>
-      <c r="M13" s="14" t="s">
+      <c r="M13" s="21" t="s">
         <v>142</v>
       </c>
-      <c r="N13" s="14" t="s">
+      <c r="N13" s="21" t="s">
         <v>143</v>
       </c>
-      <c r="O13" s="37" t="s">
+      <c r="O13" s="22" t="s">
         <v>144</v>
       </c>
-      <c r="P13" s="42" t="s">
+      <c r="P13" s="23" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="14" s="2" customFormat="1" ht="63" customHeight="1" spans="1:16">
-      <c r="A14" s="12"/>
-      <c r="B14" s="12"/>
-      <c r="C14" s="12" t="s">
+      <c r="A14" s="20"/>
+      <c r="B14" s="20"/>
+      <c r="C14" s="20" t="s">
         <v>146</v>
       </c>
-      <c r="D14" s="14" t="s">
+      <c r="D14" s="21" t="s">
         <v>147</v>
       </c>
-      <c r="E14" s="14" t="s">
+      <c r="E14" s="21" t="s">
         <v>148</v>
       </c>
-      <c r="F14" s="14" t="s">
+      <c r="F14" s="21" t="s">
         <v>149</v>
       </c>
-      <c r="G14" s="14" t="s">
+      <c r="G14" s="21" t="s">
         <v>150</v>
       </c>
-      <c r="H14" s="14" t="s">
+      <c r="H14" s="21" t="s">
         <v>151</v>
       </c>
-      <c r="I14" s="14" t="s">
+      <c r="I14" s="21" t="s">
         <v>152</v>
       </c>
-      <c r="J14" s="14" t="s">
+      <c r="J14" s="21" t="s">
         <v>153</v>
       </c>
-      <c r="K14" s="14" t="s">
+      <c r="K14" s="21" t="s">
         <v>154</v>
       </c>
-      <c r="L14" s="14" t="s">
+      <c r="L14" s="21" t="s">
         <v>155</v>
       </c>
-      <c r="M14" s="14" t="s">
+      <c r="M14" s="21" t="s">
         <v>156</v>
       </c>
-      <c r="N14" s="14" t="s">
+      <c r="N14" s="21" t="s">
         <v>157</v>
       </c>
-      <c r="O14" s="37" t="s">
+      <c r="O14" s="22" t="s">
         <v>158</v>
       </c>
-      <c r="P14" s="42" t="s">
+      <c r="P14" s="23" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="15" s="2" customFormat="1" ht="33" customHeight="1" spans="1:16">
-      <c r="A15" s="12"/>
-      <c r="B15" s="12" t="s">
+      <c r="A15" s="20"/>
+      <c r="B15" s="20" t="s">
         <v>160</v>
       </c>
-      <c r="C15" s="12"/>
-      <c r="D15" s="14" t="s">
+      <c r="C15" s="20"/>
+      <c r="D15" s="21" t="s">
         <v>161</v>
       </c>
-      <c r="E15" s="14" t="s">
+      <c r="E15" s="21" t="s">
         <v>162</v>
       </c>
-      <c r="F15" s="14" t="s">
+      <c r="F15" s="21" t="s">
         <v>163</v>
       </c>
-      <c r="G15" s="14" t="s">
+      <c r="G15" s="21" t="s">
         <v>164</v>
       </c>
-      <c r="H15" s="14" t="s">
+      <c r="H15" s="21" t="s">
         <v>165</v>
       </c>
-      <c r="I15" s="14" t="s">
+      <c r="I15" s="21" t="s">
         <v>166</v>
       </c>
-      <c r="J15" s="14" t="s">
+      <c r="J15" s="21" t="s">
         <v>167</v>
       </c>
-      <c r="K15" s="14" t="s">
+      <c r="K15" s="21" t="s">
         <v>168</v>
       </c>
-      <c r="L15" s="14" t="s">
+      <c r="L15" s="21" t="s">
         <v>169</v>
       </c>
-      <c r="M15" s="14" t="s">
+      <c r="M15" s="21" t="s">
         <v>170</v>
       </c>
-      <c r="N15" s="14" t="s">
+      <c r="N15" s="21" t="s">
         <v>171</v>
       </c>
-      <c r="O15" s="37" t="s">
+      <c r="O15" s="22" t="s">
         <v>172</v>
       </c>
-      <c r="P15" s="42" t="s">
+      <c r="P15" s="23" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="16" s="2" customFormat="1" ht="33" customHeight="1" spans="1:16">
-      <c r="A16" s="12"/>
-      <c r="B16" s="17" t="s">
+      <c r="A16" s="20"/>
+      <c r="B16" s="30" t="s">
         <v>174</v>
       </c>
-      <c r="C16" s="18"/>
-      <c r="D16" s="14" t="s">
+      <c r="C16" s="31"/>
+      <c r="D16" s="21" t="s">
         <v>175</v>
       </c>
-      <c r="E16" s="14" t="s">
+      <c r="E16" s="21" t="s">
         <v>176</v>
       </c>
-      <c r="F16" s="14" t="s">
+      <c r="F16" s="21" t="s">
         <v>177</v>
       </c>
-      <c r="G16" s="14" t="s">
+      <c r="G16" s="21" t="s">
         <v>178</v>
       </c>
-      <c r="H16" s="14" t="s">
+      <c r="H16" s="21" t="s">
         <v>179</v>
       </c>
-      <c r="I16" s="14" t="s">
+      <c r="I16" s="21" t="s">
         <v>180</v>
       </c>
-      <c r="J16" s="14" t="s">
+      <c r="J16" s="21" t="s">
         <v>181</v>
       </c>
-      <c r="K16" s="14" t="s">
+      <c r="K16" s="21" t="s">
         <v>182</v>
       </c>
-      <c r="L16" s="14" t="s">
+      <c r="L16" s="21" t="s">
         <v>183</v>
       </c>
-      <c r="M16" s="14" t="s">
+      <c r="M16" s="21" t="s">
         <v>184</v>
       </c>
-      <c r="N16" s="14" t="s">
+      <c r="N16" s="21" t="s">
         <v>185</v>
       </c>
-      <c r="O16" s="37" t="s">
+      <c r="O16" s="22" t="s">
         <v>186</v>
       </c>
-      <c r="P16" s="42" t="s">
+      <c r="P16" s="23" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="17" s="2" customFormat="1" ht="33" customHeight="1" spans="1:16">
-      <c r="A17" s="12"/>
-      <c r="B17" s="17" t="s">
+      <c r="A17" s="20"/>
+      <c r="B17" s="30" t="s">
         <v>188</v>
       </c>
-      <c r="C17" s="18"/>
-      <c r="D17" s="14" t="s">
+      <c r="C17" s="31"/>
+      <c r="D17" s="21" t="s">
         <v>189</v>
       </c>
-      <c r="E17" s="14" t="s">
+      <c r="E17" s="21" t="s">
         <v>190</v>
       </c>
-      <c r="F17" s="14" t="s">
+      <c r="F17" s="21" t="s">
         <v>191</v>
       </c>
-      <c r="G17" s="14" t="s">
+      <c r="G17" s="21" t="s">
         <v>192</v>
       </c>
-      <c r="H17" s="14" t="s">
+      <c r="H17" s="21" t="s">
         <v>193</v>
       </c>
-      <c r="I17" s="14" t="s">
+      <c r="I17" s="21" t="s">
         <v>194</v>
       </c>
-      <c r="J17" s="14" t="s">
+      <c r="J17" s="21" t="s">
         <v>195</v>
       </c>
-      <c r="K17" s="14" t="s">
+      <c r="K17" s="21" t="s">
         <v>196</v>
       </c>
-      <c r="L17" s="14" t="s">
+      <c r="L17" s="21" t="s">
         <v>197</v>
       </c>
-      <c r="M17" s="14" t="s">
+      <c r="M17" s="21" t="s">
         <v>198</v>
       </c>
-      <c r="N17" s="14" t="s">
+      <c r="N17" s="21" t="s">
         <v>199</v>
       </c>
-      <c r="O17" s="37" t="s">
+      <c r="O17" s="22" t="s">
         <v>200</v>
       </c>
-      <c r="P17" s="42" t="s">
+      <c r="P17" s="23" t="s">
         <v>201</v>
       </c>
     </row>
     <row r="18" s="3" customFormat="1" ht="33" customHeight="1" spans="1:16">
-      <c r="A18" s="15"/>
-      <c r="B18" s="20" t="s">
+      <c r="A18" s="27"/>
+      <c r="B18" s="32" t="s">
         <v>203</v>
       </c>
-      <c r="C18" s="21"/>
-      <c r="D18" s="30" t="s">
+      <c r="C18" s="33"/>
+      <c r="D18" s="28" t="s">
         <v>204</v>
       </c>
-      <c r="E18" s="30" t="s">
+      <c r="E18" s="28" t="s">
         <v>205</v>
       </c>
-      <c r="F18" s="30" t="s">
+      <c r="F18" s="28" t="s">
         <v>206</v>
       </c>
-      <c r="G18" s="30" t="s">
+      <c r="G18" s="28" t="s">
         <v>207</v>
       </c>
-      <c r="H18" s="30" t="s">
+      <c r="H18" s="28" t="s">
         <v>208</v>
       </c>
-      <c r="I18" s="30" t="s">
+      <c r="I18" s="28" t="s">
         <v>209</v>
       </c>
-      <c r="J18" s="30" t="s">
+      <c r="J18" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="K18" s="30" t="s">
+      <c r="K18" s="28" t="s">
         <v>211</v>
       </c>
-      <c r="L18" s="30" t="s">
+      <c r="L18" s="28" t="s">
         <v>212</v>
       </c>
-      <c r="M18" s="30" t="s">
+      <c r="M18" s="28" t="s">
         <v>213</v>
       </c>
-      <c r="N18" s="30" t="s">
+      <c r="N18" s="28" t="s">
         <v>214</v>
       </c>
-      <c r="O18" s="30" t="s">
+      <c r="O18" s="28" t="s">
         <v>215</v>
       </c>
-      <c r="P18" s="46" t="s">
+      <c r="P18" s="29" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="19" s="3" customFormat="1" ht="42" customHeight="1" spans="1:16">
-      <c r="A19" s="23" t="s">
+      <c r="A19" s="34" t="s">
         <v>217</v>
       </c>
-      <c r="B19" s="23"/>
-      <c r="C19" s="23"/>
-      <c r="D19" s="31" t="s">
+      <c r="B19" s="34"/>
+      <c r="C19" s="34"/>
+      <c r="D19" s="35" t="s">
         <v>218</v>
       </c>
-      <c r="E19" s="31" t="s">
+      <c r="E19" s="35" t="s">
         <v>219</v>
       </c>
-      <c r="F19" s="31" t="s">
+      <c r="F19" s="35" t="s">
         <v>220</v>
       </c>
-      <c r="G19" s="31" t="s">
+      <c r="G19" s="35" t="s">
         <v>221</v>
       </c>
-      <c r="H19" s="31" t="s">
+      <c r="H19" s="35" t="s">
         <v>222</v>
       </c>
-      <c r="I19" s="31" t="s">
+      <c r="I19" s="35" t="s">
         <v>223</v>
       </c>
-      <c r="J19" s="31" t="s">
+      <c r="J19" s="35" t="s">
         <v>224</v>
       </c>
-      <c r="K19" s="31" t="s">
+      <c r="K19" s="35" t="s">
         <v>225</v>
       </c>
-      <c r="L19" s="31" t="s">
+      <c r="L19" s="35" t="s">
         <v>226</v>
       </c>
-      <c r="M19" s="31" t="s">
+      <c r="M19" s="35" t="s">
         <v>227</v>
       </c>
-      <c r="N19" s="31" t="s">
+      <c r="N19" s="35" t="s">
         <v>228</v>
       </c>
-      <c r="O19" s="31" t="s">
+      <c r="O19" s="35" t="s">
         <v>229</v>
       </c>
-      <c r="P19" s="46" t="s">
+      <c r="P19" s="29" t="s">
         <v>230</v>
       </c>
     </row>
@@ -5108,960 +4965,900 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:R21"/>
+  <dimension ref="A1:Q21"/>
   <sheetFormatPr defaultColWidth="9.69230769230769" defaultRowHeight="17.6"/>
   <cols>
     <col min="1" max="1" width="10.6346153846154" style="1" customWidth="1"/>
     <col min="2" max="2" width="11.3076923076923" style="1" customWidth="1"/>
-    <col min="3" max="4" width="11.9807692307692" style="1" customWidth="1"/>
-    <col min="5" max="17" width="11.3076923076923" style="5" customWidth="1"/>
-    <col min="18" max="16384" width="9.69230769230769" style="1"/>
+    <col min="3" max="3" width="11.9807692307692" style="1" customWidth="1"/>
+    <col min="4" max="16" width="11.3076923076923" style="5" customWidth="1"/>
+    <col min="17" max="16384" width="9.69230769230769" style="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="42" customHeight="1" spans="1:17">
       <c r="A1" s="6" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26"/>
-      <c r="H1" s="26"/>
-      <c r="I1" s="26"/>
-      <c r="J1" s="26"/>
-      <c r="K1" s="26"/>
-      <c r="L1" s="26"/>
-      <c r="M1" s="26"/>
-      <c r="N1" s="26"/>
-      <c r="O1" s="26"/>
-      <c r="P1" s="26"/>
-      <c r="Q1" s="26"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
+      <c r="H1" s="7"/>
+      <c r="I1" s="7"/>
+      <c r="J1" s="7"/>
+      <c r="K1" s="7"/>
+      <c r="L1" s="7"/>
+      <c r="M1" s="7"/>
+      <c r="N1" s="7"/>
+      <c r="O1" s="7"/>
+      <c r="P1" s="7"/>
     </row>
     <row r="2" s="1" customFormat="1" ht="20" customHeight="1" spans="1:17">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="27"/>
-      <c r="F2" s="27"/>
-      <c r="G2" s="27"/>
-      <c r="H2" s="27"/>
-      <c r="I2" s="27"/>
-      <c r="J2" s="27"/>
-      <c r="K2" s="27"/>
-      <c r="L2" s="27"/>
-      <c r="M2" s="27"/>
-      <c r="N2" s="27"/>
-      <c r="O2" s="27"/>
-      <c r="P2" s="27"/>
-      <c r="Q2" s="27"/>
-    </row>
-    <row r="3" ht="26" customHeight="1" spans="1:18">
-      <c r="A3" s="8" t="s">
+      <c r="B2" s="8"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="9"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="9"/>
+      <c r="K2" s="9"/>
+      <c r="L2" s="9"/>
+      <c r="M2" s="9"/>
+      <c r="N2" s="9"/>
+      <c r="O2" s="9"/>
+      <c r="P2" s="9"/>
+    </row>
+    <row r="3" ht="26" customHeight="1" spans="1:17">
+      <c r="A3" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="8"/>
-      <c r="C3" s="8"/>
-      <c r="D3" s="9" t="s">
+      <c r="B3" s="10"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" s="11"/>
+      <c r="F3" s="11"/>
+      <c r="G3" s="11"/>
+      <c r="H3" s="11"/>
+      <c r="I3" s="11"/>
+      <c r="J3" s="11"/>
+      <c r="K3" s="11"/>
+      <c r="L3" s="11"/>
+      <c r="M3" s="11"/>
+      <c r="N3" s="11"/>
+      <c r="O3" s="12"/>
+      <c r="P3" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q3" s="14" t="s">
         <v>232</v>
       </c>
-      <c r="E3" s="28" t="s">
-        <v>3</v>
-      </c>
-      <c r="F3" s="28"/>
-      <c r="G3" s="28"/>
-      <c r="H3" s="28"/>
-      <c r="I3" s="28"/>
-      <c r="J3" s="28"/>
-      <c r="K3" s="28"/>
-      <c r="L3" s="28"/>
-      <c r="M3" s="28"/>
-      <c r="N3" s="28"/>
-      <c r="O3" s="28"/>
-      <c r="P3" s="35"/>
-      <c r="Q3" s="38" t="s">
-        <v>4</v>
-      </c>
-      <c r="R3" s="39" t="s">
+    </row>
+    <row r="4" ht="26" customHeight="1" spans="1:17">
+      <c r="A4" s="15"/>
+      <c r="B4" s="15"/>
+      <c r="C4" s="15"/>
+      <c r="D4" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="E4" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="F4" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="G4" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="H4" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="I4" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J4" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="K4" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="L4" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="M4" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="N4" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="O4" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="P4" s="18"/>
+      <c r="Q4" s="19"/>
+    </row>
+    <row r="5" s="2" customFormat="1" ht="33" customHeight="1" spans="1:17">
+      <c r="A5" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="20"/>
+      <c r="D5" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="E5" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="F5" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="G5" s="21" t="s">
+        <v>22</v>
+      </c>
+      <c r="H5" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="I5" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="J5" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="K5" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="L5" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="M5" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="N5" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="O5" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="P5" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q5" s="19"/>
+    </row>
+    <row r="6" s="2" customFormat="1" ht="33" customHeight="1" spans="1:17">
+      <c r="A6" s="20"/>
+      <c r="B6" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="C6" s="20"/>
+      <c r="D6" s="21" t="s">
+        <v>33</v>
+      </c>
+      <c r="E6" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="F6" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="G6" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="H6" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="I6" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="J6" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="K6" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="L6" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="M6" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="N6" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="O6" s="22" t="s">
+        <v>44</v>
+      </c>
+      <c r="P6" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q6" s="24" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="4" ht="26" customHeight="1" spans="1:18">
-      <c r="A4" s="10"/>
-      <c r="B4" s="10"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="11"/>
-      <c r="E4" s="29" t="s">
-        <v>5</v>
-      </c>
-      <c r="F4" s="29" t="s">
-        <v>6</v>
-      </c>
-      <c r="G4" s="29" t="s">
-        <v>7</v>
-      </c>
-      <c r="H4" s="29" t="s">
-        <v>8</v>
-      </c>
-      <c r="I4" s="29" t="s">
-        <v>9</v>
-      </c>
-      <c r="J4" s="29" t="s">
-        <v>10</v>
-      </c>
-      <c r="K4" s="29" t="s">
-        <v>11</v>
-      </c>
-      <c r="L4" s="29" t="s">
-        <v>12</v>
-      </c>
-      <c r="M4" s="29" t="s">
-        <v>13</v>
-      </c>
-      <c r="N4" s="29" t="s">
-        <v>14</v>
-      </c>
-      <c r="O4" s="29" t="s">
-        <v>15</v>
-      </c>
-      <c r="P4" s="36" t="s">
-        <v>16</v>
-      </c>
-      <c r="Q4" s="40"/>
-      <c r="R4" s="41"/>
-    </row>
-    <row r="5" s="2" customFormat="1" ht="33" customHeight="1" spans="1:18">
-      <c r="A5" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="B5" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="C5" s="12"/>
-      <c r="D5" s="13" t="s">
+    <row r="7" s="2" customFormat="1" ht="33" customHeight="1" spans="1:17">
+      <c r="A7" s="20"/>
+      <c r="B7" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="C7" s="20"/>
+      <c r="D7" s="21" t="s">
+        <v>47</v>
+      </c>
+      <c r="E7" s="21" t="s">
+        <v>48</v>
+      </c>
+      <c r="F7" s="21" t="s">
+        <v>49</v>
+      </c>
+      <c r="G7" s="21" t="s">
+        <v>50</v>
+      </c>
+      <c r="H7" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="I7" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="J7" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="K7" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="L7" s="21" t="s">
+        <v>55</v>
+      </c>
+      <c r="M7" s="21" t="s">
+        <v>56</v>
+      </c>
+      <c r="N7" s="21" t="s">
+        <v>57</v>
+      </c>
+      <c r="O7" s="22" t="s">
+        <v>58</v>
+      </c>
+      <c r="P7" s="23" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q7" s="25"/>
+    </row>
+    <row r="8" s="2" customFormat="1" ht="33" customHeight="1" spans="1:17">
+      <c r="A8" s="20"/>
+      <c r="B8" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="C8" s="20"/>
+      <c r="D8" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="E8" s="21" t="s">
+        <v>62</v>
+      </c>
+      <c r="F8" s="21" t="s">
+        <v>63</v>
+      </c>
+      <c r="G8" s="21" t="s">
+        <v>64</v>
+      </c>
+      <c r="H8" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="I8" s="21" t="s">
+        <v>66</v>
+      </c>
+      <c r="J8" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="K8" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="L8" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="M8" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="N8" s="21" t="s">
+        <v>71</v>
+      </c>
+      <c r="O8" s="22" t="s">
+        <v>72</v>
+      </c>
+      <c r="P8" s="23" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q8" s="25"/>
+    </row>
+    <row r="9" s="2" customFormat="1" ht="33" customHeight="1" spans="1:17">
+      <c r="A9" s="20"/>
+      <c r="B9" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="C9" s="20"/>
+      <c r="D9" s="21" t="s">
+        <v>75</v>
+      </c>
+      <c r="E9" s="21" t="s">
+        <v>76</v>
+      </c>
+      <c r="F9" s="21" t="s">
+        <v>77</v>
+      </c>
+      <c r="G9" s="21" t="s">
+        <v>78</v>
+      </c>
+      <c r="H9" s="21" t="s">
+        <v>79</v>
+      </c>
+      <c r="I9" s="21" t="s">
+        <v>80</v>
+      </c>
+      <c r="J9" s="21" t="s">
+        <v>81</v>
+      </c>
+      <c r="K9" s="21" t="s">
+        <v>82</v>
+      </c>
+      <c r="L9" s="21" t="s">
+        <v>83</v>
+      </c>
+      <c r="M9" s="21" t="s">
+        <v>84</v>
+      </c>
+      <c r="N9" s="21" t="s">
+        <v>85</v>
+      </c>
+      <c r="O9" s="22" t="s">
+        <v>86</v>
+      </c>
+      <c r="P9" s="23" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q9" s="26"/>
+    </row>
+    <row r="10" s="2" customFormat="1" ht="33" customHeight="1" spans="1:17">
+      <c r="A10" s="20"/>
+      <c r="B10" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="C10" s="20"/>
+      <c r="D10" s="21" t="s">
+        <v>89</v>
+      </c>
+      <c r="E10" s="21" t="s">
+        <v>90</v>
+      </c>
+      <c r="F10" s="21" t="s">
+        <v>91</v>
+      </c>
+      <c r="G10" s="21" t="s">
+        <v>92</v>
+      </c>
+      <c r="H10" s="21" t="s">
+        <v>93</v>
+      </c>
+      <c r="I10" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="J10" s="21" t="s">
+        <v>95</v>
+      </c>
+      <c r="K10" s="21" t="s">
+        <v>96</v>
+      </c>
+      <c r="L10" s="21" t="s">
+        <v>97</v>
+      </c>
+      <c r="M10" s="21" t="s">
+        <v>98</v>
+      </c>
+      <c r="N10" s="21" t="s">
+        <v>99</v>
+      </c>
+      <c r="O10" s="21" t="s">
+        <v>100</v>
+      </c>
+      <c r="P10" s="23" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="11" s="2" customFormat="1" ht="33" customHeight="1" spans="1:17">
+      <c r="A11" s="20"/>
+      <c r="B11" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="C11" s="20"/>
+      <c r="D11" s="21" t="s">
+        <v>103</v>
+      </c>
+      <c r="E11" s="21" t="s">
+        <v>104</v>
+      </c>
+      <c r="F11" s="21" t="s">
+        <v>105</v>
+      </c>
+      <c r="G11" s="21" t="s">
+        <v>106</v>
+      </c>
+      <c r="H11" s="21" t="s">
+        <v>107</v>
+      </c>
+      <c r="I11" s="21" t="s">
+        <v>108</v>
+      </c>
+      <c r="J11" s="21" t="s">
+        <v>109</v>
+      </c>
+      <c r="K11" s="21" t="s">
+        <v>110</v>
+      </c>
+      <c r="L11" s="21" t="s">
+        <v>111</v>
+      </c>
+      <c r="M11" s="21" t="s">
+        <v>112</v>
+      </c>
+      <c r="N11" s="21" t="s">
+        <v>113</v>
+      </c>
+      <c r="O11" s="22" t="s">
+        <v>114</v>
+      </c>
+      <c r="P11" s="23" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="12" s="3" customFormat="1" ht="33" customHeight="1" spans="1:17">
+      <c r="A12" s="27"/>
+      <c r="B12" s="27" t="s">
+        <v>116</v>
+      </c>
+      <c r="C12" s="27"/>
+      <c r="D12" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="E12" s="28" t="s">
+        <v>118</v>
+      </c>
+      <c r="F12" s="28" t="s">
+        <v>119</v>
+      </c>
+      <c r="G12" s="28" t="s">
+        <v>120</v>
+      </c>
+      <c r="H12" s="28" t="s">
+        <v>121</v>
+      </c>
+      <c r="I12" s="28" t="s">
+        <v>122</v>
+      </c>
+      <c r="J12" s="28" t="s">
+        <v>123</v>
+      </c>
+      <c r="K12" s="28" t="s">
+        <v>124</v>
+      </c>
+      <c r="L12" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="M12" s="28" t="s">
+        <v>126</v>
+      </c>
+      <c r="N12" s="28" t="s">
+        <v>127</v>
+      </c>
+      <c r="O12" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="P12" s="29" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="13" s="2" customFormat="1" ht="57" customHeight="1" spans="1:17">
+      <c r="A13" s="20" t="s">
+        <v>130</v>
+      </c>
+      <c r="B13" s="20" t="s">
+        <v>131</v>
+      </c>
+      <c r="C13" s="20" t="s">
+        <v>132</v>
+      </c>
+      <c r="D13" s="21" t="s">
+        <v>133</v>
+      </c>
+      <c r="E13" s="21" t="s">
+        <v>134</v>
+      </c>
+      <c r="F13" s="21" t="s">
+        <v>135</v>
+      </c>
+      <c r="G13" s="21" t="s">
+        <v>136</v>
+      </c>
+      <c r="H13" s="21" t="s">
+        <v>137</v>
+      </c>
+      <c r="I13" s="21" t="s">
+        <v>138</v>
+      </c>
+      <c r="J13" s="21" t="s">
+        <v>139</v>
+      </c>
+      <c r="K13" s="21" t="s">
+        <v>140</v>
+      </c>
+      <c r="L13" s="21" t="s">
+        <v>141</v>
+      </c>
+      <c r="M13" s="21" t="s">
+        <v>142</v>
+      </c>
+      <c r="N13" s="21" t="s">
+        <v>143</v>
+      </c>
+      <c r="O13" s="22" t="s">
+        <v>144</v>
+      </c>
+      <c r="P13" s="23" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="14" s="2" customFormat="1" ht="63" customHeight="1" spans="1:17">
+      <c r="A14" s="20"/>
+      <c r="B14" s="20"/>
+      <c r="C14" s="20" t="s">
+        <v>146</v>
+      </c>
+      <c r="D14" s="21" t="s">
+        <v>147</v>
+      </c>
+      <c r="E14" s="21" t="s">
+        <v>148</v>
+      </c>
+      <c r="F14" s="21" t="s">
+        <v>149</v>
+      </c>
+      <c r="G14" s="21" t="s">
+        <v>150</v>
+      </c>
+      <c r="H14" s="21" t="s">
+        <v>151</v>
+      </c>
+      <c r="I14" s="21" t="s">
+        <v>152</v>
+      </c>
+      <c r="J14" s="21" t="s">
+        <v>153</v>
+      </c>
+      <c r="K14" s="21" t="s">
+        <v>154</v>
+      </c>
+      <c r="L14" s="21" t="s">
+        <v>155</v>
+      </c>
+      <c r="M14" s="21" t="s">
+        <v>156</v>
+      </c>
+      <c r="N14" s="21" t="s">
+        <v>157</v>
+      </c>
+      <c r="O14" s="22" t="s">
+        <v>158</v>
+      </c>
+      <c r="P14" s="23" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="15" s="2" customFormat="1" ht="33" customHeight="1" spans="1:17">
+      <c r="A15" s="20"/>
+      <c r="B15" s="20" t="s">
+        <v>160</v>
+      </c>
+      <c r="C15" s="20"/>
+      <c r="D15" s="21" t="s">
+        <v>161</v>
+      </c>
+      <c r="E15" s="21" t="s">
+        <v>162</v>
+      </c>
+      <c r="F15" s="21" t="s">
+        <v>163</v>
+      </c>
+      <c r="G15" s="21" t="s">
+        <v>164</v>
+      </c>
+      <c r="H15" s="21" t="s">
+        <v>165</v>
+      </c>
+      <c r="I15" s="21" t="s">
+        <v>166</v>
+      </c>
+      <c r="J15" s="21" t="s">
+        <v>167</v>
+      </c>
+      <c r="K15" s="21" t="s">
+        <v>168</v>
+      </c>
+      <c r="L15" s="21" t="s">
+        <v>169</v>
+      </c>
+      <c r="M15" s="21" t="s">
+        <v>170</v>
+      </c>
+      <c r="N15" s="21" t="s">
+        <v>171</v>
+      </c>
+      <c r="O15" s="22" t="s">
+        <v>172</v>
+      </c>
+      <c r="P15" s="23" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="16" s="2" customFormat="1" ht="33" customHeight="1" spans="1:17">
+      <c r="A16" s="20"/>
+      <c r="B16" s="30" t="s">
+        <v>174</v>
+      </c>
+      <c r="C16" s="31"/>
+      <c r="D16" s="21" t="s">
+        <v>175</v>
+      </c>
+      <c r="E16" s="21" t="s">
+        <v>176</v>
+      </c>
+      <c r="F16" s="21" t="s">
+        <v>177</v>
+      </c>
+      <c r="G16" s="21" t="s">
+        <v>178</v>
+      </c>
+      <c r="H16" s="21" t="s">
+        <v>179</v>
+      </c>
+      <c r="I16" s="21" t="s">
+        <v>180</v>
+      </c>
+      <c r="J16" s="21" t="s">
+        <v>181</v>
+      </c>
+      <c r="K16" s="21" t="s">
+        <v>182</v>
+      </c>
+      <c r="L16" s="21" t="s">
+        <v>183</v>
+      </c>
+      <c r="M16" s="21" t="s">
+        <v>184</v>
+      </c>
+      <c r="N16" s="21" t="s">
+        <v>185</v>
+      </c>
+      <c r="O16" s="22" t="s">
+        <v>186</v>
+      </c>
+      <c r="P16" s="23" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="17" s="2" customFormat="1" ht="33" customHeight="1" spans="1:16">
+      <c r="A17" s="20"/>
+      <c r="B17" s="30" t="s">
+        <v>188</v>
+      </c>
+      <c r="C17" s="31"/>
+      <c r="D17" s="21" t="s">
+        <v>189</v>
+      </c>
+      <c r="E17" s="21" t="s">
+        <v>190</v>
+      </c>
+      <c r="F17" s="21" t="s">
+        <v>191</v>
+      </c>
+      <c r="G17" s="21" t="s">
+        <v>192</v>
+      </c>
+      <c r="H17" s="21" t="s">
+        <v>193</v>
+      </c>
+      <c r="I17" s="21" t="s">
+        <v>194</v>
+      </c>
+      <c r="J17" s="21" t="s">
+        <v>195</v>
+      </c>
+      <c r="K17" s="21" t="s">
+        <v>196</v>
+      </c>
+      <c r="L17" s="21" t="s">
+        <v>197</v>
+      </c>
+      <c r="M17" s="21" t="s">
+        <v>198</v>
+      </c>
+      <c r="N17" s="21" t="s">
+        <v>199</v>
+      </c>
+      <c r="O17" s="22" t="s">
+        <v>200</v>
+      </c>
+      <c r="P17" s="23" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="18" s="3" customFormat="1" ht="33" customHeight="1" spans="1:16">
+      <c r="A18" s="27"/>
+      <c r="B18" s="32" t="s">
+        <v>203</v>
+      </c>
+      <c r="C18" s="33"/>
+      <c r="D18" s="28" t="s">
+        <v>204</v>
+      </c>
+      <c r="E18" s="28" t="s">
+        <v>205</v>
+      </c>
+      <c r="F18" s="28" t="s">
+        <v>206</v>
+      </c>
+      <c r="G18" s="28" t="s">
+        <v>207</v>
+      </c>
+      <c r="H18" s="28" t="s">
+        <v>208</v>
+      </c>
+      <c r="I18" s="28" t="s">
+        <v>209</v>
+      </c>
+      <c r="J18" s="28" t="s">
+        <v>210</v>
+      </c>
+      <c r="K18" s="28" t="s">
+        <v>211</v>
+      </c>
+      <c r="L18" s="28" t="s">
+        <v>212</v>
+      </c>
+      <c r="M18" s="28" t="s">
+        <v>213</v>
+      </c>
+      <c r="N18" s="28" t="s">
+        <v>214</v>
+      </c>
+      <c r="O18" s="28" t="s">
+        <v>215</v>
+      </c>
+      <c r="P18" s="29" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="19" s="3" customFormat="1" ht="42" customHeight="1" spans="1:16">
+      <c r="A19" s="34" t="s">
+        <v>217</v>
+      </c>
+      <c r="B19" s="34"/>
+      <c r="C19" s="34"/>
+      <c r="D19" s="35" t="s">
+        <v>218</v>
+      </c>
+      <c r="E19" s="35" t="s">
+        <v>219</v>
+      </c>
+      <c r="F19" s="35" t="s">
+        <v>220</v>
+      </c>
+      <c r="G19" s="35" t="s">
+        <v>221</v>
+      </c>
+      <c r="H19" s="35" t="s">
+        <v>222</v>
+      </c>
+      <c r="I19" s="35" t="s">
+        <v>223</v>
+      </c>
+      <c r="J19" s="35" t="s">
+        <v>224</v>
+      </c>
+      <c r="K19" s="35" t="s">
+        <v>225</v>
+      </c>
+      <c r="L19" s="35" t="s">
+        <v>226</v>
+      </c>
+      <c r="M19" s="35" t="s">
+        <v>227</v>
+      </c>
+      <c r="N19" s="35" t="s">
+        <v>228</v>
+      </c>
+      <c r="O19" s="35" t="s">
+        <v>229</v>
+      </c>
+      <c r="P19" s="29" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="20" ht="38" customHeight="1" spans="1:16">
+      <c r="A20" s="36" t="s">
+        <v>237</v>
+      </c>
+      <c r="B20" s="36"/>
+      <c r="C20" s="36"/>
+      <c r="D20" s="37" t="s">
+        <v>238</v>
+      </c>
+      <c r="E20" s="37" t="s">
+        <v>239</v>
+      </c>
+      <c r="F20" s="37" t="s">
+        <v>240</v>
+      </c>
+      <c r="G20" s="37" t="s">
+        <v>241</v>
+      </c>
+      <c r="H20" s="37" t="s">
+        <v>242</v>
+      </c>
+      <c r="I20" s="37" t="s">
+        <v>243</v>
+      </c>
+      <c r="J20" s="37" t="s">
+        <v>244</v>
+      </c>
+      <c r="K20" s="37" t="s">
+        <v>245</v>
+      </c>
+      <c r="L20" s="37" t="s">
+        <v>246</v>
+      </c>
+      <c r="M20" s="37" t="s">
+        <v>247</v>
+      </c>
+      <c r="N20" s="37" t="s">
+        <v>248</v>
+      </c>
+      <c r="O20" s="37" t="s">
+        <v>249</v>
+      </c>
+      <c r="P20" s="37" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="21" s="4" customFormat="1" ht="78" customHeight="1" spans="1:16">
+      <c r="A21" s="2" t="s">
         <v>234</v>
-      </c>
-      <c r="E5" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="F5" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="G5" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="H5" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="I5" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="J5" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="K5" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="L5" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="M5" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="N5" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="O5" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="P5" s="37" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q5" s="42" t="s">
-        <v>31</v>
-      </c>
-      <c r="R5" s="41"/>
-    </row>
-    <row r="6" s="2" customFormat="1" ht="33" customHeight="1" spans="1:18">
-      <c r="A6" s="12"/>
-      <c r="B6" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="C6" s="12"/>
-      <c r="D6" s="13" t="s">
-        <v>234</v>
-      </c>
-      <c r="E6" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="F6" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="G6" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="H6" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="I6" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="J6" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="K6" s="14" t="s">
-        <v>39</v>
-      </c>
-      <c r="L6" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="M6" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="N6" s="14" t="s">
-        <v>42</v>
-      </c>
-      <c r="O6" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="P6" s="37" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q6" s="42" t="s">
-        <v>45</v>
-      </c>
-      <c r="R6" s="43" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="7" s="2" customFormat="1" ht="33" customHeight="1" spans="1:18">
-      <c r="A7" s="12"/>
-      <c r="B7" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="C7" s="12"/>
-      <c r="D7" s="13" t="s">
-        <v>234</v>
-      </c>
-      <c r="E7" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="F7" s="14" t="s">
-        <v>48</v>
-      </c>
-      <c r="G7" s="14" t="s">
-        <v>49</v>
-      </c>
-      <c r="H7" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="I7" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="J7" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="K7" s="14" t="s">
-        <v>53</v>
-      </c>
-      <c r="L7" s="14" t="s">
-        <v>54</v>
-      </c>
-      <c r="M7" s="14" t="s">
-        <v>55</v>
-      </c>
-      <c r="N7" s="14" t="s">
-        <v>56</v>
-      </c>
-      <c r="O7" s="14" t="s">
-        <v>57</v>
-      </c>
-      <c r="P7" s="37" t="s">
-        <v>58</v>
-      </c>
-      <c r="Q7" s="42" t="s">
-        <v>59</v>
-      </c>
-      <c r="R7" s="44"/>
-    </row>
-    <row r="8" s="2" customFormat="1" ht="33" customHeight="1" spans="1:18">
-      <c r="A8" s="12"/>
-      <c r="B8" s="12" t="s">
-        <v>60</v>
-      </c>
-      <c r="C8" s="12"/>
-      <c r="D8" s="13" t="s">
-        <v>234</v>
-      </c>
-      <c r="E8" s="14" t="s">
-        <v>61</v>
-      </c>
-      <c r="F8" s="14" t="s">
-        <v>62</v>
-      </c>
-      <c r="G8" s="14" t="s">
-        <v>63</v>
-      </c>
-      <c r="H8" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="I8" s="14" t="s">
-        <v>65</v>
-      </c>
-      <c r="J8" s="14" t="s">
-        <v>66</v>
-      </c>
-      <c r="K8" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="L8" s="14" t="s">
-        <v>68</v>
-      </c>
-      <c r="M8" s="14" t="s">
-        <v>69</v>
-      </c>
-      <c r="N8" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="O8" s="14" t="s">
-        <v>71</v>
-      </c>
-      <c r="P8" s="37" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q8" s="42" t="s">
-        <v>73</v>
-      </c>
-      <c r="R8" s="44"/>
-    </row>
-    <row r="9" s="2" customFormat="1" ht="33" customHeight="1" spans="1:18">
-      <c r="A9" s="12"/>
-      <c r="B9" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="C9" s="12"/>
-      <c r="D9" s="14">
-        <f>970000</f>
-        <v>970000</v>
-      </c>
-      <c r="E9" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="F9" s="14" t="s">
-        <v>76</v>
-      </c>
-      <c r="G9" s="14" t="s">
-        <v>77</v>
-      </c>
-      <c r="H9" s="14" t="s">
-        <v>78</v>
-      </c>
-      <c r="I9" s="14" t="s">
-        <v>79</v>
-      </c>
-      <c r="J9" s="14" t="s">
-        <v>80</v>
-      </c>
-      <c r="K9" s="14" t="s">
-        <v>81</v>
-      </c>
-      <c r="L9" s="14" t="s">
-        <v>82</v>
-      </c>
-      <c r="M9" s="14" t="s">
-        <v>83</v>
-      </c>
-      <c r="N9" s="14" t="s">
-        <v>84</v>
-      </c>
-      <c r="O9" s="14" t="s">
-        <v>85</v>
-      </c>
-      <c r="P9" s="37" t="s">
-        <v>86</v>
-      </c>
-      <c r="Q9" s="42" t="s">
-        <v>87</v>
-      </c>
-      <c r="R9" s="45"/>
-    </row>
-    <row r="10" s="2" customFormat="1" ht="33" customHeight="1" spans="1:17">
-      <c r="A10" s="12"/>
-      <c r="B10" s="12" t="s">
-        <v>88</v>
-      </c>
-      <c r="C10" s="12"/>
-      <c r="D10" s="13" t="s">
-        <v>234</v>
-      </c>
-      <c r="E10" s="14" t="s">
-        <v>89</v>
-      </c>
-      <c r="F10" s="14" t="s">
-        <v>90</v>
-      </c>
-      <c r="G10" s="14" t="s">
-        <v>91</v>
-      </c>
-      <c r="H10" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="I10" s="14" t="s">
-        <v>93</v>
-      </c>
-      <c r="J10" s="14" t="s">
-        <v>94</v>
-      </c>
-      <c r="K10" s="14" t="s">
-        <v>95</v>
-      </c>
-      <c r="L10" s="14" t="s">
-        <v>96</v>
-      </c>
-      <c r="M10" s="14" t="s">
-        <v>97</v>
-      </c>
-      <c r="N10" s="14" t="s">
-        <v>98</v>
-      </c>
-      <c r="O10" s="14" t="s">
-        <v>99</v>
-      </c>
-      <c r="P10" s="14" t="s">
-        <v>100</v>
-      </c>
-      <c r="Q10" s="42" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="11" s="2" customFormat="1" ht="33" customHeight="1" spans="1:17">
-      <c r="A11" s="12"/>
-      <c r="B11" s="12" t="s">
-        <v>102</v>
-      </c>
-      <c r="C11" s="12"/>
-      <c r="D11" s="13" t="s">
-        <v>234</v>
-      </c>
-      <c r="E11" s="14" t="s">
-        <v>103</v>
-      </c>
-      <c r="F11" s="14" t="s">
-        <v>104</v>
-      </c>
-      <c r="G11" s="14" t="s">
-        <v>105</v>
-      </c>
-      <c r="H11" s="14" t="s">
-        <v>106</v>
-      </c>
-      <c r="I11" s="14" t="s">
-        <v>107</v>
-      </c>
-      <c r="J11" s="14" t="s">
-        <v>108</v>
-      </c>
-      <c r="K11" s="14" t="s">
-        <v>109</v>
-      </c>
-      <c r="L11" s="14" t="s">
-        <v>110</v>
-      </c>
-      <c r="M11" s="14" t="s">
-        <v>111</v>
-      </c>
-      <c r="N11" s="14" t="s">
-        <v>112</v>
-      </c>
-      <c r="O11" s="14" t="s">
-        <v>113</v>
-      </c>
-      <c r="P11" s="37" t="s">
-        <v>114</v>
-      </c>
-      <c r="Q11" s="42" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="12" s="3" customFormat="1" ht="33" customHeight="1" spans="1:17">
-      <c r="A12" s="15"/>
-      <c r="B12" s="15" t="s">
-        <v>116</v>
-      </c>
-      <c r="C12" s="15"/>
-      <c r="D12" s="16" t="s">
-        <v>234</v>
-      </c>
-      <c r="E12" s="30" t="s">
-        <v>117</v>
-      </c>
-      <c r="F12" s="30" t="s">
-        <v>118</v>
-      </c>
-      <c r="G12" s="30" t="s">
-        <v>119</v>
-      </c>
-      <c r="H12" s="30" t="s">
-        <v>120</v>
-      </c>
-      <c r="I12" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="J12" s="30" t="s">
-        <v>122</v>
-      </c>
-      <c r="K12" s="30" t="s">
-        <v>123</v>
-      </c>
-      <c r="L12" s="30" t="s">
-        <v>124</v>
-      </c>
-      <c r="M12" s="30" t="s">
-        <v>125</v>
-      </c>
-      <c r="N12" s="30" t="s">
-        <v>126</v>
-      </c>
-      <c r="O12" s="30" t="s">
-        <v>127</v>
-      </c>
-      <c r="P12" s="30" t="s">
-        <v>128</v>
-      </c>
-      <c r="Q12" s="46" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="13" s="2" customFormat="1" ht="57" customHeight="1" spans="1:17">
-      <c r="A13" s="12" t="s">
-        <v>130</v>
-      </c>
-      <c r="B13" s="12" t="s">
-        <v>131</v>
-      </c>
-      <c r="C13" s="12" t="s">
-        <v>132</v>
-      </c>
-      <c r="D13" s="13" t="s">
-        <v>234</v>
-      </c>
-      <c r="E13" s="14" t="s">
-        <v>133</v>
-      </c>
-      <c r="F13" s="14" t="s">
-        <v>134</v>
-      </c>
-      <c r="G13" s="14" t="s">
-        <v>135</v>
-      </c>
-      <c r="H13" s="14" t="s">
-        <v>136</v>
-      </c>
-      <c r="I13" s="14" t="s">
-        <v>137</v>
-      </c>
-      <c r="J13" s="14" t="s">
-        <v>138</v>
-      </c>
-      <c r="K13" s="14" t="s">
-        <v>139</v>
-      </c>
-      <c r="L13" s="14" t="s">
-        <v>140</v>
-      </c>
-      <c r="M13" s="14" t="s">
-        <v>141</v>
-      </c>
-      <c r="N13" s="14" t="s">
-        <v>142</v>
-      </c>
-      <c r="O13" s="14" t="s">
-        <v>143</v>
-      </c>
-      <c r="P13" s="37" t="s">
-        <v>144</v>
-      </c>
-      <c r="Q13" s="42" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="14" s="2" customFormat="1" ht="63" customHeight="1" spans="1:17">
-      <c r="A14" s="12"/>
-      <c r="B14" s="12"/>
-      <c r="C14" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="D14" s="13" t="s">
-        <v>234</v>
-      </c>
-      <c r="E14" s="14" t="s">
-        <v>147</v>
-      </c>
-      <c r="F14" s="14" t="s">
-        <v>148</v>
-      </c>
-      <c r="G14" s="14" t="s">
-        <v>149</v>
-      </c>
-      <c r="H14" s="14" t="s">
-        <v>150</v>
-      </c>
-      <c r="I14" s="14" t="s">
-        <v>151</v>
-      </c>
-      <c r="J14" s="14" t="s">
-        <v>152</v>
-      </c>
-      <c r="K14" s="14" t="s">
-        <v>153</v>
-      </c>
-      <c r="L14" s="14" t="s">
-        <v>154</v>
-      </c>
-      <c r="M14" s="14" t="s">
-        <v>155</v>
-      </c>
-      <c r="N14" s="14" t="s">
-        <v>156</v>
-      </c>
-      <c r="O14" s="14" t="s">
-        <v>157</v>
-      </c>
-      <c r="P14" s="37" t="s">
-        <v>158</v>
-      </c>
-      <c r="Q14" s="42" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="15" s="2" customFormat="1" ht="33" customHeight="1" spans="1:17">
-      <c r="A15" s="12"/>
-      <c r="B15" s="12" t="s">
-        <v>160</v>
-      </c>
-      <c r="C15" s="12"/>
-      <c r="D15" s="13" t="s">
-        <v>234</v>
-      </c>
-      <c r="E15" s="14" t="s">
-        <v>161</v>
-      </c>
-      <c r="F15" s="14" t="s">
-        <v>162</v>
-      </c>
-      <c r="G15" s="14" t="s">
-        <v>163</v>
-      </c>
-      <c r="H15" s="14" t="s">
-        <v>164</v>
-      </c>
-      <c r="I15" s="14" t="s">
-        <v>165</v>
-      </c>
-      <c r="J15" s="14" t="s">
-        <v>166</v>
-      </c>
-      <c r="K15" s="14" t="s">
-        <v>167</v>
-      </c>
-      <c r="L15" s="14" t="s">
-        <v>168</v>
-      </c>
-      <c r="M15" s="14" t="s">
-        <v>169</v>
-      </c>
-      <c r="N15" s="14" t="s">
-        <v>170</v>
-      </c>
-      <c r="O15" s="14" t="s">
-        <v>171</v>
-      </c>
-      <c r="P15" s="37" t="s">
-        <v>172</v>
-      </c>
-      <c r="Q15" s="42" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="16" s="2" customFormat="1" ht="33" customHeight="1" spans="1:17">
-      <c r="A16" s="12"/>
-      <c r="B16" s="17" t="s">
-        <v>174</v>
-      </c>
-      <c r="C16" s="18"/>
-      <c r="D16" s="19" t="s">
-        <v>234</v>
-      </c>
-      <c r="E16" s="14" t="s">
-        <v>175</v>
-      </c>
-      <c r="F16" s="14" t="s">
-        <v>176</v>
-      </c>
-      <c r="G16" s="14" t="s">
-        <v>177</v>
-      </c>
-      <c r="H16" s="14" t="s">
-        <v>178</v>
-      </c>
-      <c r="I16" s="14" t="s">
-        <v>179</v>
-      </c>
-      <c r="J16" s="14" t="s">
-        <v>180</v>
-      </c>
-      <c r="K16" s="14" t="s">
-        <v>181</v>
-      </c>
-      <c r="L16" s="14" t="s">
-        <v>182</v>
-      </c>
-      <c r="M16" s="14" t="s">
-        <v>183</v>
-      </c>
-      <c r="N16" s="14" t="s">
-        <v>184</v>
-      </c>
-      <c r="O16" s="14" t="s">
-        <v>185</v>
-      </c>
-      <c r="P16" s="37" t="s">
-        <v>186</v>
-      </c>
-      <c r="Q16" s="42" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="17" s="2" customFormat="1" ht="33" customHeight="1" spans="1:17">
-      <c r="A17" s="12"/>
-      <c r="B17" s="17" t="s">
-        <v>188</v>
-      </c>
-      <c r="C17" s="18"/>
-      <c r="D17" s="19" t="s">
-        <v>234</v>
-      </c>
-      <c r="E17" s="14" t="s">
-        <v>189</v>
-      </c>
-      <c r="F17" s="14" t="s">
-        <v>190</v>
-      </c>
-      <c r="G17" s="14" t="s">
-        <v>191</v>
-      </c>
-      <c r="H17" s="14" t="s">
-        <v>192</v>
-      </c>
-      <c r="I17" s="14" t="s">
-        <v>193</v>
-      </c>
-      <c r="J17" s="14" t="s">
-        <v>194</v>
-      </c>
-      <c r="K17" s="14" t="s">
-        <v>195</v>
-      </c>
-      <c r="L17" s="14" t="s">
-        <v>196</v>
-      </c>
-      <c r="M17" s="14" t="s">
-        <v>197</v>
-      </c>
-      <c r="N17" s="14" t="s">
-        <v>198</v>
-      </c>
-      <c r="O17" s="14" t="s">
-        <v>199</v>
-      </c>
-      <c r="P17" s="37" t="s">
-        <v>200</v>
-      </c>
-      <c r="Q17" s="42" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="18" s="3" customFormat="1" ht="33" customHeight="1" spans="1:17">
-      <c r="A18" s="15"/>
-      <c r="B18" s="20" t="s">
-        <v>203</v>
-      </c>
-      <c r="C18" s="21"/>
-      <c r="D18" s="22" t="s">
-        <v>234</v>
-      </c>
-      <c r="E18" s="30" t="s">
-        <v>204</v>
-      </c>
-      <c r="F18" s="30" t="s">
-        <v>205</v>
-      </c>
-      <c r="G18" s="30" t="s">
-        <v>206</v>
-      </c>
-      <c r="H18" s="30" t="s">
-        <v>207</v>
-      </c>
-      <c r="I18" s="30" t="s">
-        <v>208</v>
-      </c>
-      <c r="J18" s="30" t="s">
-        <v>209</v>
-      </c>
-      <c r="K18" s="30" t="s">
-        <v>210</v>
-      </c>
-      <c r="L18" s="30" t="s">
-        <v>211</v>
-      </c>
-      <c r="M18" s="30" t="s">
-        <v>212</v>
-      </c>
-      <c r="N18" s="30" t="s">
-        <v>213</v>
-      </c>
-      <c r="O18" s="30" t="s">
-        <v>214</v>
-      </c>
-      <c r="P18" s="30" t="s">
-        <v>215</v>
-      </c>
-      <c r="Q18" s="46" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="19" s="3" customFormat="1" ht="42" customHeight="1" spans="1:17">
-      <c r="A19" s="23" t="s">
-        <v>217</v>
-      </c>
-      <c r="B19" s="23"/>
-      <c r="C19" s="23"/>
-      <c r="D19" s="24" t="s">
-        <v>234</v>
-      </c>
-      <c r="E19" s="31" t="s">
-        <v>218</v>
-      </c>
-      <c r="F19" s="31" t="s">
-        <v>219</v>
-      </c>
-      <c r="G19" s="31" t="s">
-        <v>220</v>
-      </c>
-      <c r="H19" s="31" t="s">
-        <v>221</v>
-      </c>
-      <c r="I19" s="31" t="s">
-        <v>222</v>
-      </c>
-      <c r="J19" s="31" t="s">
-        <v>223</v>
-      </c>
-      <c r="K19" s="31" t="s">
-        <v>224</v>
-      </c>
-      <c r="L19" s="31" t="s">
-        <v>225</v>
-      </c>
-      <c r="M19" s="31" t="s">
-        <v>226</v>
-      </c>
-      <c r="N19" s="31" t="s">
-        <v>227</v>
-      </c>
-      <c r="O19" s="31" t="s">
-        <v>228</v>
-      </c>
-      <c r="P19" s="31" t="s">
-        <v>229</v>
-      </c>
-      <c r="Q19" s="46" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="20" ht="38" customHeight="1" spans="1:17">
-      <c r="A20" s="25" t="s">
-        <v>241</v>
-      </c>
-      <c r="B20" s="25"/>
-      <c r="C20" s="25"/>
-      <c r="D20" s="25"/>
-      <c r="E20" s="32" t="s">
-        <v>242</v>
-      </c>
-      <c r="F20" s="32" t="s">
-        <v>243</v>
-      </c>
-      <c r="G20" s="32" t="s">
-        <v>244</v>
-      </c>
-      <c r="H20" s="32" t="s">
-        <v>245</v>
-      </c>
-      <c r="I20" s="32" t="s">
-        <v>246</v>
-      </c>
-      <c r="J20" s="32" t="s">
-        <v>247</v>
-      </c>
-      <c r="K20" s="32" t="s">
-        <v>248</v>
-      </c>
-      <c r="L20" s="32" t="s">
-        <v>249</v>
-      </c>
-      <c r="M20" s="32" t="s">
-        <v>250</v>
-      </c>
-      <c r="N20" s="32" t="s">
-        <v>251</v>
-      </c>
-      <c r="O20" s="32" t="s">
-        <v>252</v>
-      </c>
-      <c r="P20" s="32" t="s">
-        <v>253</v>
-      </c>
-      <c r="Q20" s="32" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="21" s="4" customFormat="1" ht="78" customHeight="1" spans="1:17">
-      <c r="A21" s="2" t="s">
-        <v>236</v>
       </c>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
-      <c r="D21" s="2"/>
-      <c r="E21" s="33" t="s">
-        <v>255</v>
-      </c>
-      <c r="F21" s="33" t="s">
-        <v>256</v>
-      </c>
-      <c r="G21" s="33" t="s">
-        <v>257</v>
-      </c>
-      <c r="H21" s="34"/>
-      <c r="I21" s="34"/>
-      <c r="J21" s="34"/>
-      <c r="K21" s="34"/>
-      <c r="L21" s="34"/>
-      <c r="M21" s="34"/>
-      <c r="N21" s="34"/>
-      <c r="O21" s="34"/>
-      <c r="P21" s="34"/>
-      <c r="Q21" s="34"/>
+      <c r="D21" s="38"/>
+      <c r="E21" s="38"/>
+      <c r="F21" s="38"/>
+      <c r="G21" s="39"/>
+      <c r="H21" s="39"/>
+      <c r="I21" s="39"/>
+      <c r="J21" s="39"/>
+      <c r="K21" s="39"/>
+      <c r="L21" s="39"/>
+      <c r="M21" s="39"/>
+      <c r="N21" s="39"/>
+      <c r="O21" s="39"/>
+      <c r="P21" s="39"/>
     </row>
   </sheetData>
-  <mergeCells count="26">
-    <mergeCell ref="A1:Q1"/>
-    <mergeCell ref="A2:Q2"/>
-    <mergeCell ref="E3:P3"/>
+  <mergeCells count="25">
+    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="A2:P2"/>
+    <mergeCell ref="D3:O3"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="B7:C7"/>
@@ -6080,10 +5877,9 @@
     <mergeCell ref="A5:A12"/>
     <mergeCell ref="A13:A18"/>
     <mergeCell ref="B13:B14"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="Q3:Q4"/>
-    <mergeCell ref="R3:R5"/>
-    <mergeCell ref="R6:R9"/>
+    <mergeCell ref="P3:P4"/>
+    <mergeCell ref="Q3:Q5"/>
+    <mergeCell ref="Q6:Q9"/>
     <mergeCell ref="A3:C4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511805555555556" footer="0.511805555555556"/>
